--- a/Security-data/data/output/ccs_2025_us_institutions.xlsx
+++ b/Security-data/data/output/ccs_2025_us_institutions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E409"/>
+  <dimension ref="A1:E411"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2102,7 +2102,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sam A. Markelon</t>
+          <t>Jaehyung Kim 0002</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -2110,22 +2110,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>CCS-Probabilistic Skipping-Based Data Structures with Robust Efficiency Guarantees.</t>
+          <t>CCS-Grafting: Decoupled Scale Factors and Modulus in RNS-CKKS.</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>University of Florida</t>
+          <t>Stanford University</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Gefei Tan</t>
+          <t>Sam A. Markelon</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -2133,22 +2133,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CCS-Founding Zero-Knowledge Proof of Training on Optimum Vicinity.</t>
+          <t>CCS-Probabilistic Skipping-Based Data Structures with Robust Efficiency Guarantees.</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Northwestern University</t>
+          <t>University of Florida</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Adrià Gascón</t>
+          <t>Gefei Tan</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -2160,18 +2160,18 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>Northwestern University</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Mariana Raykova 0001</t>
+          <t>Adrià Gascón</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -2183,7 +2183,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Xiao Wang 0012</t>
+          <t>Mariana Raykova 0001</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -2206,18 +2206,18 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Northwestern University</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Xiaolin Li 0015</t>
+          <t>Xiao Wang 0012</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -2225,22 +2225,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>CCS-Mitigating Data Poisoning Attacks to Local Differential Privacy.</t>
+          <t>CCS-Founding Zero-Knowledge Proof of Training on Optimum Vicinity.</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>Northwestern University</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Ninghui Li 0001</t>
+          <t>Xiaolin Li 0015</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Boyang Wang 0001</t>
+          <t>Ninghui Li 0001</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -2275,18 +2275,18 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>University of Cincinnati</t>
+          <t>Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Wenhai Sun</t>
+          <t>Boyang Wang 0001</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -2298,18 +2298,18 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>University of Cincinnati</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Ali Naseh</t>
+          <t>Wenhai Sun</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -2317,22 +2317,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CCS-Riddle Me This! Stealthy Membership Inference for Retrieval-Augmented Generation.</t>
+          <t>CCS-Mitigating Data Poisoning Attacks to Local Differential Privacy.</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>University of Massachusetts Amherst</t>
+          <t>Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Yuefeng Peng</t>
+          <t>Ali Naseh</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Anshuman Suri</t>
+          <t>Yuefeng Peng</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -2367,18 +2367,18 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>University of Massachusetts Amherst</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Harsh Chaudhari</t>
+          <t>Anshuman Suri</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -2390,7 +2390,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Alina Oprea</t>
+          <t>Harsh Chaudhari</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Amir Houmansadr</t>
+          <t>Alina Oprea</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -2436,18 +2436,18 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>University of Massachusetts Amherst</t>
+          <t>Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Alexandra Nisenoff</t>
+          <t>Amir Houmansadr</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -2455,22 +2455,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>CCS-Exploiting the Shared Storage API.</t>
+          <t>CCS-Riddle Me This! Stealthy Membership Inference for Retrieval-Augmented Generation.</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>University of Massachusetts Amherst</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Deian Stefan</t>
+          <t>Alexandra Nisenoff</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -2482,18 +2482,18 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>University of California San Diego</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Nicolas Christin</t>
+          <t>Deian Stefan</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -2505,18 +2505,18 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>University of California San Diego</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Michael A. Specter</t>
+          <t>Nicolas Christin</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>CCS-Fingerprinting SDKs for Mobile Apps and Where to Find Them: Understanding the Market for Device Fingerprinting.</t>
+          <t>CCS-Exploiting the Shared Storage API.</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Mihai Christodorescu</t>
+          <t>Michael A. Specter</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -2551,7 +2551,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Abbie Farr</t>
+          <t>Mihai Christodorescu</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -2574,7 +2574,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Bo Ma 0013</t>
+          <t>Abbie Farr</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Robin Lassonde</t>
+          <t>Bo Ma 0013</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Haichuan Xu</t>
+          <t>Robin Lassonde</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -2639,22 +2639,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>CCS-Lock the Door But Keep the Window Open: Extracting App-Protected Accessibility Information from Browser-Rendered Websites.</t>
+          <t>CCS-Fingerprinting SDKs for Mobile Apps and Where to Find Them: Understanding the Market for Device Fingerprinting.</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Runze Zhang</t>
+          <t>Haichuan Xu</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Mingxuan Yao</t>
+          <t>Runze Zhang</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -2689,7 +2689,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>David Oygenblik</t>
+          <t>Mingxuan Yao</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -2712,7 +2712,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Brendan Saltaformaggio</t>
+          <t>David Oygenblik</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -2735,7 +2735,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Alisha Ukani</t>
+          <t>Brendan Saltaformaggio</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -2754,22 +2754,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>CCS-Local Frames: Exploiting Inherited Origins to Bypass Content Blockers.</t>
+          <t>CCS-Lock the Door But Keep the Window Open: Extracting App-Protected Accessibility Information from Browser-Rendered Websites.</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>University of California San Diego</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Alex C. Snoeren</t>
+          <t>Alisha Ukani</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Jonathan Fuller</t>
+          <t>Alex C. Snoeren</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -2800,22 +2800,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>CCS-Enhanced Web Application Security Through Proactive Dead Drop Resolver Remediation.</t>
+          <t>CCS-Local Frames: Exploiting Inherited Origins to Bypass Content Blockers.</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>United States Military Academy</t>
+          <t>University of California San Diego</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Mingxuan Yao</t>
+          <t>Jonathan Fuller</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -2827,18 +2827,18 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>United States Military Academy</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Saumya Agarwal</t>
+          <t>Mingxuan Yao</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -2850,7 +2850,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Srimanta Barua</t>
+          <t>Saumya Agarwal</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Taleb Hirani</t>
+          <t>Srimanta Barua</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Brendan Saltaformaggio</t>
+          <t>Taleb Hirani</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -2919,7 +2919,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Simon Oddershede Gregersen</t>
+          <t>Brendan Saltaformaggio</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -2938,22 +2938,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>CCS-Logical Relations for Formally Verified Authenticated Data Structures.</t>
+          <t>CCS-Enhanced Web Application Security Through Proactive Dead Drop Resolver Remediation.</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>New York University</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Chaitanya Agarwal</t>
+          <t>Simon Oddershede Gregersen</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Joseph Tassarotti</t>
+          <t>Chaitanya Agarwal</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A. Prasad Sistla</t>
+          <t>Joseph Tassarotti</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>CCS-Approximate Algorithms for Verifying Differential Privacy with Gaussian Distributions.</t>
+          <t>CCS-Logical Relations for Formally Verified Authenticated Data Structures.</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -3015,14 +3015,14 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>University of Illinois Chicago</t>
+          <t>New York University</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Mahesh Viswanathan 0001</t>
+          <t>A. Prasad Sistla</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -3034,18 +3034,18 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>University of Illinois Chicago</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Anitha Gollamudi</t>
+          <t>Mahesh Viswanathan 0001</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -3053,22 +3053,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>CCS-ILA: Correctness via Type Checking for Fully Homomorphic Encryption.</t>
+          <t>CCS-Approximate Algorithms for Verifying Differential Privacy with Gaussian Distributions.</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>University of Massachusetts Lowell</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Joshua Gancher</t>
+          <t>Anitha Gollamudi</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -3080,18 +3080,18 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>University of Massachusetts Lowell</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Kangjie Lu</t>
+          <t>Joshua Gancher</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -3099,22 +3099,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>CCS-SyzParam: Incorporating Runtime Parameters into Kernel Driver Fuzzing.</t>
+          <t>CCS-ILA: Correctness via Type Checking for Fully Homomorphic Encryption.</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>University of Minnesota</t>
+          <t>Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Xin Wang 0001</t>
+          <t>Kangjie Lu</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -3122,22 +3122,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>CCS-FlowSentry: Accelerating NetFlow-based DDoS Detection.</t>
+          <t>CCS-SyzParam: Incorporating Runtime Parameters into Kernel Driver Fuzzing.</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Stony Brook University</t>
+          <t>University of Minnesota</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Ziming Zhao 0001</t>
+          <t>Xin Wang 0001</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -3145,22 +3145,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>CCS-5G-RNAKA : A Random Number-based Authentication and Key Agreement Protocol for 5G Systems.</t>
+          <t>CCS-FlowSentry: Accelerating NetFlow-based DDoS Detection.</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>Stony Brook University</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Xuening Xu</t>
+          <t>Ziming Zhao 0001</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -3168,22 +3168,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>CCS-Discovering and Exploiting IoT Device Hidden Attributes: A New Vulnerability in Smart Homes.</t>
+          <t>CCS-5G-RNAKA : A Random Number-based Authentication and Key Agreement Protocol for 5G Systems.</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Stevens Institute of Technology</t>
+          <t>Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Chenglong Fu 0002</t>
+          <t>Xuening Xu</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -3195,18 +3195,18 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>University of North Carolina at Charlotte</t>
+          <t>Stevens Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Xiaojiang Du</t>
+          <t>Chenglong Fu 0002</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -3218,18 +3218,18 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Stevens Institute of Technology</t>
+          <t>University of North Carolina at Charlotte</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Bo Luo</t>
+          <t>Xiaojiang Du</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -3241,18 +3241,18 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>University of Kansas</t>
+          <t>Stevens Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Shengzhi Zhang</t>
+          <t>Bo Luo</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -3260,22 +3260,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>CCS-RAG-WM: An Efficient Black-Box Watermarking Approach for Retrieval-Augmented Generation of Large Language Models.</t>
+          <t>CCS-Discovering and Exploiting IoT Device Hidden Attributes: A New Vulnerability in Smart Homes.</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Boston University; Metropolitan College of New York</t>
+          <t>University of Kansas</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Zhiqi Wang</t>
+          <t>Shengzhi Zhang</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -3283,22 +3283,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>CCS-Membership Inference Attacks as Privacy Tools: Reliability, Disparity and Ensemble.</t>
+          <t>CCS-RAG-WM: An Efficient Black-Box Watermarking Approach for Retrieval-Augmented Generation of Large Language Models.</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Rensselaer Polytechnic Institute</t>
+          <t>Boston University; Metropolitan College of New York</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Chengyu Zhang</t>
+          <t>Zhiqi Wang</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -3310,7 +3310,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Yuetian Chen</t>
+          <t>Chengyu Zhang</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -3333,7 +3333,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Nathalie Baracaldo</t>
+          <t>Yuetian Chen</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -3356,18 +3356,18 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>IBM Research - Almaden</t>
+          <t>Rensselaer Polytechnic Institute</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Lei Yu 0002</t>
+          <t>Nathalie Baracaldo</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -3379,18 +3379,18 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Rensselaer Polytechnic Institute</t>
+          <t>IBM Research - Almaden</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Jiahui Gao</t>
+          <t>Lei Yu 0002</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -3398,22 +3398,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>CCS-PULSE: Parallel Private Set Union for Large-Scale Entities.</t>
+          <t>CCS-Membership Inference Attacks as Privacy Tools: Reliability, Disparity and Ensemble.</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Rensselaer Polytechnic Institute</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Son Nguyen</t>
+          <t>Jiahui Gao</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -3425,7 +3425,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Ni Trieu</t>
+          <t>Son Nguyen</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -3448,7 +3448,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Akhil Bandarupalli</t>
+          <t>Ni Trieu</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -3467,22 +3467,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>CCS-Velox: Scalable Fair Asynchronous MPC from Lightweight Cryptography.</t>
+          <t>CCS-PULSE: Parallel Private Set Union for Large-Scale Entities.</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>David Adei</t>
+          <t>Akhil Bandarupalli</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>CCS-How to Recover a Cryptographic Secret From the Cloud.</t>
+          <t>CCS-Velox: Scalable Fair Asynchronous MPC from Lightweight Cryptography.</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -3498,14 +3498,14 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>North Carolina State University</t>
+          <t>Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Chris Orsini</t>
+          <t>David Adei</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Alessandra Scafuro</t>
+          <t>Chris Orsini</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -3540,7 +3540,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Tanner Verber</t>
+          <t>Alessandra Scafuro</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -3563,7 +3563,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Anuj Gautam</t>
+          <t>Tanner Verber</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -3582,22 +3582,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>CCS-Passwords and FIDO2 Are Meant To Be Secret: A Practical Secure Authentication Channel for Web Browsers.</t>
+          <t>CCS-How to Recover a Cryptographic Secret From the Cloud.</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>University of Tennessee at Knoxville</t>
+          <t>North Carolina State University</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Scott Ruoti</t>
+          <t>Anuj Gautam</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Ahsan Zafar</t>
+          <t>Scott Ruoti</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -3628,22 +3628,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>CCS-Same Script, Different Behavior: Characterizing Divergent JavaScript Execution Across Different Device Platforms.</t>
+          <t>CCS-Passwords and FIDO2 Are Meant To Be Secret: A Practical Secure Authentication Channel for Web Browsers.</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>North Carolina State University</t>
+          <t>University of Tennessee at Knoxville</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Junhua Su</t>
+          <t>Ahsan Zafar</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -3655,7 +3655,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Sohom Datta</t>
+          <t>Junhua Su</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Alexandros Kapravelos</t>
+          <t>Sohom Datta</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -3701,7 +3701,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Anupam Das 0001</t>
+          <t>Alexandros Kapravelos</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -3724,7 +3724,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Ahmet Okutan</t>
+          <t>Anupam Das 0001</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -3743,22 +3743,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>CCS-Conflicting Scores, Confusing Signals: An Empirical Study of Vulnerability Scoring Systems.</t>
+          <t>CCS-Same Script, Different Behavior: Characterizing Divergent JavaScript Execution Across Different Device Platforms.</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Leidos (United States)</t>
+          <t>North Carolina State University</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Yaxing Yao</t>
+          <t>Ahmet Okutan</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -3766,22 +3766,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>CCS-Empowering Parents to Support Children's Online Security and Privacy: Findings from a Randomized Controlled Trial.</t>
+          <t>CCS-Conflicting Scores, Confusing Signals: An Empirical Study of Vulnerability Scoring Systems.</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Johns Hopkins University; Johns Hopkins Medicine</t>
+          <t>Leidos (United States)</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>R. Spencer Hallyburton</t>
+          <t>Yaxing Yao</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -3789,22 +3789,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>CCS-Security-Aware Sensor Fusion with MATE: the Multi-Agent Trust Estimator.</t>
+          <t>CCS-Empowering Parents to Support Children's Online Security and Privacy: Findings from a Randomized Controlled Trial.</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Duke University</t>
+          <t>Johns Hopkins University; Johns Hopkins Medicine</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Mu Zhang 0001</t>
+          <t>R. Spencer Hallyburton</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -3812,22 +3812,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>CCS-Needle in a Haystack: Automated and Scalable Vulnerability Hunting in the Windows ALPC Sea.</t>
+          <t>CCS-Security-Aware Sensor Fusion with MATE: the Multi-Agent Trust Estimator.</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>Duke University</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Lucien K. L. Ng</t>
+          <t>Mu Zhang 0001</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -3835,22 +3835,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>CCS-Lite-PoT: Practical Powers-of-Tau Setup Ceremony.</t>
+          <t>CCS-Needle in a Haystack: Automated and Scalable Vulnerability Hunting in the Windows ALPC Sea.</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology; Visa (United States)</t>
+          <t>University of Utah</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Mohsen Minaei</t>
+          <t>Lucien K. L. Ng</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -3862,18 +3862,18 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Visa (United States)</t>
+          <t>Georgia Institute of Technology; Visa (United States)</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Panagiotis Chatzigiannis</t>
+          <t>Mohsen Minaei</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -3885,7 +3885,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Adithya Bhat</t>
+          <t>Panagiotis Chatzigiannis</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -3908,7 +3908,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Jie Fu 0003</t>
+          <t>Adithya Bhat</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -3927,22 +3927,22 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>CCS-Safeguarding Graph Neural Networks against Topology Inference Attacks.</t>
+          <t>CCS-Lite-PoT: Practical Powers-of-Tau Setup Ceremony.</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Stevens Institute of Technology</t>
+          <t>Visa (United States)</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Yuan Hong 0001</t>
+          <t>Jie Fu 0003</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -3954,18 +3954,18 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>University of Connecticut</t>
+          <t>Stevens Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Wendy Hui Wang</t>
+          <t>Yuan Hong 0001</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -3977,18 +3977,18 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Stevens Institute of Technology</t>
+          <t>University of Connecticut</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Ruyi Ding</t>
+          <t>Wendy Hui Wang</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -3996,22 +3996,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>CCS-MoEcho: Exploiting Side-Channel Attacks to Compromise User Privacy in Mixture-of-Experts LLMs.</t>
+          <t>CCS-Safeguarding Graph Neural Networks against Topology Inference Attacks.</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>Stevens Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Tianhong Xu</t>
+          <t>Ruyi Ding</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -4023,7 +4023,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Xinyi Shen</t>
+          <t>Tianhong Xu</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -4046,18 +4046,18 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Yale University</t>
+          <t>Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Yunsi Fei</t>
+          <t>Xinyi Shen</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -4069,18 +4069,18 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>Yale University</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>David Oygenblik</t>
+          <t>Yunsi Fei</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -4088,22 +4088,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>CCS-VillainNet: Targeted Poisoning Attacks Against SuperNets Along the Accuracy-Latency Pareto Frontier.</t>
+          <t>CCS-MoEcho: Exploiting Side-Channel Attacks to Compromise User Privacy in Mixture-of-Experts LLMs.</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Debopam Sanyal</t>
+          <t>David Oygenblik</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Alexey Tumanov</t>
+          <t>Debopam Sanyal</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -4138,7 +4138,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Brendan Saltaformaggio</t>
+          <t>Alexey Tumanov</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Yiping Ma 0001</t>
+          <t>Brendan Saltaformaggio</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -4180,22 +4180,22 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>CCS-Armadillo: Robust Single-Server Secure Aggregation for Federated Learning with Input Validation.</t>
+          <t>CCS-VillainNet: Targeted Poisoning Attacks Against SuperNets Along the Accuracy-Latency Pareto Frontier.</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>California University of Pennsylvania; University of California, Berkeley</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Yue Guo</t>
+          <t>Yiping Ma 0001</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -4207,18 +4207,18 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co (United States)</t>
+          <t>California University of Pennsylvania; University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Harish Karthikeyan</t>
+          <t>Yue Guo</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -4230,7 +4230,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Antigoni Polychroniadou</t>
+          <t>Harish Karthikeyan</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -4253,18 +4253,18 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Morgan Stanley (United States)</t>
+          <t>JPMorgan Chase &amp; Co (United States)</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Sanketh Menda</t>
+          <t>Antigoni Polychroniadou</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -4272,22 +4272,22 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>CCS-The OCH Authenticated Encryption Scheme.</t>
+          <t>CCS-Armadillo: Robust Single-Server Secure Aggregation for Federated Learning with Input Validation.</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>Morgan Stanley (United States)</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Mihir Bellare</t>
+          <t>Sanketh Menda</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -4299,18 +4299,18 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>University of California San Diego</t>
+          <t>Cornell University</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Julia Len</t>
+          <t>Mihir Bellare</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -4322,18 +4322,18 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>University of North Carolina at Chapel Hill; University of North Carolina Health Care</t>
+          <t>University of California San Diego</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Thomas Ristenpart</t>
+          <t>Julia Len</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -4345,18 +4345,18 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>University of North Carolina at Chapel Hill; University of North Carolina Health Care</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Jack Doerner</t>
+          <t>Thomas Ristenpart</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -4364,22 +4364,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>CCS-From OT to OLE with Subquadratic Communication.</t>
+          <t>CCS-The OCH Authenticated Encryption Scheme.</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>Cornell University</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Carolina Ortega Pérez</t>
+          <t>Jack Doerner</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>CCS-Interoperable Symmetric Message Franking.</t>
+          <t>CCS-From OT to OLE with Subquadratic Communication.</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -4395,14 +4395,14 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>University of Virginia</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Thomas Ristenpart</t>
+          <t>Carolina Ortega Pérez</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -4414,7 +4414,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Julia Len</t>
+          <t>Thomas Ristenpart</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -4437,18 +4437,18 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>University of North Carolina at Chapel Hill; University of North Carolina Health Care</t>
+          <t>Cornell University</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Felix Günther 0001</t>
+          <t>Julia Len</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -4456,22 +4456,22 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>CCS-Breaking and Fixing Content-Defined Chunking.</t>
+          <t>CCS-Interoperable Symmetric Message Franking.</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>IBM Research - Zurich</t>
+          <t>University of North Carolina at Chapel Hill; University of North Carolina Health Care</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Syomantak Chaudhuri</t>
+          <t>Felix Günther 0001</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -4479,22 +4479,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>CCS-Managing Correlations in Data and Privacy Demand.</t>
+          <t>CCS-Breaking and Fixing Content-Defined Chunking.</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>University of California, Berkeley</t>
+          <t>IBM Research - Zurich</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Thomas A. Courtade</t>
+          <t>Chris Peikert</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -4502,22 +4502,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>CCS-Managing Correlations in Data and Privacy Demand.</t>
+          <t>CCS-High-Throughput Universally Composable Threshold FHE Decryption.</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>University of California, Berkeley</t>
+          <t>University of Michigan</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Yuntao Du 0002</t>
+          <t>Syomantak Chaudhuri</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>CCS-Systematic Assessment of Tabular Data Synthesis.</t>
+          <t>CCS-Managing Correlations in Data and Privacy Demand.</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -4533,14 +4533,14 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Mandy Lanyon</t>
+          <t>Thomas A. Courtade</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>CCS-'Is this a scam?': The Nature and Quality of Reddit Discussion about Scams.</t>
+          <t>CCS-Managing Correlations in Data and Privacy Demand.</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -4556,14 +4556,14 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Lorrie Faith Cranor</t>
+          <t>Yuntao Du 0002</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -4571,22 +4571,22 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>CCS-'Is this a scam?': The Nature and Quality of Reddit Discussion about Scams.</t>
+          <t>CCS-Systematic Assessment of Tabular Data Synthesis.</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Xi Tan 0002</t>
+          <t>Mandy Lanyon</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -4594,22 +4594,22 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>CCS-'We just did not have that on the embedded system': Insights and Challenges for Securing Microcontroller Systems from the Embedded CTF Competitions.</t>
+          <t>CCS-'Is this a scam?': The Nature and Quality of Reddit Discussion about Scams.</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>University of Colorado Colorado Springs</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Katherine Jesse</t>
+          <t>Lorrie Faith Cranor</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -4617,22 +4617,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>CCS-'We just did not have that on the embedded system': Insights and Challenges for Securing Microcontroller Systems from the Embedded CTF Competitions.</t>
+          <t>CCS-'Is this a scam?': The Nature and Quality of Reddit Discussion about Scams.</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Worcester Polytechnic Institute</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Robert J. Walls</t>
+          <t>Xi Tan 0002</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -4644,18 +4644,18 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Worcester Polytechnic Institute</t>
+          <t>University of Colorado Colorado Springs</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Ziming Zhao 0001</t>
+          <t>Katherine Jesse</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -4667,18 +4667,18 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>Worcester Polytechnic Institute</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Joshua Wiedemeier</t>
+          <t>Robert J. Walls</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -4686,22 +4686,22 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>CCS-Walking The Last Mile: Studying Decompiler Output Correction in Practice.</t>
+          <t>CCS-'We just did not have that on the embedded system': Insights and Challenges for Securing Microcontroller Systems from the Embedded CTF Competitions.</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>The University of Texas at Dallas</t>
+          <t>Worcester Polytechnic Institute</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Simon Klancher</t>
+          <t>Ziming Zhao 0001</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -4709,22 +4709,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>CCS-Walking The Last Mile: Studying Decompiler Output Correction in Practice.</t>
+          <t>CCS-'We just did not have that on the embedded system': Insights and Challenges for Securing Microcontroller Systems from the Embedded CTF Competitions.</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>The University of Texas at Dallas</t>
+          <t>Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Jaehyun Park</t>
+          <t>Joshua Wiedemeier</t>
         </is>
       </c>
       <c r="B188" t="n">
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Kangkook Jee</t>
+          <t>Simon Klancher</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -4759,7 +4759,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Yunze Zhao</t>
+          <t>Jaehyun Park</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -4778,22 +4778,22 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>CCS-A Qualitative Analysis of Fuzzer Usability and Challenges.</t>
+          <t>CCS-Walking The Last Mile: Studying Decompiler Output Correction in Practice.</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>University of Maryland, College Park</t>
+          <t>The University of Texas at Dallas</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Wentao Guo 0005</t>
+          <t>Kangkook Jee</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -4801,22 +4801,22 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>CCS-A Qualitative Analysis of Fuzzer Usability and Challenges.</t>
+          <t>CCS-Walking The Last Mile: Studying Decompiler Output Correction in Practice.</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>University of Maryland, College Park</t>
+          <t>The University of Texas at Dallas</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Harrison Goldstein</t>
+          <t>Yunze Zhao</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -4828,7 +4828,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Michelle L. Mazurek</t>
+          <t>Wentao Guo 0005</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Lorenzo Neil</t>
+          <t>Harrison Goldstein</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -4870,22 +4870,22 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>CCS-It Should Be Easy but... New Users' Experiences and Challenges with Secret Management Tools.</t>
+          <t>CCS-A Qualitative Analysis of Fuzzer Usability and Challenges.</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>North Carolina State University</t>
+          <t>University of Maryland, College Park</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Bradley Reaves</t>
+          <t>Michelle L. Mazurek</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -4893,22 +4893,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>CCS-It Should Be Easy but... New Users' Experiences and Challenges with Secret Management Tools.</t>
+          <t>CCS-A Qualitative Analysis of Fuzzer Usability and Challenges.</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>North Carolina State University</t>
+          <t>University of Maryland, College Park</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Daniel Moghimi</t>
+          <t>Lorenzo Neil</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -4916,22 +4916,22 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>CCS-ExfilState: Automated Discovery of Timer-Free Cache Side Channels on ARM CPUs.</t>
+          <t>CCS-It Should Be Easy but... New Users' Experiences and Challenges with Secret Management Tools.</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>North Carolina State University</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Flavien Solt</t>
+          <t>Bradley Reaves</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -4939,22 +4939,22 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>CCS-MileSan: Detecting Exploitable Microarchitectural Leakage via Differential Hardware-Software Taint Tracking.</t>
+          <t>CCS-It Should Be Easy but... New Users' Experiences and Challenges with Secret Management Tools.</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Berkeley College; University of California, Berkeley</t>
+          <t>North Carolina State University</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Rui Zhao</t>
+          <t>Daniel Moghimi</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -4962,22 +4962,22 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>CCS-Rethinking Tamper-Evident Logging: A High-Performance, Co-Designed Auditing System.</t>
+          <t>CCS-ExfilState: Automated Discovery of Timer-Free Cache Side Channels on ARM CPUs.</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Muhammad Shoaib</t>
+          <t>Flavien Solt</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -4985,7 +4985,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>CCS-Rethinking Tamper-Evident Logging: A High-Performance, Co-Designed Auditing System.</t>
+          <t>CCS-MileSan: Detecting Exploitable Microarchitectural Leakage via Differential Hardware-Software Taint Tracking.</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -4993,14 +4993,14 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>Berkeley College; University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Wajih Ul Hassan</t>
+          <t>Rui Zhao</t>
         </is>
       </c>
       <c r="B200" t="n">
@@ -5012,7 +5012,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Moritz Schloegel</t>
+          <t>Muhammad Shoaib</t>
         </is>
       </c>
       <c r="B201" t="n">
@@ -5031,22 +5031,22 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>CCS-Empirical Security Analysis of Software-based Fault Isolation through Controlled Fault Injection.</t>
+          <t>CCS-Rethinking Tamper-Evident Logging: A High-Performance, Co-Designed Auditing System.</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>University of Virginia</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Shixuan Zhao 0002</t>
+          <t>Wajih Ul Hassan</t>
         </is>
       </c>
       <c r="B202" t="n">
@@ -5054,22 +5054,22 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>CCS-GPU Travelling: Efficient Confidential Collaborative Training with TEE-Enabled GPUs.</t>
+          <t>CCS-Rethinking Tamper-Evident Logging: A High-Performance, Co-Designed Auditing System.</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>The Ohio State University</t>
+          <t>University of Virginia</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Zhongshu Gu</t>
+          <t>Moritz Schloegel</t>
         </is>
       </c>
       <c r="B203" t="n">
@@ -5077,22 +5077,22 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>CCS-GPU Travelling: Efficient Confidential Collaborative Training with TEE-Enabled GPUs.</t>
+          <t>CCS-Empirical Security Analysis of Software-based Fault Isolation through Controlled Fault Injection.</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>IBM (United States)</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Salman Ahmed 0001</t>
+          <t>Shixuan Zhao 0002</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -5104,18 +5104,18 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>IBM (United States)</t>
+          <t>The Ohio State University</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Enriquillo Valdez</t>
+          <t>Zhongshu Gu</t>
         </is>
       </c>
       <c r="B205" t="n">
@@ -5127,7 +5127,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Hani Jamjoom</t>
+          <t>Salman Ahmed 0001</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -5150,7 +5150,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Zhiqiang Lin 0001</t>
+          <t>Enriquillo Valdez</t>
         </is>
       </c>
       <c r="B207" t="n">
@@ -5173,18 +5173,18 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>The Ohio State University</t>
+          <t>IBM (United States)</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Tahina Ramananandro</t>
+          <t>Hani Jamjoom</t>
         </is>
       </c>
       <c r="B208" t="n">
@@ -5192,22 +5192,22 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>CCS-Secure Parsing and Serializing with Separation Logic Applied to CBOR, CDDL, and COSE.</t>
+          <t>CCS-GPU Travelling: Efficient Confidential Collaborative Training with TEE-Enabled GPUs.</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Microsoft (United States)</t>
+          <t>IBM (United States)</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Gabriel Ebner</t>
+          <t>Zhiqiang Lin 0001</t>
         </is>
       </c>
       <c r="B209" t="n">
@@ -5215,22 +5215,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>CCS-Secure Parsing and Serializing with Separation Logic Applied to CBOR, CDDL, and COSE.</t>
+          <t>CCS-GPU Travelling: Efficient Confidential Collaborative Training with TEE-Enabled GPUs.</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Microsoft (United States)</t>
+          <t>The Ohio State University</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Guido Martínez</t>
+          <t>Tahina Ramananandro</t>
         </is>
       </c>
       <c r="B210" t="n">
@@ -5242,7 +5242,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Nikhil Swamy</t>
+          <t>Gabriel Ebner</t>
         </is>
       </c>
       <c r="B211" t="n">
@@ -5265,7 +5265,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Sizhe Chen</t>
+          <t>Guido Martínez</t>
         </is>
       </c>
       <c r="B212" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>CCS-SecAlign: Defending Against Prompt Injection with Preference Optimization.</t>
+          <t>CCS-Secure Parsing and Serializing with Separation Logic Applied to CBOR, CDDL, and COSE.</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Berkeley College; University of California, Berkeley</t>
+          <t>Microsoft (United States)</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Ronik Bhaskar</t>
+          <t>Nikhil Swamy</t>
         </is>
       </c>
       <c r="B213" t="n">
@@ -5307,22 +5307,22 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>CCS-On the Feasibility of Poisoning Text-to-Image AI Models via Adversarial Mislabeling.</t>
+          <t>CCS-Secure Parsing and Serializing with Separation Logic Applied to CBOR, CDDL, and COSE.</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>University of Illinois Chicago; University of Chicago</t>
+          <t>Microsoft (United States)</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Anna Yoo Jeong Ha</t>
+          <t>Sizhe Chen</t>
         </is>
       </c>
       <c r="B214" t="n">
@@ -5330,22 +5330,22 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>CCS-On the Feasibility of Poisoning Text-to-Image AI Models via Adversarial Mislabeling.</t>
+          <t>CCS-SecAlign: Defending Against Prompt Injection with Preference Optimization.</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>University of Illinois Chicago; University of Chicago</t>
+          <t>Berkeley College; University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Shawn Shan</t>
+          <t>Ronik Bhaskar</t>
         </is>
       </c>
       <c r="B215" t="n">
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Haitao Zheng 0001</t>
+          <t>Anna Yoo Jeong Ha</t>
         </is>
       </c>
       <c r="B216" t="n">
@@ -5380,7 +5380,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Ben Y. Zhao</t>
+          <t>Shawn Shan</t>
         </is>
       </c>
       <c r="B217" t="n">
@@ -5403,7 +5403,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Zeyu Liu 0004</t>
+          <t>Haitao Zheng 0001</t>
         </is>
       </c>
       <c r="B218" t="n">
@@ -5422,22 +5422,22 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>CCS-IND-CPA-D of Relaxed Functional Bootstrapping: A New Attack, A General Fix, and A Stronger Model.</t>
+          <t>CCS-On the Feasibility of Poisoning Text-to-Image AI Models via Adversarial Mislabeling.</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Yale University</t>
+          <t>University of Illinois Chicago; University of Chicago</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Yunhao Wang 0002</t>
+          <t>Ben Y. Zhao</t>
         </is>
       </c>
       <c r="B219" t="n">
@@ -5445,22 +5445,22 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>CCS-IND-CPA-D of Relaxed Functional Bootstrapping: A New Attack, A General Fix, and A Stronger Model.</t>
+          <t>CCS-On the Feasibility of Poisoning Text-to-Image AI Models via Adversarial Mislabeling.</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Yale University</t>
+          <t>University of Illinois Chicago; University of Chicago</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Ben Fisch</t>
+          <t>Zeyu Liu 0004</t>
         </is>
       </c>
       <c r="B220" t="n">
@@ -5472,7 +5472,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Chris Tsoukaladelis</t>
+          <t>Yunhao Wang 0002</t>
         </is>
       </c>
       <c r="B221" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>CCS-The Power to Never Be Wrong: Evasions and Anachronistic Attacks Against Web Archives.</t>
+          <t>CCS-IND-CPA-D of Relaxed Functional Bootstrapping: A New Attack, A General Fix, and A Stronger Model.</t>
         </is>
       </c>
       <c r="D221" t="n">
@@ -5499,14 +5499,14 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Stony Brook University</t>
+          <t>Yale University</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Nick Nikiforakis</t>
+          <t>Ben Fisch</t>
         </is>
       </c>
       <c r="B222" t="n">
@@ -5514,22 +5514,22 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>CCS-The Power to Never Be Wrong: Evasions and Anachronistic Attacks Against Web Archives.</t>
+          <t>CCS-IND-CPA-D of Relaxed Functional Bootstrapping: A New Attack, A General Fix, and A Stronger Model.</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Stony Brook University</t>
+          <t>Yale University</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Johnny So</t>
+          <t>Chris Tsoukaladelis</t>
         </is>
       </c>
       <c r="B223" t="n">
@@ -5537,11 +5537,11 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>CCS-What Gets Measured Gets Managed: Mitigating Supply Chain Attacks with a Link Integrity Management System.</t>
+          <t>CCS-The Power to Never Be Wrong: Evasions and Anachronistic Attacks Against Web Archives.</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Michael Ferdman</t>
+          <t>Nick Nikiforakis</t>
         </is>
       </c>
       <c r="B224" t="n">
@@ -5560,11 +5560,11 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>CCS-What Gets Measured Gets Managed: Mitigating Supply Chain Attacks with a Link Integrity Management System.</t>
+          <t>CCS-The Power to Never Be Wrong: Evasions and Anachronistic Attacks Against Web Archives.</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Nick Nikiforakis</t>
+          <t>Johnny So</t>
         </is>
       </c>
       <c r="B225" t="n">
@@ -5587,7 +5587,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Bo Li 0026</t>
+          <t>Michael Ferdman</t>
         </is>
       </c>
       <c r="B226" t="n">
@@ -5606,22 +5606,22 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>CCS-What's Pulling the Strings? Evaluating Integrity and Attribution in AI Training and Inference through Concept Shift.</t>
+          <t>CCS-What Gets Measured Gets Managed: Mitigating Supply Chain Attacks with a Link Integrity Management System.</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>Stony Brook University</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Caleb Manicke</t>
+          <t>Nick Nikiforakis</t>
         </is>
       </c>
       <c r="B227" t="n">
@@ -5629,22 +5629,22 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>CCS-Busting the Paper Ballot: Voting Meets Adversarial Machine Learning.</t>
+          <t>CCS-What Gets Measured Gets Managed: Mitigating Supply Chain Attacks with a Link Integrity Management System.</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>University of Connecticut</t>
+          <t>Stony Brook University</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Ethan Rathbun</t>
+          <t>Bo Li 0026</t>
         </is>
       </c>
       <c r="B228" t="n">
@@ -5652,22 +5652,22 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>CCS-Busting the Paper Ballot: Voting Meets Adversarial Machine Learning.</t>
+          <t>CCS-What's Pulling the Strings? Evaluating Integrity and Attribution in AI Training and Inference through Concept Shift.</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Sohaib Ahmad</t>
+          <t>Caleb Manicke</t>
         </is>
       </c>
       <c r="B229" t="n">
@@ -5679,7 +5679,7 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Nicholas Stamatakis</t>
+          <t>Ethan Rathbun</t>
         </is>
       </c>
       <c r="B230" t="n">
@@ -5702,18 +5702,18 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Stony Brook University</t>
+          <t>Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Laurent Michel</t>
+          <t>Sohaib Ahmad</t>
         </is>
       </c>
       <c r="B231" t="n">
@@ -5725,7 +5725,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Benjamin Fuller 0001</t>
+          <t>Nicholas Stamatakis</t>
         </is>
       </c>
       <c r="B232" t="n">
@@ -5748,18 +5748,18 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>University of Connecticut</t>
+          <t>Stony Brook University</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Lu Xian</t>
+          <t>Laurent Michel</t>
         </is>
       </c>
       <c r="B233" t="n">
@@ -5767,22 +5767,22 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>CCS-Layered, Overlapping, and Inconsistent: A Large-Scale Analysis of the Multiple Privacy Policies and Controls of U.S. Banks.</t>
+          <t>CCS-Busting the Paper Ballot: Voting Meets Adversarial Machine Learning.</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>University of Michigan</t>
+          <t>University of Connecticut</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Lauren Lee</t>
+          <t>Benjamin Fuller 0001</t>
         </is>
       </c>
       <c r="B234" t="n">
@@ -5790,22 +5790,22 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>CCS-Layered, Overlapping, and Inconsistent: A Large-Scale Analysis of the Multiple Privacy Policies and Controls of U.S. Banks.</t>
+          <t>CCS-Busting the Paper Ballot: Voting Meets Adversarial Machine Learning.</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>University of Michigan</t>
+          <t>University of Connecticut</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Meera Kumar</t>
+          <t>Lu Xian</t>
         </is>
       </c>
       <c r="B235" t="n">
@@ -5817,7 +5817,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Yichen Zhang</t>
+          <t>Lauren Lee</t>
         </is>
       </c>
       <c r="B236" t="n">
@@ -5840,18 +5840,18 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>University of Wisconsin–Madison</t>
+          <t>University of Michigan</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Florian Schaub</t>
+          <t>Meera Kumar</t>
         </is>
       </c>
       <c r="B237" t="n">
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Nick Nikiforakis</t>
+          <t>Yichen Zhang</t>
         </is>
       </c>
       <c r="B238" t="n">
@@ -5882,22 +5882,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>CCS-A Decade-long Landscape of Advanced Persistent Threats: Longitudinal Analysis and Global Trends.</t>
+          <t>CCS-Layered, Overlapping, and Inconsistent: A Large-Scale Analysis of the Multiple Privacy Policies and Controls of U.S. Banks.</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Stony Brook University</t>
+          <t>University of Wisconsin–Madison</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Emiliano De Cristofaro</t>
+          <t>Florian Schaub</t>
         </is>
       </c>
       <c r="B239" t="n">
@@ -5905,22 +5905,22 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>CCS-The Importance of Being Discrete: Measuring the Impact of Discretization in End-to-End Differentially Private Synthetic Data.</t>
+          <t>CCS-Layered, Overlapping, and Inconsistent: A Large-Scale Analysis of the Multiple Privacy Policies and Controls of U.S. Banks.</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>University of California, Riverside</t>
+          <t>University of Michigan</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Yi Zhu 0012</t>
+          <t>Nick Nikiforakis</t>
         </is>
       </c>
       <c r="B240" t="n">
@@ -5928,22 +5928,22 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>CCS-Asymmetry Vulnerability and Physical Attacks on Online Map Construction for Autonomous Driving.</t>
+          <t>CCS-A Decade-long Landscape of Advanced Persistent Threats: Longitudinal Analysis and Global Trends.</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Wayne State University</t>
+          <t>Stony Brook University</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Alan Wang 0004</t>
+          <t>Emiliano De Cristofaro</t>
         </is>
       </c>
       <c r="B241" t="n">
@@ -5951,22 +5951,22 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>CCS-Pixnapping: Bringing Pixel Stealing out of the Stone Age.</t>
+          <t>CCS-The Importance of Being Discrete: Measuring the Impact of Discretization in End-to-End Differentially Private Synthetic Data.</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>University of California, Berkeley</t>
+          <t>University of California, Riverside</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Pranav Gopalkrishnan</t>
+          <t>Yi Zhu 0012</t>
         </is>
       </c>
       <c r="B242" t="n">
@@ -5974,22 +5974,22 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>CCS-Pixnapping: Bringing Pixel Stealing out of the Stone Age.</t>
+          <t>CCS-Asymmetry Vulnerability and Physical Attacks on Online Map Construction for Autonomous Driving.</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>University of Washington</t>
+          <t>Wayne State University</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Yingchen Wang</t>
+          <t>Alan Wang 0004</t>
         </is>
       </c>
       <c r="B243" t="n">
@@ -6001,7 +6001,7 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Christopher W. Fletcher</t>
+          <t>Pranav Gopalkrishnan</t>
         </is>
       </c>
       <c r="B244" t="n">
@@ -6024,18 +6024,18 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>University of California, Berkeley</t>
+          <t>University of Washington</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Hovav Shacham</t>
+          <t>Yingchen Wang</t>
         </is>
       </c>
       <c r="B245" t="n">
@@ -6047,18 +6047,18 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>University of California San Diego</t>
+          <t>University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>David Kohlbrenner</t>
+          <t>Christopher W. Fletcher</t>
         </is>
       </c>
       <c r="B246" t="n">
@@ -6070,18 +6070,18 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>University of Washington</t>
+          <t>University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Riccardo Paccagnella</t>
+          <t>Hovav Shacham</t>
         </is>
       </c>
       <c r="B247" t="n">
@@ -6093,18 +6093,18 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>University of California San Diego</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Long Huang</t>
+          <t>David Kohlbrenner</t>
         </is>
       </c>
       <c r="B248" t="n">
@@ -6112,22 +6112,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>CCS-HW-Spy: Handwriting Inference by Tracing Pen-Tail Movements.</t>
+          <t>CCS-Pixnapping: Bringing Pixel Stealing out of the Stone Age.</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>University of Michigan</t>
+          <t>University of Washington</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Kang G. Shin</t>
+          <t>Riccardo Paccagnella</t>
         </is>
       </c>
       <c r="B249" t="n">
@@ -6135,22 +6135,22 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>CCS-HW-Spy: Handwriting Inference by Tracing Pen-Tail Movements.</t>
+          <t>CCS-Pixnapping: Bringing Pixel Stealing out of the Stone Age.</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>University of Michigan</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Hadleigh Schwartz</t>
+          <t>Long Huang</t>
         </is>
       </c>
       <c r="B250" t="n">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>CCS-Combating Falsification of Speech Videos with Live Optical Signatures.</t>
+          <t>CCS-HW-Spy: Handwriting Inference by Tracing Pen-Tail Movements.</t>
         </is>
       </c>
       <c r="D250" t="n">
@@ -6166,14 +6166,14 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Columbia University</t>
+          <t>University of Michigan</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Xiaofeng Yan</t>
+          <t>Kang G. Shin</t>
         </is>
       </c>
       <c r="B251" t="n">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>CCS-Combating Falsification of Speech Videos with Live Optical Signatures.</t>
+          <t>CCS-HW-Spy: Handwriting Inference by Tracing Pen-Tail Movements.</t>
         </is>
       </c>
       <c r="D251" t="n">
@@ -6189,14 +6189,14 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Columbia University</t>
+          <t>University of Michigan</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Charles J. Carver</t>
+          <t>Hadleigh Schwartz</t>
         </is>
       </c>
       <c r="B252" t="n">
@@ -6208,18 +6208,18 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Massachusetts Institute of Technology</t>
+          <t>Columbia University</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Xia Zhou</t>
+          <t>Xiaofeng Yan</t>
         </is>
       </c>
       <c r="B253" t="n">
@@ -6231,7 +6231,7 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
@@ -6242,7 +6242,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Jinwen Wang</t>
+          <t>Charles J. Carver</t>
         </is>
       </c>
       <c r="B254" t="n">
@@ -6250,22 +6250,22 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>CCS-ConTest: Taming the Cyber-physical Input Space in Fuzz Testing with Control Theory.</t>
+          <t>CCS-Combating Falsification of Speech Videos with Live Optical Signatures.</t>
         </is>
       </c>
       <c r="D254" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>The University of Texas at Dallas</t>
+          <t>Massachusetts Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Neophytos Christou</t>
+          <t>Xia Zhou</t>
         </is>
       </c>
       <c r="B255" t="n">
@@ -6273,22 +6273,22 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>CCS-PickleBall: Secure Deserialization of Pickle-based Machine Learning Models.</t>
+          <t>CCS-Combating Falsification of Speech Videos with Live Optical Signatures.</t>
         </is>
       </c>
       <c r="D255" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Brown University</t>
+          <t>Columbia University</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Wenxin Jiang 0001</t>
+          <t>Jinwen Wang</t>
         </is>
       </c>
       <c r="B256" t="n">
@@ -6296,22 +6296,22 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>CCS-PickleBall: Secure Deserialization of Pickle-based Machine Learning Models.</t>
+          <t>CCS-ConTest: Taming the Cyber-physical Input Space in Fuzz Testing with Control Theory.</t>
         </is>
       </c>
       <c r="D256" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>The University of Texas at Dallas</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Penghui Li 0001</t>
+          <t>Neophytos Christou</t>
         </is>
       </c>
       <c r="B257" t="n">
@@ -6323,18 +6323,18 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Columbia University</t>
+          <t>Brown University</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Laurent Simon</t>
+          <t>Wenxin Jiang 0001</t>
         </is>
       </c>
       <c r="B258" t="n">
@@ -6346,18 +6346,18 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Vasileios P. Kemerlis</t>
+          <t>Penghui Li 0001</t>
         </is>
       </c>
       <c r="B259" t="n">
@@ -6369,18 +6369,18 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Brown University</t>
+          <t>Columbia University</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>James C. Davis 0001</t>
+          <t>Laurent Simon</t>
         </is>
       </c>
       <c r="B260" t="n">
@@ -6392,18 +6392,18 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Junfeng Yang</t>
+          <t>Vasileios P. Kemerlis</t>
         </is>
       </c>
       <c r="B261" t="n">
@@ -6415,18 +6415,18 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Columbia University</t>
+          <t>Brown University</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Kangjie Lu</t>
+          <t>James C. Davis 0001</t>
         </is>
       </c>
       <c r="B262" t="n">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>CCS-Dangers Behind Access Control: Understanding and Exploiting Implicit Permissions in Kubernetes.</t>
+          <t>CCS-PickleBall: Secure Deserialization of Pickle-based Machine Learning Models.</t>
         </is>
       </c>
       <c r="D262" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>University of Minnesota</t>
+          <t>Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Tim Roughgarden</t>
+          <t>Junfeng Yang</t>
         </is>
       </c>
       <c r="B263" t="n">
@@ -6457,11 +6457,11 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>CCS-Accountable Liveness.</t>
+          <t>CCS-PickleBall: Secure Deserialization of Pickle-based Machine Learning Models.</t>
         </is>
       </c>
       <c r="D263" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Shu-Jie Cao</t>
+          <t>Kangjie Lu</t>
         </is>
       </c>
       <c r="B264" t="n">
@@ -6480,22 +6480,22 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>CCS-How to Beat Nakamoto in the Race.</t>
+          <t>CCS-Dangers Behind Access Control: Understanding and Exploiting Implicit Permissions in Kubernetes.</t>
         </is>
       </c>
       <c r="D264" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Northwestern University</t>
+          <t>University of Minnesota</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Dongning Guo</t>
+          <t>Tim Roughgarden</t>
         </is>
       </c>
       <c r="B265" t="n">
@@ -6503,22 +6503,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>CCS-How to Beat Nakamoto in the Race.</t>
+          <t>CCS-Accountable Liveness.</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Northwestern University</t>
+          <t>Columbia University</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Xinwen Fu</t>
+          <t>Shu-Jie Cao</t>
         </is>
       </c>
       <c r="B266" t="n">
@@ -6526,22 +6526,22 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>CCS-Time Tells All: Deanonymization of Blockchain RPC Users with Zero Transaction Fee.</t>
+          <t>CCS-How to Beat Nakamoto in the Race.</t>
         </is>
       </c>
       <c r="D266" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>University of Massachusetts Lowell</t>
+          <t>Northwestern University</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Mahimna Kelkar</t>
+          <t>Dongning Guo</t>
         </is>
       </c>
       <c r="B267" t="n">
@@ -6549,22 +6549,22 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>CCS-Breaking Omertà: On Threshold Cryptography, Smart Collusion, and Whistleblowing.</t>
+          <t>CCS-How to Beat Nakamoto in the Race.</t>
         </is>
       </c>
       <c r="D267" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>Northwestern University</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Aadityan Ganesh</t>
+          <t>Xinwen Fu</t>
         </is>
       </c>
       <c r="B268" t="n">
@@ -6572,22 +6572,22 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>CCS-Breaking Omertà: On Threshold Cryptography, Smart Collusion, and Whistleblowing.</t>
+          <t>CCS-Time Tells All: Deanonymization of Blockchain RPC Users with Zero Transaction Fee.</t>
         </is>
       </c>
       <c r="D268" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Princeton University</t>
+          <t>University of Massachusetts Lowell</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Aditi Partap</t>
+          <t>Mahimna Kelkar</t>
         </is>
       </c>
       <c r="B269" t="n">
@@ -6599,18 +6599,18 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>Cornell University</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Joseph Bonneau</t>
+          <t>Aadityan Ganesh</t>
         </is>
       </c>
       <c r="B270" t="n">
@@ -6622,18 +6622,18 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>New York University</t>
+          <t>Princeton University</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>S. Matthew Weinberg</t>
+          <t>Aditi Partap</t>
         </is>
       </c>
       <c r="B271" t="n">
@@ -6645,18 +6645,18 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Princeton University</t>
+          <t>Stanford University</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Tianfang Zhang</t>
+          <t>Joseph Bonneau</t>
         </is>
       </c>
       <c r="B272" t="n">
@@ -6664,22 +6664,22 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>CCS-Harnessing Vital Sign Vibration Harmonics for Effortless and Inbuilt XR User Authentication.</t>
+          <t>CCS-Breaking Omertà: On Threshold Cryptography, Smart Collusion, and Whistleblowing.</t>
         </is>
       </c>
       <c r="D272" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Rutgers, The State University of New Jersey</t>
+          <t>New York University</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Md Mojibur Rahman Redoy Akanda</t>
+          <t>S. Matthew Weinberg</t>
         </is>
       </c>
       <c r="B273" t="n">
@@ -6687,22 +6687,22 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>CCS-Harnessing Vital Sign Vibration Harmonics for Effortless and Inbuilt XR User Authentication.</t>
+          <t>CCS-Breaking Omertà: On Threshold Cryptography, Smart Collusion, and Whistleblowing.</t>
         </is>
       </c>
       <c r="D273" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>Princeton University</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Ahmed Tanvir Mahdad</t>
+          <t>Tianfang Zhang</t>
         </is>
       </c>
       <c r="B274" t="n">
@@ -6714,18 +6714,18 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>Rutgers, The State University of New Jersey</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Nitesh Saxena</t>
+          <t>Md Mojibur Rahman Redoy Akanda</t>
         </is>
       </c>
       <c r="B275" t="n">
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E275" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Yingying Chen 0001</t>
+          <t>Ahmed Tanvir Mahdad</t>
         </is>
       </c>
       <c r="B276" t="n">
@@ -6760,18 +6760,18 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Rutgers, The State University of New Jersey</t>
+          <t>Texas A&amp;M University</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Andrew Gan</t>
+          <t>Nitesh Saxena</t>
         </is>
       </c>
       <c r="B277" t="n">
@@ -6779,22 +6779,22 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>CCS-Sentry: Authenticating Machine Learning Artifacts on the Fly.</t>
+          <t>CCS-Harnessing Vital Sign Vibration Harmonics for Effortless and Inbuilt XR User Authentication.</t>
         </is>
       </c>
       <c r="D277" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>Texas A&amp;M University</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Zahra Ghodsi</t>
+          <t>Yingying Chen 0001</t>
         </is>
       </c>
       <c r="B278" t="n">
@@ -6802,22 +6802,22 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>CCS-Sentry: Authenticating Machine Learning Artifacts on the Fly.</t>
+          <t>CCS-Harnessing Vital Sign Vibration Harmonics for Effortless and Inbuilt XR User Authentication.</t>
         </is>
       </c>
       <c r="D278" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>Rutgers, The State University of New Jersey</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Kun Sun 0001</t>
+          <t>Andrew Gan</t>
         </is>
       </c>
       <c r="B279" t="n">
@@ -6825,22 +6825,22 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>CCS-Training Robust Classifiers for Classifying Encrypted Traffic under Dynamic Network Conditions.</t>
+          <t>CCS-Sentry: Authenticating Machine Learning Artifacts on the Fly.</t>
         </is>
       </c>
       <c r="D279" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>George Mason University</t>
+          <t>Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Benjamin Fuller 0001</t>
+          <t>Zahra Ghodsi</t>
         </is>
       </c>
       <c r="B280" t="n">
@@ -6848,22 +6848,22 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>CCS-Fuzzy Extractors are Practical: Cryptographic Strength Key Derivation from the Iris.</t>
+          <t>CCS-Sentry: Authenticating Machine Learning Artifacts on the Fly.</t>
         </is>
       </c>
       <c r="D280" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>University of Connecticut</t>
+          <t>Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Sohaib Ahmad</t>
+          <t>Kun Sun 0001</t>
         </is>
       </c>
       <c r="B281" t="n">
@@ -6871,22 +6871,22 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>CCS-Fuzzy Extractors are Practical: Cryptographic Strength Key Derivation from the Iris.</t>
+          <t>CCS-Training Robust Classifiers for Classifying Encrypted Traffic under Dynamic Network Conditions.</t>
         </is>
       </c>
       <c r="D281" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>University of Connecticut</t>
+          <t>George Mason University</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Caleb Manicke</t>
+          <t>Benjamin Fuller 0001</t>
         </is>
       </c>
       <c r="B282" t="n">
@@ -6898,7 +6898,7 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E282" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Alexander Russell</t>
+          <t>Sohaib Ahmad</t>
         </is>
       </c>
       <c r="B283" t="n">
@@ -6921,7 +6921,7 @@
         </is>
       </c>
       <c r="D283" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E283" t="inlineStr">
         <is>
@@ -6932,7 +6932,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Alexandra Boldyreva</t>
+          <t>Caleb Manicke</t>
         </is>
       </c>
       <c r="B284" t="n">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>CCS-May the Force</t>
+          <t>CCS-Fuzzy Extractors are Practical: Cryptographic Strength Key Derivation from the Iris.</t>
         </is>
       </c>
       <c r="D284" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>University of Connecticut</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Deep Inder Mohan</t>
+          <t>Alexander Russell</t>
         </is>
       </c>
       <c r="B285" t="n">
@@ -6963,22 +6963,22 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>CCS-May the Force</t>
+          <t>CCS-Fuzzy Extractors are Practical: Cryptographic Strength Key Derivation from the Iris.</t>
         </is>
       </c>
       <c r="D285" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>University of Connecticut</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Yunqing Sun</t>
+          <t>Alexandra Boldyreva</t>
         </is>
       </c>
       <c r="B286" t="n">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>CCS-Committed Vector Oblivious Linear Evaluation and Its Applications.</t>
+          <t>CCS-May the Force</t>
         </is>
       </c>
       <c r="D286" t="n">
@@ -6994,14 +6994,14 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Northwestern University</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Hanlin Liu</t>
+          <t>Deep Inder Mohan</t>
         </is>
       </c>
       <c r="B287" t="n">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>CCS-Committed Vector Oblivious Linear Evaluation and Its Applications.</t>
+          <t>CCS-May the Force</t>
         </is>
       </c>
       <c r="D287" t="n">
@@ -7017,14 +7017,14 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Northwestern University</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Xiao Wang 0012</t>
+          <t>Yunqing Sun</t>
         </is>
       </c>
       <c r="B288" t="n">
@@ -7036,7 +7036,7 @@
         </is>
       </c>
       <c r="D288" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Chenkai Weng</t>
+          <t>Hanlin Liu</t>
         </is>
       </c>
       <c r="B289" t="n">
@@ -7059,18 +7059,18 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Northwestern University</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Zachary Ratliff</t>
+          <t>Xiao Wang 0012</t>
         </is>
       </c>
       <c r="B290" t="n">
@@ -7078,22 +7078,22 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>CCS-Timing Attacks on Differential Privacy are Practical.</t>
+          <t>CCS-Committed Vector Oblivious Linear Evaluation and Its Applications.</t>
         </is>
       </c>
       <c r="D290" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Harvard University Press</t>
+          <t>Northwestern University</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>James Mickens</t>
+          <t>Chenkai Weng</t>
         </is>
       </c>
       <c r="B291" t="n">
@@ -7101,22 +7101,22 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>CCS-Timing Attacks on Differential Privacy are Practical.</t>
+          <t>CCS-Committed Vector Oblivious Linear Evaluation and Its Applications.</t>
         </is>
       </c>
       <c r="D291" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Harvard University Press</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Pouneh Nikkhah Bahrami</t>
+          <t>Zachary Ratliff</t>
         </is>
       </c>
       <c r="B292" t="n">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>CCS-Byte by Byte: Unmasking Browser Fingerprinting at the Function Level using V8 Bytecode Transformers.</t>
+          <t>CCS-Timing Attacks on Differential Privacy are Practical.</t>
         </is>
       </c>
       <c r="D292" t="n">
@@ -7132,14 +7132,14 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>University of California, Davis</t>
+          <t>Harvard University Press</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Dylan Cutler</t>
+          <t>James Mickens</t>
         </is>
       </c>
       <c r="B293" t="n">
@@ -7147,22 +7147,22 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>CCS-Byte by Byte: Unmasking Browser Fingerprinting at the Function Level using V8 Bytecode Transformers.</t>
+          <t>CCS-Timing Attacks on Differential Privacy are Practical.</t>
         </is>
       </c>
       <c r="D293" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>Harvard University Press</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Igor Bilogrevic</t>
+          <t>Pouneh Nikkhah Bahrami</t>
         </is>
       </c>
       <c r="B294" t="n">
@@ -7174,18 +7174,18 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Google (Switzerland)</t>
+          <t>University of California, Davis</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Xiaoqian Jiang</t>
+          <t>Dylan Cutler</t>
         </is>
       </c>
       <c r="B295" t="n">
@@ -7193,22 +7193,22 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>CCS-THOR: Secure Transformer Inference with Homomorphic Encryption.</t>
+          <t>CCS-Byte by Byte: Unmasking Browser Fingerprinting at the Function Level using V8 Bytecode Transformers.</t>
         </is>
       </c>
       <c r="D295" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>The University of Texas Health Science Center at Houston</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Aniket Kate</t>
+          <t>Igor Bilogrevic</t>
         </is>
       </c>
       <c r="B296" t="n">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>CCS-Optimistic, Signature-Free Reliable Broadcast and Its Applications.</t>
+          <t>CCS-Byte by Byte: Unmasking Browser Fingerprinting at the Function Level using V8 Bytecode Transformers.</t>
         </is>
       </c>
       <c r="D296" t="n">
@@ -7224,14 +7224,14 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>Google (Switzerland)</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Giuliano Losa</t>
+          <t>Xiaoqian Jiang</t>
         </is>
       </c>
       <c r="B297" t="n">
@@ -7239,22 +7239,22 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>CCS-Optimistic, Signature-Free Reliable Broadcast and Its Applications.</t>
+          <t>CCS-THOR: Secure Transformer Inference with Homomorphic Encryption.</t>
         </is>
       </c>
       <c r="D297" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Stellar Solutions (United States)</t>
+          <t>The University of Texas Health Science Center at Houston</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Kartik Nayak</t>
+          <t>Aniket Kate</t>
         </is>
       </c>
       <c r="B298" t="n">
@@ -7266,18 +7266,18 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Duke University</t>
+          <t>Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Yi Zhu 0012</t>
+          <t>Giuliano Losa</t>
         </is>
       </c>
       <c r="B299" t="n">
@@ -7285,22 +7285,22 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>CCS-Towards Real-Time Defense against Object-Based LiDAR Attacks in Autonomous Driving.</t>
+          <t>CCS-Optimistic, Signature-Free Reliable Broadcast and Its Applications.</t>
         </is>
       </c>
       <c r="D299" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Wayne State University</t>
+          <t>Stellar Solutions (United States)</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Haining Wang 0001</t>
+          <t>Kartik Nayak</t>
         </is>
       </c>
       <c r="B300" t="n">
@@ -7308,22 +7308,22 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>CCS-Dynamic Vulnerability Patching for Heterogeneous Embedded Systems Using Stack Frame Reconstruction.</t>
+          <t>CCS-Optimistic, Signature-Free Reliable Broadcast and Its Applications.</t>
         </is>
       </c>
       <c r="D300" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>Duke University</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Elisa Bertino</t>
+          <t>Yi Zhu 0012</t>
         </is>
       </c>
       <c r="B301" t="n">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>CCS-Training with Only 1.0 ‰ Samples: Malicious Traffic Detection via Cross-Modality Feature Fusion.</t>
+          <t>CCS-Towards Real-Time Defense against Object-Based LiDAR Attacks in Autonomous Driving.</t>
         </is>
       </c>
       <c r="D301" t="n">
@@ -7339,14 +7339,14 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>Wayne State University</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Diwen Xue</t>
+          <t>Haining Wang 0001</t>
         </is>
       </c>
       <c r="B302" t="n">
@@ -7354,22 +7354,22 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>CCS-Fingerprinting Deep Packet Inspection Devices by their Ambiguities.</t>
+          <t>CCS-Dynamic Vulnerability Patching for Heterogeneous Embedded Systems Using Stack Frame Reconstruction.</t>
         </is>
       </c>
       <c r="D302" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>University of Michigan</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Armin Huremagic</t>
+          <t>Elisa Bertino</t>
         </is>
       </c>
       <c r="B303" t="n">
@@ -7377,22 +7377,22 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>CCS-Fingerprinting Deep Packet Inspection Devices by their Ambiguities.</t>
+          <t>CCS-Training with Only 1.0 ‰ Samples: Malicious Traffic Detection via Cross-Modality Feature Fusion.</t>
         </is>
       </c>
       <c r="D303" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>University of Michigan</t>
+          <t>Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Wayne Wang</t>
+          <t>Diwen Xue</t>
         </is>
       </c>
       <c r="B304" t="n">
@@ -7404,7 +7404,7 @@
         </is>
       </c>
       <c r="D304" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E304" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Ram Sundara Raman</t>
+          <t>Armin Huremagic</t>
         </is>
       </c>
       <c r="B305" t="n">
@@ -7427,18 +7427,18 @@
         </is>
       </c>
       <c r="D305" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>University of California, Santa Cruz</t>
+          <t>University of Michigan</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Roya Ensafi</t>
+          <t>Wayne Wang</t>
         </is>
       </c>
       <c r="B306" t="n">
@@ -7450,7 +7450,7 @@
         </is>
       </c>
       <c r="D306" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Annie Dai</t>
+          <t>Ram Sundara Raman</t>
         </is>
       </c>
       <c r="B307" t="n">
@@ -7469,22 +7469,22 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>CCS-Don't Look Up: There Are Sensitive Internal Links in the Clear on GEO Satellites.</t>
+          <t>CCS-Fingerprinting Deep Packet Inspection Devices by their Ambiguities.</t>
         </is>
       </c>
       <c r="D307" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>University of Maryland, College Park</t>
+          <t>University of California, Santa Cruz</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Keegan Ryan</t>
+          <t>Roya Ensafi</t>
         </is>
       </c>
       <c r="B308" t="n">
@@ -7492,22 +7492,22 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>CCS-Don't Look Up: There Are Sensitive Internal Links in the Clear on GEO Satellites.</t>
+          <t>CCS-Fingerprinting Deep Packet Inspection Devices by their Ambiguities.</t>
         </is>
       </c>
       <c r="D308" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>University of California San Diego</t>
+          <t>University of Michigan</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Dave Levin</t>
+          <t>Annie Dai</t>
         </is>
       </c>
       <c r="B309" t="n">
@@ -7519,7 +7519,7 @@
         </is>
       </c>
       <c r="D309" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Nadia Heninger</t>
+          <t>Keegan Ryan</t>
         </is>
       </c>
       <c r="B310" t="n">
@@ -7542,7 +7542,7 @@
         </is>
       </c>
       <c r="D310" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
@@ -7553,7 +7553,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Aaron Schulman</t>
+          <t>Dave Levin</t>
         </is>
       </c>
       <c r="B311" t="n">
@@ -7565,18 +7565,18 @@
         </is>
       </c>
       <c r="D311" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>University of California San Diego</t>
+          <t>University of Maryland, College Park</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Zeyu Liu 0004</t>
+          <t>Nadia Heninger</t>
         </is>
       </c>
       <c r="B312" t="n">
@@ -7584,22 +7584,22 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>CCS-Phalanx: An FHE-Friendly SNARK for Verifiable Computation on Encrypted Data.</t>
+          <t>CCS-Don't Look Up: There Are Sensitive Internal Links in the Clear on GEO Satellites.</t>
         </is>
       </c>
       <c r="D312" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Yale University</t>
+          <t>University of California San Diego</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Ben Fisch</t>
+          <t>Aaron Schulman</t>
         </is>
       </c>
       <c r="B313" t="n">
@@ -7607,7 +7607,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>CCS-Phalanx: An FHE-Friendly SNARK for Verifiable Computation on Encrypted Data.</t>
+          <t>CCS-Don't Look Up: There Are Sensitive Internal Links in the Clear on GEO Satellites.</t>
         </is>
       </c>
       <c r="D313" t="n">
@@ -7615,14 +7615,14 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Yale University</t>
+          <t>University of California San Diego</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Xiaozhong Liu 0001</t>
+          <t>Zeyu Liu 0004</t>
         </is>
       </c>
       <c r="B314" t="n">
@@ -7630,22 +7630,22 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>CCS-FlippedRAG: Black-Box Opinion Manipulation Adversarial Attacks to Retrieval-Augmented Generation Models.</t>
+          <t>CCS-Phalanx: An FHE-Friendly SNARK for Verifiable Computation on Encrypted Data.</t>
         </is>
       </c>
       <c r="D314" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Worcester Polytechnic Institute</t>
+          <t>Yale University</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Chen Gong 0005</t>
+          <t>Ben Fisch</t>
         </is>
       </c>
       <c r="B315" t="n">
@@ -7653,22 +7653,22 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>CCS-DPImageBench: A Unified Benchmark for Differentially Private Image Synthesis.</t>
+          <t>CCS-Phalanx: An FHE-Friendly SNARK for Verifiable Computation on Encrypted Data.</t>
         </is>
       </c>
       <c r="D315" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>Yale University</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Kecen Li</t>
+          <t>Xiaozhong Liu 0001</t>
         </is>
       </c>
       <c r="B316" t="n">
@@ -7676,22 +7676,22 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>CCS-DPImageBench: A Unified Benchmark for Differentially Private Image Synthesis.</t>
+          <t>CCS-FlippedRAG: Black-Box Opinion Manipulation Adversarial Attacks to Retrieval-Augmented Generation Models.</t>
         </is>
       </c>
       <c r="D316" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>Worcester Polytechnic Institute</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Zinan Lin 0001</t>
+          <t>Chen Gong 0005</t>
         </is>
       </c>
       <c r="B317" t="n">
@@ -7703,18 +7703,18 @@
         </is>
       </c>
       <c r="D317" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Microsoft (United States)</t>
+          <t>University of Virginia</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Tianhao Wang 0001</t>
+          <t>Kecen Li</t>
         </is>
       </c>
       <c r="B318" t="n">
@@ -7726,7 +7726,7 @@
         </is>
       </c>
       <c r="D318" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E318" t="inlineStr">
         <is>
@@ -7737,7 +7737,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Xiaolong Ma</t>
+          <t>Zinan Lin 0001</t>
         </is>
       </c>
       <c r="B319" t="n">
@@ -7745,22 +7745,22 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>CCS-What Lurks Within? Concept Auditing for Shared Diffusion Models at Scale.</t>
+          <t>CCS-DPImageBench: A Unified Benchmark for Differentially Private Image Synthesis.</t>
         </is>
       </c>
       <c r="D319" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>University of Arizona</t>
+          <t>Microsoft (United States)</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Hanshen Xiao</t>
+          <t>Tianhao Wang 0001</t>
         </is>
       </c>
       <c r="B320" t="n">
@@ -7768,22 +7768,22 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>CCS-One-Sided Bounded Noise: Theory, Optimization Algorithms and Applications.</t>
+          <t>CCS-DPImageBench: A Unified Benchmark for Differentially Private Image Synthesis.</t>
         </is>
       </c>
       <c r="D320" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>University of Virginia</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Elaine Shi</t>
+          <t>Xiaolong Ma</t>
         </is>
       </c>
       <c r="B321" t="n">
@@ -7791,22 +7791,22 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>CCS-One-Sided Bounded Noise: Theory, Optimization Algorithms and Applications.</t>
+          <t>CCS-What Lurks Within? Concept Auditing for Shared Diffusion Models at Scale.</t>
         </is>
       </c>
       <c r="D321" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>University of Arizona</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Srinivas Devadas</t>
+          <t>Hanshen Xiao</t>
         </is>
       </c>
       <c r="B322" t="n">
@@ -7818,18 +7818,18 @@
         </is>
       </c>
       <c r="D322" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Massachusetts Institute of Technology</t>
+          <t>Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Paschalis Bekos</t>
+          <t>Elaine Shi</t>
         </is>
       </c>
       <c r="B323" t="n">
@@ -7837,22 +7837,22 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>CCS-PIIxel Leaks: Passive Identification of Personally Identifiable Information Leakage through Meta Pixel.</t>
+          <t>CCS-One-Sided Bounded Noise: Theory, Optimization Algorithms and Applications.</t>
         </is>
       </c>
       <c r="D323" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Stony Brook University</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Michalis Polychronakis</t>
+          <t>Srinivas Devadas</t>
         </is>
       </c>
       <c r="B324" t="n">
@@ -7860,7 +7860,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>CCS-PIIxel Leaks: Passive Identification of Personally Identifiable Information Leakage through Meta Pixel.</t>
+          <t>CCS-One-Sided Bounded Noise: Theory, Optimization Algorithms and Applications.</t>
         </is>
       </c>
       <c r="D324" t="n">
@@ -7868,14 +7868,14 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Stony Brook University</t>
+          <t>Massachusetts Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>David Inyangson</t>
+          <t>Paschalis Bekos</t>
         </is>
       </c>
       <c r="B325" t="n">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>CCS-Amigo: Secure Group Mesh Messaging in Realistic Protest Settings.</t>
+          <t>CCS-PIIxel Leaks: Passive Identification of Personally Identifiable Information Leakage through Meta Pixel.</t>
         </is>
       </c>
       <c r="D325" t="n">
@@ -7891,14 +7891,14 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Johns Hopkins University</t>
+          <t>Stony Brook University</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Sarah Radway</t>
+          <t>Michalis Polychronakis</t>
         </is>
       </c>
       <c r="B326" t="n">
@@ -7906,22 +7906,22 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>CCS-Amigo: Secure Group Mesh Messaging in Realistic Protest Settings.</t>
+          <t>CCS-PIIxel Leaks: Passive Identification of Personally Identifiable Information Leakage through Meta Pixel.</t>
         </is>
       </c>
       <c r="D326" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Harvard University Press</t>
+          <t>Stony Brook University</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Tushar M. Jois</t>
+          <t>David Inyangson</t>
         </is>
       </c>
       <c r="B327" t="n">
@@ -7933,18 +7933,18 @@
         </is>
       </c>
       <c r="D327" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>City College of New York</t>
+          <t>Johns Hopkins University</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Nelly Fazio</t>
+          <t>Sarah Radway</t>
         </is>
       </c>
       <c r="B328" t="n">
@@ -7956,18 +7956,18 @@
         </is>
       </c>
       <c r="D328" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>City College of New York</t>
+          <t>Harvard University Press</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>James Mickens</t>
+          <t>Tushar M. Jois</t>
         </is>
       </c>
       <c r="B329" t="n">
@@ -7979,18 +7979,18 @@
         </is>
       </c>
       <c r="D329" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Harvard University Press</t>
+          <t>City College of New York</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Somiya Chhillar</t>
+          <t>Nelly Fazio</t>
         </is>
       </c>
       <c r="B330" t="n">
@@ -7998,22 +7998,22 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>CCS-Exposing Privacy Risks in Anonymizing Clinical Data: Combinatorial Refinement Attacks on</t>
+          <t>CCS-Amigo: Secure Group Mesh Messaging in Realistic Protest Settings.</t>
         </is>
       </c>
       <c r="D330" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>George Mason University</t>
+          <t>City College of New York</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Evgenios M. Kornaropoulos</t>
+          <t>James Mickens</t>
         </is>
       </c>
       <c r="B331" t="n">
@@ -8021,22 +8021,22 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>CCS-Exposing Privacy Risks in Anonymizing Clinical Data: Combinatorial Refinement Attacks on</t>
+          <t>CCS-Amigo: Secure Group Mesh Messaging in Realistic Protest Settings.</t>
         </is>
       </c>
       <c r="D331" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>George Mason University</t>
+          <t>Harvard University Press</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Julia Nonnenkamp</t>
+          <t>Somiya Chhillar</t>
         </is>
       </c>
       <c r="B332" t="n">
@@ -8044,7 +8044,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>CCS-Hidden in Plain Bytes: Investigating Interpersonal Account Compromise with Data Exports.</t>
+          <t>CCS-Exposing Privacy Risks in Anonymizing Clinical Data: Combinatorial Refinement Attacks on</t>
         </is>
       </c>
       <c r="D332" t="n">
@@ -8052,14 +8052,14 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>University of Wisconsin–Madison</t>
+          <t>George Mason University</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Naman Gupta</t>
+          <t>Evgenios M. Kornaropoulos</t>
         </is>
       </c>
       <c r="B333" t="n">
@@ -8067,22 +8067,22 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>CCS-Hidden in Plain Bytes: Investigating Interpersonal Account Compromise with Data Exports.</t>
+          <t>CCS-Exposing Privacy Risks in Anonymizing Clinical Data: Combinatorial Refinement Attacks on</t>
         </is>
       </c>
       <c r="D333" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>University of Wisconsin–Madison</t>
+          <t>George Mason University</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Rahul Chatterjee 0001</t>
+          <t>Julia Nonnenkamp</t>
         </is>
       </c>
       <c r="B334" t="n">
@@ -8094,7 +8094,7 @@
         </is>
       </c>
       <c r="D334" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E334" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Jan Tolsdorf</t>
+          <t>Naman Gupta</t>
         </is>
       </c>
       <c r="B335" t="n">
@@ -8113,22 +8113,22 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>CCS-Phishing Susceptibility and the (In-)Effectiveness of Common Anti-Phishing Interventions in a Large University Hospital.</t>
+          <t>CCS-Hidden in Plain Bytes: Investigating Interpersonal Account Compromise with Data Exports.</t>
         </is>
       </c>
       <c r="D335" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>George Washington University</t>
+          <t>University of Wisconsin–Madison</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Yaman Yu</t>
+          <t>Rahul Chatterjee 0001</t>
         </is>
       </c>
       <c r="B336" t="n">
@@ -8136,22 +8136,22 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>CCS-YouthSafe: A Youth-Centric Safety Benchmark and Safeguard Model for Large Language Models.</t>
+          <t>CCS-Hidden in Plain Bytes: Investigating Interpersonal Account Compromise with Data Exports.</t>
         </is>
       </c>
       <c r="D336" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>University of Wisconsin–Madison</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Yiren Liu</t>
+          <t>Jan Tolsdorf</t>
         </is>
       </c>
       <c r="B337" t="n">
@@ -8159,22 +8159,22 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>CCS-YouthSafe: A Youth-Centric Safety Benchmark and Safeguard Model for Large Language Models.</t>
+          <t>CCS-Phishing Susceptibility and the (In-)Effectiveness of Common Anti-Phishing Interventions in a Large University Hospital.</t>
         </is>
       </c>
       <c r="D337" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>George Washington University</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Yuqi Zhang</t>
+          <t>Yaman Yu</t>
         </is>
       </c>
       <c r="B338" t="n">
@@ -8186,7 +8186,7 @@
         </is>
       </c>
       <c r="D338" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E338" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Yun Huang 0003</t>
+          <t>Yiren Liu</t>
         </is>
       </c>
       <c r="B339" t="n">
@@ -8209,7 +8209,7 @@
         </is>
       </c>
       <c r="D339" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E339" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Yang Wang 0005</t>
+          <t>Yuqi Zhang</t>
         </is>
       </c>
       <c r="B340" t="n">
@@ -8232,7 +8232,7 @@
         </is>
       </c>
       <c r="D340" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E340" t="inlineStr">
         <is>
@@ -8243,7 +8243,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Milad Nasr</t>
+          <t>Yun Huang 0003</t>
         </is>
       </c>
       <c r="B341" t="n">
@@ -8251,22 +8251,22 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>CCS-Evaluating the Robustness of a Production Malware Detection System to Transferable Adversarial Attacks.</t>
+          <t>CCS-YouthSafe: A Youth-Centric Safety Benchmark and Safeguard Model for Large Language Models.</t>
         </is>
       </c>
       <c r="D341" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Yanick Fratantonio</t>
+          <t>Yang Wang 0005</t>
         </is>
       </c>
       <c r="B342" t="n">
@@ -8274,22 +8274,22 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>CCS-Evaluating the Robustness of a Production Malware Detection System to Transferable Adversarial Attacks.</t>
+          <t>CCS-YouthSafe: A Youth-Centric Safety Benchmark and Safeguard Model for Large Language Models.</t>
         </is>
       </c>
       <c r="D342" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Google (Switzerland)</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Luca Invernizzi</t>
+          <t>Milad Nasr</t>
         </is>
       </c>
       <c r="B343" t="n">
@@ -8301,18 +8301,18 @@
         </is>
       </c>
       <c r="D343" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Google (Switzerland)</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Ange Albertini</t>
+          <t>Yanick Fratantonio</t>
         </is>
       </c>
       <c r="B344" t="n">
@@ -8324,7 +8324,7 @@
         </is>
       </c>
       <c r="D344" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E344" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Alex Petit-Bianco</t>
+          <t>Luca Invernizzi</t>
         </is>
       </c>
       <c r="B345" t="n">
@@ -8347,18 +8347,18 @@
         </is>
       </c>
       <c r="D345" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>Google (Switzerland)</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Andreas Terzis</t>
+          <t>Ange Albertini</t>
         </is>
       </c>
       <c r="B346" t="n">
@@ -8370,18 +8370,18 @@
         </is>
       </c>
       <c r="D346" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>Google (Switzerland)</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Kurt Thomas</t>
+          <t>Alex Petit-Bianco</t>
         </is>
       </c>
       <c r="B347" t="n">
@@ -8393,7 +8393,7 @@
         </is>
       </c>
       <c r="D347" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E347" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Elie Bursztein</t>
+          <t>Andreas Terzis</t>
         </is>
       </c>
       <c r="B348" t="n">
@@ -8416,7 +8416,7 @@
         </is>
       </c>
       <c r="D348" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E348" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Nicholas Carlini</t>
+          <t>Kurt Thomas</t>
         </is>
       </c>
       <c r="B349" t="n">
@@ -8439,7 +8439,7 @@
         </is>
       </c>
       <c r="D349" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E349" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Harsh Chaudhari</t>
+          <t>Elie Bursztein</t>
         </is>
       </c>
       <c r="B350" t="n">
@@ -8458,22 +8458,22 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>CCS-Cascading Adversarial Bias from Injection to Distillation in Language Models.</t>
+          <t>CCS-Evaluating the Robustness of a Production Malware Detection System to Transferable Adversarial Attacks.</t>
         </is>
       </c>
       <c r="D350" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Jamie Hayes</t>
+          <t>Nicholas Carlini</t>
         </is>
       </c>
       <c r="B351" t="n">
@@ -8481,22 +8481,22 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>CCS-Cascading Adversarial Bias from Injection to Distillation in Language Models.</t>
+          <t>CCS-Evaluating the Robustness of a Production Malware Detection System to Transferable Adversarial Attacks.</t>
         </is>
       </c>
       <c r="D351" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Google (United Kingdom)</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Matthew Jagielski</t>
+          <t>Harsh Chaudhari</t>
         </is>
       </c>
       <c r="B352" t="n">
@@ -8508,18 +8508,18 @@
         </is>
       </c>
       <c r="D352" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Ilia Shumailov</t>
+          <t>Jamie Hayes</t>
         </is>
       </c>
       <c r="B353" t="n">
@@ -8531,18 +8531,18 @@
         </is>
       </c>
       <c r="D353" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Google DeepMind (United Kingdom); Google (United Kingdom)</t>
+          <t>Google (United Kingdom)</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Milad Nasr</t>
+          <t>Matthew Jagielski</t>
         </is>
       </c>
       <c r="B354" t="n">
@@ -8554,7 +8554,7 @@
         </is>
       </c>
       <c r="D354" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E354" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Alina Oprea</t>
+          <t>Ilia Shumailov</t>
         </is>
       </c>
       <c r="B355" t="n">
@@ -8577,18 +8577,18 @@
         </is>
       </c>
       <c r="D355" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>Google DeepMind (United Kingdom); Google (United Kingdom)</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Changjiang Li</t>
+          <t>Milad Nasr</t>
         </is>
       </c>
       <c r="B356" t="n">
@@ -8596,22 +8596,22 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>CCS-You Can't Steal Nothing: Mitigating Prompt Leakages in LLMs via System Vectors.</t>
+          <t>CCS-Cascading Adversarial Bias from Injection to Distillation in Language Models.</t>
         </is>
       </c>
       <c r="D356" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Palo Alto Networks (United States)</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Ting Wang 0006</t>
+          <t>Alina Oprea</t>
         </is>
       </c>
       <c r="B357" t="n">
@@ -8619,22 +8619,22 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>CCS-You Can't Steal Nothing: Mitigating Prompt Leakages in LLMs via System Vectors.</t>
+          <t>CCS-Cascading Adversarial Bias from Injection to Distillation in Language Models.</t>
         </is>
       </c>
       <c r="D357" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Stony Brook University</t>
+          <t>Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Sangho Lee 0001</t>
+          <t>Changjiang Li</t>
         </is>
       </c>
       <c r="B358" t="n">
@@ -8642,22 +8642,22 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>CCS-IOValve: Leakage-Free I/O Sandbox for Large-Scale Untrusted Data Processing.</t>
+          <t>CCS-You Can't Steal Nothing: Mitigating Prompt Leakages in LLMs via System Vectors.</t>
         </is>
       </c>
       <c r="D358" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Microsoft (United States)</t>
+          <t>Palo Alto Networks (United States)</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Jules Drean</t>
+          <t>Ting Wang 0006</t>
         </is>
       </c>
       <c r="B359" t="n">
@@ -8665,22 +8665,22 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>CCS-IOValve: Leakage-Free I/O Sandbox for Large-Scale Untrusted Data Processing.</t>
+          <t>CCS-You Can't Steal Nothing: Mitigating Prompt Leakages in LLMs via System Vectors.</t>
         </is>
       </c>
       <c r="D359" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Massachusetts Institute of Technology</t>
+          <t>Stony Brook University</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Yue Tan</t>
+          <t>Sangho Lee 0001</t>
         </is>
       </c>
       <c r="B360" t="n">
@@ -8692,18 +8692,18 @@
         </is>
       </c>
       <c r="D360" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Princeton University</t>
+          <t>Microsoft (United States)</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Marcus Peinado</t>
+          <t>Jules Drean</t>
         </is>
       </c>
       <c r="B361" t="n">
@@ -8715,18 +8715,18 @@
         </is>
       </c>
       <c r="D361" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Microsoft (United States)</t>
+          <t>Massachusetts Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Moritz Schloegel</t>
+          <t>Yue Tan</t>
         </is>
       </c>
       <c r="B362" t="n">
@@ -8734,22 +8734,22 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>CCS-Protocol-Aware Firmware Rehosting for Effective Fuzzing of Embedded Network Stacks.</t>
+          <t>CCS-IOValve: Leakage-Free I/O Sandbox for Large-Scale Untrusted Data Processing.</t>
         </is>
       </c>
       <c r="D362" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Princeton University</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Brian Johannesmeyer</t>
+          <t>Marcus Peinado</t>
         </is>
       </c>
       <c r="B363" t="n">
@@ -8757,22 +8757,22 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>CCS-Dynamic Detection of Vulnerable DMA Race Conditions.</t>
+          <t>CCS-IOValve: Leakage-Free I/O Sandbox for Large-Scale Untrusted Data Processing.</t>
         </is>
       </c>
       <c r="D363" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Qualcomm (United States)</t>
+          <t>Microsoft (United States)</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Kun Sun 0001</t>
+          <t>Moritz Schloegel</t>
         </is>
       </c>
       <c r="B364" t="n">
@@ -8780,22 +8780,22 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>CCS-Off-Path TCP Exploits: PMTUD Breaks TCP Connection Isolation in IP Address Sharing Scenarios.</t>
+          <t>CCS-Protocol-Aware Firmware Rehosting for Effective Fuzzing of Embedded Network Stacks.</t>
         </is>
       </c>
       <c r="D364" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>George Mason University</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Lucien K. L. Ng</t>
+          <t>Brian Johannesmeyer</t>
         </is>
       </c>
       <c r="B365" t="n">
@@ -8803,7 +8803,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>CCS-Toss: Garbled PIR from Table-Only Stacking.</t>
+          <t>CCS-Dynamic Detection of Vulnerable DMA Race Conditions.</t>
         </is>
       </c>
       <c r="D365" t="n">
@@ -8811,14 +8811,14 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>Qualcomm (United States)</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Vladimir Kolesnikov</t>
+          <t>Kun Sun 0001</t>
         </is>
       </c>
       <c r="B366" t="n">
@@ -8826,22 +8826,22 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>CCS-Toss: Garbled PIR from Table-Only Stacking.</t>
+          <t>CCS-Off-Path TCP Exploits: PMTUD Breaks TCP Connection Isolation in IP Address Sharing Scenarios.</t>
         </is>
       </c>
       <c r="D366" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>George Mason University</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Xiao Wang 0012</t>
+          <t>Lucien K. L. Ng</t>
         </is>
       </c>
       <c r="B367" t="n">
@@ -8849,22 +8849,22 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>CCS-Secure Noise Sampling for Differentially Private Collaborative Learning.</t>
+          <t>CCS-Toss: Garbled PIR from Table-Only Stacking.</t>
         </is>
       </c>
       <c r="D367" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Northwestern University</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Somesh Jha</t>
+          <t>Vladimir Kolesnikov</t>
         </is>
       </c>
       <c r="B368" t="n">
@@ -8872,22 +8872,22 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>CCS-Secure Noise Sampling for Differentially Private Collaborative Learning.</t>
+          <t>CCS-Toss: Garbled PIR from Table-Only Stacking.</t>
         </is>
       </c>
       <c r="D368" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Lucas Piske</t>
+          <t>Xiao Wang 0012</t>
         </is>
       </c>
       <c r="B369" t="n">
@@ -8895,22 +8895,22 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>CCS-Distance-Aware OT with Application to Fuzzy PSI.</t>
+          <t>CCS-Secure Noise Sampling for Differentially Private Collaborative Learning.</t>
         </is>
       </c>
       <c r="D369" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Northwestern University</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Jaspal Singh</t>
+          <t>Somesh Jha</t>
         </is>
       </c>
       <c r="B370" t="n">
@@ -8918,22 +8918,22 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>CCS-Distance-Aware OT with Application to Fuzzy PSI.</t>
+          <t>CCS-Secure Noise Sampling for Differentially Private Collaborative Learning.</t>
         </is>
       </c>
       <c r="D370" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology; Purdue University West Lafayette</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Ni Trieu</t>
+          <t>Lucas Piske</t>
         </is>
       </c>
       <c r="B371" t="n">
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="D371" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E371" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Vladimir Kolesnikov</t>
+          <t>Jaspal Singh</t>
         </is>
       </c>
       <c r="B372" t="n">
@@ -8968,18 +8968,18 @@
         </is>
       </c>
       <c r="D372" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>Georgia Institute of Technology; Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Vassilis Zikas</t>
+          <t>Ni Trieu</t>
         </is>
       </c>
       <c r="B373" t="n">
@@ -8991,18 +8991,18 @@
         </is>
       </c>
       <c r="D373" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Wei-Kai Lin</t>
+          <t>Vladimir Kolesnikov</t>
         </is>
       </c>
       <c r="B374" t="n">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>CCS-MegaBlocks: Breaking the Logarithmic I/O-Overhead Barrier for Oblivious RAM.</t>
+          <t>CCS-Distance-Aware OT with Application to Fuzzy PSI.</t>
         </is>
       </c>
       <c r="D374" t="n">
@@ -9018,14 +9018,14 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Sara Rampazzi</t>
+          <t>Vassilis Zikas</t>
         </is>
       </c>
       <c r="B375" t="n">
@@ -9033,22 +9033,22 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>CCS-Poster: Recapture Detection Using Disparity Map Obtained from Dual-Pixel Image Sensors.</t>
+          <t>CCS-Distance-Aware OT with Application to Fuzzy PSI.</t>
         </is>
       </c>
       <c r="D375" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>University of Florida</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Dominik Wermke</t>
+          <t>Wei-Kai Lin</t>
         </is>
       </c>
       <c r="B376" t="n">
@@ -9056,22 +9056,22 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>CCS-Poster: Computer Security Researchers' Experiences with Vulnerability Disclosures.</t>
+          <t>CCS-MegaBlocks: Breaking the Logarithmic I/O-Overhead Barrier for Oblivious RAM.</t>
         </is>
       </c>
       <c r="D376" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>North Carolina State University</t>
+          <t>University of Virginia</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Yan Chen 0004</t>
+          <t>Sara Rampazzi</t>
         </is>
       </c>
       <c r="B377" t="n">
@@ -9079,22 +9079,22 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>CCS-Poster: Obfuscating Function Activity States to Enhance Privacy in Serverless Applications.</t>
+          <t>CCS-Poster: Recapture Detection Using Disparity Map Obtained from Dual-Pixel Image Sensors.</t>
         </is>
       </c>
       <c r="D377" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>Northwestern University</t>
+          <t>University of Florida</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Tashi Stirewalt</t>
+          <t>Dominik Wermke</t>
         </is>
       </c>
       <c r="B378" t="n">
@@ -9102,22 +9102,22 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>CCS-Poster: Adversarial Habituation Attack: A Psychological Extension and Re-framing of Boiling Frog Attack.</t>
+          <t>CCS-Poster: Computer Security Researchers' Experiences with Vulnerability Disclosures.</t>
         </is>
       </c>
       <c r="D378" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>Washington State University</t>
+          <t>North Carolina State University</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Gefei Tan</t>
+          <t>Yan Chen 0004</t>
         </is>
       </c>
       <c r="B379" t="n">
@@ -9125,11 +9125,11 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>CCS-Scalable Cryptography for Trustworthy Machine Learning in the LLM Era.</t>
+          <t>CCS-Poster: Obfuscating Function Activity States to Enhance Privacy in Serverless Applications.</t>
         </is>
       </c>
       <c r="D379" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E379" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Daniel Olszewski</t>
+          <t>Tashi Stirewalt</t>
         </is>
       </c>
       <c r="B380" t="n">
@@ -9148,7 +9148,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>CCS-On Defining Reproducible Outcomes for the Computer Security Community.</t>
+          <t>CCS-Poster: Adversarial Habituation Attack: A Psychological Extension and Re-framing of Boiling Frog Attack.</t>
         </is>
       </c>
       <c r="D380" t="n">
@@ -9156,14 +9156,14 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>University of Florida</t>
+          <t>Washington State University</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>F. Betül Durak</t>
+          <t>Gefei Tan</t>
         </is>
       </c>
       <c r="B381" t="n">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>CCS-ACM CCS Young Scholars Development Program.</t>
+          <t>CCS-Scalable Cryptography for Trustworthy Machine Learning in the LLM Era.</t>
         </is>
       </c>
       <c r="D381" t="n">
@@ -9179,14 +9179,14 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>Microsoft (United States)</t>
+          <t>Northwestern University</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Fengjun Li</t>
+          <t>Daniel Olszewski</t>
         </is>
       </c>
       <c r="B382" t="n">
@@ -9194,22 +9194,22 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>CCS-ACM CCS Young Scholars Development Program.</t>
+          <t>CCS-On Defining Reproducible Outcomes for the Computer Security Community.</t>
         </is>
       </c>
       <c r="D382" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>University of Kansas</t>
+          <t>University of Florida</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Sophie Stephenson</t>
+          <t>F. Betül Durak</t>
         </is>
       </c>
       <c r="B383" t="n">
@@ -9221,18 +9221,18 @@
         </is>
       </c>
       <c r="D383" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>University of Wisconsin–Madison</t>
+          <t>Microsoft (United States)</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Ruoxi Jia 0001</t>
+          <t>Fengjun Li</t>
         </is>
       </c>
       <c r="B384" t="n">
@@ -9240,22 +9240,22 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>CCS-AISec '25: 18th ACM Workshop on Artificial Intelligence and Security.</t>
+          <t>CCS-ACM CCS Young Scholars Development Program.</t>
         </is>
       </c>
       <c r="D384" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>University of Kansas</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Kassem Fawaz</t>
+          <t>Sophie Stephenson</t>
         </is>
       </c>
       <c r="B385" t="n">
@@ -9263,11 +9263,11 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>CCS-CPSIoTSec'25: The 7th Joint Workshop on CPS &amp; IoT Security and Privacy.</t>
+          <t>CCS-ACM CCS Young Scholars Development Program.</t>
         </is>
       </c>
       <c r="D385" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E385" t="inlineStr">
         <is>
@@ -9278,7 +9278,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Jinoh Kim</t>
+          <t>Ruoxi Jia 0001</t>
         </is>
       </c>
       <c r="B386" t="n">
@@ -9286,22 +9286,22 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>CCS-WATCH '25: First Workshop on Analytics, Telemetry, and Cybersecurity for HPCC.</t>
+          <t>CCS-AISec '25: 18th ACM Workshop on Artificial Intelligence and Security.</t>
         </is>
       </c>
       <c r="D386" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>East Texas A&amp;M University</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Aditya Sirish A Yelgundhalli</t>
+          <t>Kassem Fawaz</t>
         </is>
       </c>
       <c r="B387" t="n">
@@ -9309,7 +9309,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>CCS-SCORED '25: Workshop on Software Supply Chain Offensive Research and Ecosystem Defenses.</t>
+          <t>CCS-CPSIoTSec'25: The 7th Joint Workshop on CPS &amp; IoT Security and Privacy.</t>
         </is>
       </c>
       <c r="D387" t="n">
@@ -9317,14 +9317,14 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>Bloomberg (United States)</t>
+          <t>University of Wisconsin–Madison</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Dennis Roellke</t>
+          <t>Jinoh Kim</t>
         </is>
       </c>
       <c r="B388" t="n">
@@ -9332,22 +9332,22 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>CCS-SCORED '25: Workshop on Software Supply Chain Offensive Research and Ecosystem Defenses.</t>
+          <t>CCS-WATCH '25: First Workshop on Analytics, Telemetry, and Cybersecurity for HPCC.</t>
         </is>
       </c>
       <c r="D388" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>Bloomberg (United States)</t>
+          <t>East Texas A&amp;M University</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Drew Davidson</t>
+          <t>Aditya Sirish A Yelgundhalli</t>
         </is>
       </c>
       <c r="B389" t="n">
@@ -9359,18 +9359,18 @@
         </is>
       </c>
       <c r="D389" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>University of Kansas</t>
+          <t>Bloomberg (United States)</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Marcela S. Melara</t>
+          <t>Dennis Roellke</t>
         </is>
       </c>
       <c r="B390" t="n">
@@ -9382,18 +9382,18 @@
         </is>
       </c>
       <c r="D390" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>Intel (United States)</t>
+          <t>Bloomberg (United States)</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Santiago Torres-Arias</t>
+          <t>Drew Davidson</t>
         </is>
       </c>
       <c r="B391" t="n">
@@ -9405,18 +9405,18 @@
         </is>
       </c>
       <c r="D391" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>University of Kansas</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Sarah Evans</t>
+          <t>Marcela S. Melara</t>
         </is>
       </c>
       <c r="B392" t="n">
@@ -9428,18 +9428,18 @@
         </is>
       </c>
       <c r="D392" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>DELL (United States)</t>
+          <t>Intel (United States)</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Yuchen Zhang 0006</t>
+          <t>Santiago Torres-Arias</t>
         </is>
       </c>
       <c r="B393" t="n">
@@ -9451,18 +9451,18 @@
         </is>
       </c>
       <c r="D393" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>New York University</t>
+          <t>Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Tianshi Li 0001</t>
+          <t>Sarah Evans</t>
         </is>
       </c>
       <c r="B394" t="n">
@@ -9470,22 +9470,22 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>CCS-HAIPS '25: First ACM CCS Workshop on Human-Centered AI Privacy and Security.</t>
+          <t>CCS-SCORED '25: Workshop on Software Supply Chain Offensive Research and Ecosystem Defenses.</t>
         </is>
       </c>
       <c r="D394" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>University of Notre Dame; Northeastern University</t>
+          <t>DELL (United States)</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Toby Jia-Jun Li</t>
+          <t>Yuchen Zhang 0006</t>
         </is>
       </c>
       <c r="B395" t="n">
@@ -9493,22 +9493,22 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>CCS-HAIPS '25: First ACM CCS Workshop on Human-Centered AI Privacy and Security.</t>
+          <t>CCS-SCORED '25: Workshop on Software Supply Chain Offensive Research and Ecosystem Defenses.</t>
         </is>
       </c>
       <c r="D395" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>University of Notre Dame; Northeastern University</t>
+          <t>New York University</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Yaxing Yao</t>
+          <t>Tianshi Li 0001</t>
         </is>
       </c>
       <c r="B396" t="n">
@@ -9520,18 +9520,18 @@
         </is>
       </c>
       <c r="D396" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>Johns Hopkins University</t>
+          <t>University of Notre Dame; Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Sauvik Das</t>
+          <t>Toby Jia-Jun Li</t>
         </is>
       </c>
       <c r="B397" t="n">
@@ -9543,18 +9543,18 @@
         </is>
       </c>
       <c r="D397" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>University of Notre Dame; Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Zion Leonahenahe Basque</t>
+          <t>Yaxing Yao</t>
         </is>
       </c>
       <c r="B398" t="n">
@@ -9562,22 +9562,22 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>CCS-SURE '25: The 1st ACM Workshop on Software Understanding and Reverse Engineering.</t>
+          <t>CCS-HAIPS '25: First ACM CCS Workshop on Human-Centered AI Privacy and Security.</t>
         </is>
       </c>
       <c r="D398" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Johns Hopkins University</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Ati Priya Bajaj</t>
+          <t>Sauvik Das</t>
         </is>
       </c>
       <c r="B399" t="n">
@@ -9585,22 +9585,22 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>CCS-SURE '25: The 1st ACM Workshop on Software Understanding and Reverse Engineering.</t>
+          <t>CCS-HAIPS '25: First ACM CCS Workshop on Human-Centered AI Privacy and Security.</t>
         </is>
       </c>
       <c r="D399" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Muhammad Taqi Raza</t>
+          <t>Zion Leonahenahe Basque</t>
         </is>
       </c>
       <c r="B400" t="n">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>CCS-QSec '25: Workshop on Quantum Security and Privacy.</t>
+          <t>CCS-SURE '25: The 1st ACM Workshop on Software Understanding and Reverse Engineering.</t>
         </is>
       </c>
       <c r="D400" t="n">
@@ -9616,14 +9616,14 @@
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>University of Massachusetts Amherst</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Jakub Szefer</t>
+          <t>Ati Priya Bajaj</t>
         </is>
       </c>
       <c r="B401" t="n">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>CCS-QSec '25: Workshop on Quantum Security and Privacy.</t>
+          <t>CCS-SURE '25: The 1st ACM Workshop on Software Understanding and Reverse Engineering.</t>
         </is>
       </c>
       <c r="D401" t="n">
@@ -9639,14 +9639,14 @@
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>Northwestern University</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Cristina Nita-Rotaru</t>
+          <t>Muhammad Taqi Raza</t>
         </is>
       </c>
       <c r="B402" t="n">
@@ -9654,22 +9654,22 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>CCS-QRSec 2025: ACM CCS First Workshop on Quantum-Resistant Cryptography and Security.</t>
+          <t>CCS-QSec '25: Workshop on Quantum Security and Privacy.</t>
         </is>
       </c>
       <c r="D402" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>University of Massachusetts Amherst</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Mu Zhang 0001</t>
+          <t>Jakub Szefer</t>
         </is>
       </c>
       <c r="B403" t="n">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>CCS-RICSS'25: 3rd International Workshop on Re-design Industrial Control Systems with Security.</t>
+          <t>CCS-QSec '25: Workshop on Quantum Security and Privacy.</t>
         </is>
       </c>
       <c r="D403" t="n">
@@ -9685,14 +9685,14 @@
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>Northwestern University</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Bimal Viswanath</t>
+          <t>Cristina Nita-Rotaru</t>
         </is>
       </c>
       <c r="B404" t="n">
@@ -9700,22 +9700,22 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>CCS-3D-Sec '25: The 1st ACM Workshop on Deepfake, Deception, and Disinformation Security.</t>
+          <t>CCS-QRSec 2025: ACM CCS First Workshop on Quantum-Resistant Cryptography and Security.</t>
         </is>
       </c>
       <c r="D404" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Luyi Xing</t>
+          <t>Mu Zhang 0001</t>
         </is>
       </c>
       <c r="B405" t="n">
@@ -9723,22 +9723,22 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>CCS-SaTS '25: The 3rd ACM Workshop on Security and Privacy of AI-Empowered Mobile Super Apps.</t>
+          <t>CCS-RICSS'25: 3rd International Workshop on Re-design Industrial Control Systems with Security.</t>
         </is>
       </c>
       <c r="D405" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>University of Utah</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Yue Xiao 0007</t>
+          <t>Bimal Viswanath</t>
         </is>
       </c>
       <c r="B406" t="n">
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>CCS-SaTS '25: The 3rd ACM Workshop on Security and Privacy of AI-Empowered Mobile Super Apps.</t>
+          <t>CCS-3D-Sec '25: The 1st ACM Workshop on Deepfake, Deception, and Disinformation Security.</t>
         </is>
       </c>
       <c r="D406" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>William &amp; Mary; Williams (United States)</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Yuriy Polyakov</t>
+          <t>Luyi Xing</t>
         </is>
       </c>
       <c r="B407" t="n">
@@ -9769,22 +9769,22 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>CCS-WAHC 2025: 13th Workshop on Encrypted Computing &amp; Applied Homomorphic Cryptography.</t>
+          <t>CCS-SaTS '25: The 3rd ACM Workshop on Security and Privacy of AI-Empowered Mobile Super Apps.</t>
         </is>
       </c>
       <c r="D407" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>Duality (United States)</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Kurt Rohloff</t>
+          <t>Yue Xiao 0007</t>
         </is>
       </c>
       <c r="B408" t="n">
@@ -9792,22 +9792,22 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>CCS-WAHC 2025: 13th Workshop on Encrypted Computing &amp; Applied Homomorphic Cryptography.</t>
+          <t>CCS-SaTS '25: The 3rd ACM Workshop on Security and Privacy of AI-Empowered Mobile Super Apps.</t>
         </is>
       </c>
       <c r="D408" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>Duality (United States)</t>
+          <t>William &amp; Mary; Williams (United States)</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>K. K. Ramakrishnan</t>
+          <t>Yuriy Polyakov</t>
         </is>
       </c>
       <c r="B409" t="n">
@@ -9815,13 +9815,59 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>CCS-free5GC '25: The 1st free5GC World Forum.</t>
+          <t>CCS-WAHC 2025: 13th Workshop on Encrypted Computing &amp; Applied Homomorphic Cryptography.</t>
         </is>
       </c>
       <c r="D409" t="n">
         <v>1</v>
       </c>
       <c r="E409" t="inlineStr">
+        <is>
+          <t>Duality (United States)</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Kurt Rohloff</t>
+        </is>
+      </c>
+      <c r="B410" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>CCS-WAHC 2025: 13th Workshop on Encrypted Computing &amp; Applied Homomorphic Cryptography.</t>
+        </is>
+      </c>
+      <c r="D410" t="n">
+        <v>2</v>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>Duality (United States)</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>K. K. Ramakrishnan</t>
+        </is>
+      </c>
+      <c r="B411" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>CCS-free5GC '25: The 1st free5GC World Forum.</t>
+        </is>
+      </c>
+      <c r="D411" t="n">
+        <v>1</v>
+      </c>
+      <c r="E411" t="inlineStr">
         <is>
           <t>University of California, Riverside</t>
         </is>

--- a/Security-data/data/output/ccs_2025_us_institutions.xlsx
+++ b/Security-data/data/output/ccs_2025_us_institutions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E443"/>
+  <dimension ref="A1:E445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2378,7 +2378,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Mariana Raykova 0001</t>
+          <t>Sarah Meiklejohn</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -2390,18 +2390,18 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>Google (United Kingdom); University College London</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Xiao Wang 0012</t>
+          <t>Mariana Raykova 0001</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -2413,18 +2413,18 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Northwestern University</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Xiaolin Li 0015</t>
+          <t>Xiao Wang 0012</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>CCS-Mitigating Data Poisoning Attacks to Local Differential Privacy.</t>
+          <t>CCS-Founding Zero-Knowledge Proof of Training on Optimum Vicinity.</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>Northwestern University</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Ninghui Li 0001</t>
+          <t>Xiaolin Li 0015</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -2459,7 +2459,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Boyang Wang 0001</t>
+          <t>Ninghui Li 0001</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -2482,18 +2482,18 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>University of Cincinnati</t>
+          <t>Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Wenhai Sun</t>
+          <t>Boyang Wang 0001</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -2505,18 +2505,18 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>University of Cincinnati</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Ali Naseh</t>
+          <t>Wenhai Sun</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>CCS-Riddle Me This! Stealthy Membership Inference for Retrieval-Augmented Generation.</t>
+          <t>CCS-Mitigating Data Poisoning Attacks to Local Differential Privacy.</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>University of Massachusetts Amherst</t>
+          <t>Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Yuefeng Peng</t>
+          <t>Ali Naseh</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -2551,7 +2551,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Anshuman Suri</t>
+          <t>Yuefeng Peng</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -2574,18 +2574,18 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>University of Massachusetts Amherst</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Harsh Chaudhari</t>
+          <t>Anshuman Suri</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Alina Oprea</t>
+          <t>Harsh Chaudhari</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Amir Houmansadr</t>
+          <t>Alina Oprea</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -2643,18 +2643,18 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>University of Massachusetts Amherst</t>
+          <t>Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Alexandra Nisenoff</t>
+          <t>Amir Houmansadr</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -2662,22 +2662,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>CCS-Exploiting the Shared Storage API.</t>
+          <t>CCS-Riddle Me This! Stealthy Membership Inference for Retrieval-Augmented Generation.</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>University of Massachusetts Amherst</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Deian Stefan</t>
+          <t>Alexandra Nisenoff</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -2689,18 +2689,18 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>University of California San Diego</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Nicolas Christin</t>
+          <t>Deian Stefan</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -2712,18 +2712,18 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>University of California San Diego</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Michael A. Specter</t>
+          <t>Nicolas Christin</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -2731,22 +2731,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>CCS-Fingerprinting SDKs for Mobile Apps and Where to Find Them: Understanding the Market for Device Fingerprinting.</t>
+          <t>CCS-Exploiting the Shared Storage API.</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Mihai Christodorescu</t>
+          <t>Michael A. Specter</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -2758,7 +2758,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Abbie Farr</t>
+          <t>Mihai Christodorescu</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Bo Ma 0013</t>
+          <t>Abbie Farr</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -2804,7 +2804,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Robin Lassonde</t>
+          <t>Bo Ma 0013</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Haichuan Xu</t>
+          <t>Robin Lassonde</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -2846,22 +2846,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>CCS-Lock the Door But Keep the Window Open: Extracting App-Protected Accessibility Information from Browser-Rendered Websites.</t>
+          <t>CCS-Fingerprinting SDKs for Mobile Apps and Where to Find Them: Understanding the Market for Device Fingerprinting.</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Runze Zhang</t>
+          <t>Haichuan Xu</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Mingxuan Yao</t>
+          <t>Runze Zhang</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>David Oygenblik</t>
+          <t>Mingxuan Yao</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -2919,7 +2919,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Yizhi Huang</t>
+          <t>David Oygenblik</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Brendan Saltaformaggio</t>
+          <t>Yizhi Huang</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Alisha Ukani</t>
+          <t>Brendan Saltaformaggio</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -2984,22 +2984,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>CCS-Local Frames: Exploiting Inherited Origins to Bypass Content Blockers.</t>
+          <t>CCS-Lock the Door But Keep the Window Open: Extracting App-Protected Accessibility Information from Browser-Rendered Websites.</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>University of California San Diego</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Alex C. Snoeren</t>
+          <t>Alisha Ukani</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Jonathan Fuller</t>
+          <t>Alex C. Snoeren</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -3030,22 +3030,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>CCS-Enhanced Web Application Security Through Proactive Dead Drop Resolver Remediation.</t>
+          <t>CCS-Local Frames: Exploiting Inherited Origins to Bypass Content Blockers.</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>United States Military Academy</t>
+          <t>University of California San Diego</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Mingxuan Yao</t>
+          <t>Jonathan Fuller</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -3057,18 +3057,18 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>United States Military Academy</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Saumya Agarwal</t>
+          <t>Mingxuan Yao</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Srimanta Barua</t>
+          <t>Saumya Agarwal</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Taleb Hirani</t>
+          <t>Srimanta Barua</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Brendan Saltaformaggio</t>
+          <t>Taleb Hirani</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -3149,7 +3149,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Simon Oddershede Gregersen</t>
+          <t>Brendan Saltaformaggio</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -3168,22 +3168,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>CCS-Logical Relations for Formally Verified Authenticated Data Structures.</t>
+          <t>CCS-Enhanced Web Application Security Through Proactive Dead Drop Resolver Remediation.</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>New York University</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Chaitanya Agarwal</t>
+          <t>Simon Oddershede Gregersen</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Joseph Tassarotti</t>
+          <t>Chaitanya Agarwal</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -3218,7 +3218,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A. Prasad Sistla</t>
+          <t>Joseph Tassarotti</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>CCS-Approximate Algorithms for Verifying Differential Privacy with Gaussian Distributions.</t>
+          <t>CCS-Logical Relations for Formally Verified Authenticated Data Structures.</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -3245,14 +3245,14 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>University of Illinois Chicago</t>
+          <t>New York University</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Mahesh Viswanathan 0001</t>
+          <t>A. Prasad Sistla</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -3264,18 +3264,18 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>University of Illinois Chicago</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Anitha Gollamudi</t>
+          <t>Mahesh Viswanathan 0001</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -3283,22 +3283,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>CCS-ILA: Correctness via Type Checking for Fully Homomorphic Encryption.</t>
+          <t>CCS-Approximate Algorithms for Verifying Differential Privacy with Gaussian Distributions.</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>University of Massachusetts Lowell</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Joshua Gancher</t>
+          <t>Anitha Gollamudi</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -3310,18 +3310,18 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>University of Massachusetts Lowell</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Kangjie Lu</t>
+          <t>Joshua Gancher</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -3329,22 +3329,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>CCS-SyzParam: Incorporating Runtime Parameters into Kernel Driver Fuzzing.</t>
+          <t>CCS-ILA: Correctness via Type Checking for Fully Homomorphic Encryption.</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>University of Minnesota</t>
+          <t>Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Xin Wang 0001</t>
+          <t>Kangjie Lu</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>CCS-FlowSentry: Accelerating NetFlow-based DDoS Detection.</t>
+          <t>CCS-SyzParam: Incorporating Runtime Parameters into Kernel Driver Fuzzing.</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Stony Brook University</t>
+          <t>University of Minnesota</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Ziming Zhao 0001</t>
+          <t>Xin Wang 0001</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -3375,22 +3375,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>CCS-5G-RNAKA : A Random Number-based Authentication and Key Agreement Protocol for 5G Systems.</t>
+          <t>CCS-FlowSentry: Accelerating NetFlow-based DDoS Detection.</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>Stony Brook University</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Xuening Xu</t>
+          <t>Ziming Zhao 0001</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -3398,22 +3398,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>CCS-Discovering and Exploiting IoT Device Hidden Attributes: A New Vulnerability in Smart Homes.</t>
+          <t>CCS-5G-RNAKA : A Random Number-based Authentication and Key Agreement Protocol for 5G Systems.</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Stevens Institute of Technology</t>
+          <t>Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Chenglong Fu 0002</t>
+          <t>Xuening Xu</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -3425,18 +3425,18 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>University of North Carolina at Charlotte</t>
+          <t>Stevens Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Xiaojiang Du</t>
+          <t>Chenglong Fu 0002</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -3448,18 +3448,18 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Stevens Institute of Technology</t>
+          <t>University of North Carolina at Charlotte</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Bo Luo</t>
+          <t>Xiaojiang Du</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -3471,18 +3471,18 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>University of Kansas</t>
+          <t>Stevens Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Shengzhi Zhang</t>
+          <t>Bo Luo</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -3490,22 +3490,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>CCS-RAG-WM: An Efficient Black-Box Watermarking Approach for Retrieval-Augmented Generation of Large Language Models.</t>
+          <t>CCS-Discovering and Exploiting IoT Device Hidden Attributes: A New Vulnerability in Smart Homes.</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Boston University; Metropolitan College of New York</t>
+          <t>University of Kansas</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Zhiqi Wang</t>
+          <t>Shengzhi Zhang</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -3513,22 +3513,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>CCS-Membership Inference Attacks as Privacy Tools: Reliability, Disparity and Ensemble.</t>
+          <t>CCS-RAG-WM: An Efficient Black-Box Watermarking Approach for Retrieval-Augmented Generation of Large Language Models.</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Rensselaer Polytechnic Institute</t>
+          <t>Boston University; Metropolitan College of New York</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Chengyu Zhang</t>
+          <t>Zhiqi Wang</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -3540,7 +3540,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Yuetian Chen</t>
+          <t>Chengyu Zhang</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -3563,7 +3563,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Nathalie Baracaldo</t>
+          <t>Yuetian Chen</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -3586,18 +3586,18 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>IBM Research - Almaden</t>
+          <t>Rensselaer Polytechnic Institute</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Swanand Ravindra Kadhe</t>
+          <t>Nathalie Baracaldo</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Lei Yu 0002</t>
+          <t>Swanand Ravindra Kadhe</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -3632,18 +3632,18 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Rensselaer Polytechnic Institute</t>
+          <t>IBM Research - Almaden</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Jiahui Gao</t>
+          <t>Lei Yu 0002</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -3651,22 +3651,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>CCS-PULSE: Parallel Private Set Union for Large-Scale Entities.</t>
+          <t>CCS-Membership Inference Attacks as Privacy Tools: Reliability, Disparity and Ensemble.</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Rensselaer Polytechnic Institute</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Son Nguyen</t>
+          <t>Jiahui Gao</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Ni Trieu</t>
+          <t>Son Nguyen</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -3701,7 +3701,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Akhil Bandarupalli</t>
+          <t>Ni Trieu</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -3720,22 +3720,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>CCS-Velox: Scalable Fair Asynchronous MPC from Lightweight Cryptography.</t>
+          <t>CCS-PULSE: Parallel Private Set Union for Large-Scale Entities.</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>David Adei</t>
+          <t>Akhil Bandarupalli</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>CCS-How to Recover a Cryptographic Secret From the Cloud.</t>
+          <t>CCS-Velox: Scalable Fair Asynchronous MPC from Lightweight Cryptography.</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -3751,14 +3751,14 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>North Carolina State University</t>
+          <t>Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Chris Orsini</t>
+          <t>David Adei</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -3770,7 +3770,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Alessandra Scafuro</t>
+          <t>Chris Orsini</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -3793,7 +3793,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Tanner Verber</t>
+          <t>Alessandra Scafuro</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Anuj Gautam</t>
+          <t>Tanner Verber</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -3835,22 +3835,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>CCS-Passwords and FIDO2 Are Meant To Be Secret: A Practical Secure Authentication Channel for Web Browsers.</t>
+          <t>CCS-How to Recover a Cryptographic Secret From the Cloud.</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>University of Tennessee at Knoxville</t>
+          <t>North Carolina State University</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Scott Ruoti</t>
+          <t>Anuj Gautam</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -3862,7 +3862,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Ahsan Zafar</t>
+          <t>Scott Ruoti</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -3881,22 +3881,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>CCS-Same Script, Different Behavior: Characterizing Divergent JavaScript Execution Across Different Device Platforms.</t>
+          <t>CCS-Passwords and FIDO2 Are Meant To Be Secret: A Practical Secure Authentication Channel for Web Browsers.</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>North Carolina State University</t>
+          <t>University of Tennessee at Knoxville</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Junhua Su</t>
+          <t>Ahsan Zafar</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -3908,7 +3908,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Sohom Datta</t>
+          <t>Junhua Su</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Alexandros Kapravelos</t>
+          <t>Sohom Datta</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Anupam Das 0001</t>
+          <t>Alexandros Kapravelos</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -3977,7 +3977,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Ahmet Okutan</t>
+          <t>Anupam Das 0001</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -3996,22 +3996,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>CCS-Conflicting Scores, Confusing Signals: An Empirical Study of Vulnerability Scoring Systems.</t>
+          <t>CCS-Same Script, Different Behavior: Characterizing Divergent JavaScript Execution Across Different Device Platforms.</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Leidos (United States)</t>
+          <t>North Carolina State University</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Yaxing Yao</t>
+          <t>Ahmet Okutan</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -4019,22 +4019,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>CCS-Empowering Parents to Support Children's Online Security and Privacy: Findings from a Randomized Controlled Trial.</t>
+          <t>CCS-Conflicting Scores, Confusing Signals: An Empirical Study of Vulnerability Scoring Systems.</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Johns Hopkins University; Johns Hopkins Medicine</t>
+          <t>Leidos (United States)</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>R. Spencer Hallyburton</t>
+          <t>Yaxing Yao</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -4042,22 +4042,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>CCS-Security-Aware Sensor Fusion with MATE: the Multi-Agent Trust Estimator.</t>
+          <t>CCS-Empowering Parents to Support Children's Online Security and Privacy: Findings from a Randomized Controlled Trial.</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Duke University</t>
+          <t>Johns Hopkins University; Johns Hopkins Medicine</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Mu Zhang 0001</t>
+          <t>R. Spencer Hallyburton</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -4065,22 +4065,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>CCS-Needle in a Haystack: Automated and Scalable Vulnerability Hunting in the Windows ALPC Sea.</t>
+          <t>CCS-Security-Aware Sensor Fusion with MATE: the Multi-Agent Trust Estimator.</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>Duke University</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Lucien K. L. Ng</t>
+          <t>Mu Zhang 0001</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -4088,22 +4088,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>CCS-Lite-PoT: Practical Powers-of-Tau Setup Ceremony.</t>
+          <t>CCS-Needle in a Haystack: Automated and Scalable Vulnerability Hunting in the Windows ALPC Sea.</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology; Visa (United States)</t>
+          <t>University of Utah</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Mohsen Minaei</t>
+          <t>Lucien K. L. Ng</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -4115,18 +4115,18 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Visa (United States)</t>
+          <t>Georgia Institute of Technology; Visa (United States)</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Panagiotis Chatzigiannis</t>
+          <t>Mohsen Minaei</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -4138,7 +4138,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Adithya Bhat</t>
+          <t>Panagiotis Chatzigiannis</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Jie Fu 0003</t>
+          <t>Adithya Bhat</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -4180,22 +4180,22 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>CCS-Safeguarding Graph Neural Networks against Topology Inference Attacks.</t>
+          <t>CCS-Lite-PoT: Practical Powers-of-Tau Setup Ceremony.</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Stevens Institute of Technology</t>
+          <t>Visa (United States)</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Yuan Hong 0001</t>
+          <t>Jie Fu 0003</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -4207,18 +4207,18 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>University of Connecticut</t>
+          <t>Stevens Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Wendy Hui Wang</t>
+          <t>Yuan Hong 0001</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -4230,18 +4230,18 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Stevens Institute of Technology</t>
+          <t>University of Connecticut</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Ruyi Ding</t>
+          <t>Wendy Hui Wang</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -4249,22 +4249,22 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>CCS-MoEcho: Exploiting Side-Channel Attacks to Compromise User Privacy in Mixture-of-Experts LLMs.</t>
+          <t>CCS-Safeguarding Graph Neural Networks against Topology Inference Attacks.</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>Stevens Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Tianhong Xu</t>
+          <t>Ruyi Ding</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -4276,7 +4276,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Xinyi Shen</t>
+          <t>Tianhong Xu</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -4299,18 +4299,18 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Yale University</t>
+          <t>Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Aidong Adam Ding</t>
+          <t>Xinyi Shen</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -4322,18 +4322,18 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>Yale University</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Yunsi Fei</t>
+          <t>Aidong Adam Ding</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>David Oygenblik</t>
+          <t>Yunsi Fei</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -4364,22 +4364,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>CCS-VillainNet: Targeted Poisoning Attacks Against SuperNets Along the Accuracy-Latency Pareto Frontier.</t>
+          <t>CCS-MoEcho: Exploiting Side-Channel Attacks to Compromise User Privacy in Mixture-of-Experts LLMs.</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Abhinav Vemulapalli</t>
+          <t>David Oygenblik</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -4391,7 +4391,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Debopam Sanyal</t>
+          <t>Abhinav Vemulapalli</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -4414,7 +4414,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Alexey Tumanov</t>
+          <t>Debopam Sanyal</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -4437,7 +4437,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Brendan Saltaformaggio</t>
+          <t>Alexey Tumanov</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -4460,7 +4460,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Yiping Ma 0001</t>
+          <t>Brendan Saltaformaggio</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -4479,22 +4479,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>CCS-Armadillo: Robust Single-Server Secure Aggregation for Federated Learning with Input Validation.</t>
+          <t>CCS-VillainNet: Targeted Poisoning Attacks Against SuperNets Along the Accuracy-Latency Pareto Frontier.</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>California University of Pennsylvania; University of California, Berkeley</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Yue Guo</t>
+          <t>Yiping Ma 0001</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -4506,18 +4506,18 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co (United States)</t>
+          <t>California University of Pennsylvania; University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Harish Karthikeyan</t>
+          <t>Yue Guo</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Antigoni Polychroniadou</t>
+          <t>Harish Karthikeyan</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -4552,18 +4552,18 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Morgan Stanley (United States)</t>
+          <t>JPMorgan Chase &amp; Co (United States)</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Sanketh Menda</t>
+          <t>Antigoni Polychroniadou</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -4571,22 +4571,22 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>CCS-The OCH Authenticated Encryption Scheme.</t>
+          <t>CCS-Armadillo: Robust Single-Server Secure Aggregation for Federated Learning with Input Validation.</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>Morgan Stanley (United States)</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Mihir Bellare</t>
+          <t>Sanketh Menda</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -4598,18 +4598,18 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>University of California San Diego</t>
+          <t>Cornell University</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Julia Len</t>
+          <t>Mihir Bellare</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -4621,18 +4621,18 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>University of North Carolina at Chapel Hill; University of North Carolina Health Care</t>
+          <t>University of California San Diego</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Thomas Ristenpart</t>
+          <t>Julia Len</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -4644,18 +4644,18 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>University of North Carolina at Chapel Hill; University of North Carolina Health Care</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Jack Doerner</t>
+          <t>Thomas Ristenpart</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -4663,22 +4663,22 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>CCS-From OT to OLE with Subquadratic Communication.</t>
+          <t>CCS-The OCH Authenticated Encryption Scheme.</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>Cornell University</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Carolina Ortega Pérez</t>
+          <t>Jack Doerner</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>CCS-Interoperable Symmetric Message Franking.</t>
+          <t>CCS-From OT to OLE with Subquadratic Communication.</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -4694,14 +4694,14 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>University of Virginia</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Thomas Ristenpart</t>
+          <t>Carolina Ortega Pérez</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -4713,7 +4713,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Julia Len</t>
+          <t>Thomas Ristenpart</t>
         </is>
       </c>
       <c r="B188" t="n">
@@ -4736,18 +4736,18 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>University of North Carolina at Chapel Hill; University of North Carolina Health Care</t>
+          <t>Cornell University</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Felix Günther 0001</t>
+          <t>Julia Len</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -4755,22 +4755,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>CCS-Breaking and Fixing Content-Defined Chunking.</t>
+          <t>CCS-Interoperable Symmetric Message Franking.</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>IBM Research - Zurich</t>
+          <t>University of North Carolina at Chapel Hill; University of North Carolina Health Care</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Chris Peikert</t>
+          <t>Felix Günther 0001</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>CCS-High-Throughput Universally Composable Threshold FHE Decryption.</t>
+          <t>CCS-Breaking and Fixing Content-Defined Chunking.</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -4786,14 +4786,14 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>University of Michigan</t>
+          <t>IBM Research - Zurich</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Syomantak Chaudhuri</t>
+          <t>Chris Peikert</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -4801,22 +4801,22 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>CCS-Managing Correlations in Data and Privacy Demand.</t>
+          <t>CCS-High-Throughput Universally Composable Threshold FHE Decryption.</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>University of California, Berkeley</t>
+          <t>University of Michigan</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Thomas A. Courtade</t>
+          <t>Syomantak Chaudhuri</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -4828,7 +4828,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Yuntao Du 0002</t>
+          <t>Thomas A. Courtade</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -4847,22 +4847,22 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>CCS-Systematic Assessment of Tabular Data Synthesis.</t>
+          <t>CCS-Managing Correlations in Data and Privacy Demand.</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Elijah Robert Bouma-Sims</t>
+          <t>Yuntao Du 0002</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>CCS-'Is this a scam?': The Nature and Quality of Reddit Discussion about Scams.</t>
+          <t>CCS-Systematic Assessment of Tabular Data Synthesis.</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -4878,14 +4878,14 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Mandy Lanyon</t>
+          <t>Elijah Robert Bouma-Sims</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Lorrie Faith Cranor</t>
+          <t>Mandy Lanyon</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -4920,7 +4920,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Kai Kaufman</t>
+          <t>Lorrie Faith Cranor</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -4939,22 +4939,22 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>CCS-'We just did not have that on the embedded system': Insights and Challenges for Securing Microcontroller Systems from the Embedded CTF Competitions.</t>
+          <t>CCS-'Is this a scam?': The Nature and Quality of Reddit Discussion about Scams.</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Worcester Polytechnic Institute</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Md. Armanuzzaman</t>
+          <t>Kai Kaufman</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -4966,18 +4966,18 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>Worcester Polytechnic Institute</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Xi Tan 0002</t>
+          <t>Md. Armanuzzaman</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -4989,18 +4989,18 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>University of Colorado Colorado Springs</t>
+          <t>Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Katherine Jesse</t>
+          <t>Xi Tan 0002</t>
         </is>
       </c>
       <c r="B200" t="n">
@@ -5012,18 +5012,18 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Worcester Polytechnic Institute</t>
+          <t>University of Colorado Colorado Springs</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Robert J. Walls</t>
+          <t>Katherine Jesse</t>
         </is>
       </c>
       <c r="B201" t="n">
@@ -5035,7 +5035,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Ziming Zhao 0001</t>
+          <t>Robert J. Walls</t>
         </is>
       </c>
       <c r="B202" t="n">
@@ -5058,18 +5058,18 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>Worcester Polytechnic Institute</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Joshua Wiedemeier</t>
+          <t>Ziming Zhao 0001</t>
         </is>
       </c>
       <c r="B203" t="n">
@@ -5077,22 +5077,22 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>CCS-Walking The Last Mile: Studying Decompiler Output Correction in Practice.</t>
+          <t>CCS-'We just did not have that on the embedded system': Insights and Challenges for Securing Microcontroller Systems from the Embedded CTF Competitions.</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>The University of Texas at Dallas</t>
+          <t>Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Simon Klancher</t>
+          <t>Joshua Wiedemeier</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Joel Flores</t>
+          <t>Simon Klancher</t>
         </is>
       </c>
       <c r="B205" t="n">
@@ -5127,7 +5127,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Max Zheng</t>
+          <t>Joel Flores</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -5150,7 +5150,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Jaehyun Park</t>
+          <t>Max Zheng</t>
         </is>
       </c>
       <c r="B207" t="n">
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Kangkook Jee</t>
+          <t>Jaehyun Park</t>
         </is>
       </c>
       <c r="B208" t="n">
@@ -5196,7 +5196,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Yunze Zhao</t>
+          <t>Kangkook Jee</t>
         </is>
       </c>
       <c r="B209" t="n">
@@ -5215,22 +5215,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>CCS-A Qualitative Analysis of Fuzzer Usability and Challenges.</t>
+          <t>CCS-Walking The Last Mile: Studying Decompiler Output Correction in Practice.</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>University of Maryland, College Park</t>
+          <t>The University of Texas at Dallas</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Wentao Guo 0005</t>
+          <t>Yunze Zhao</t>
         </is>
       </c>
       <c r="B210" t="n">
@@ -5242,7 +5242,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Harrison Goldstein</t>
+          <t>Wentao Guo 0005</t>
         </is>
       </c>
       <c r="B211" t="n">
@@ -5265,7 +5265,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Michelle L. Mazurek</t>
+          <t>Harrison Goldstein</t>
         </is>
       </c>
       <c r="B212" t="n">
@@ -5288,7 +5288,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
@@ -5299,7 +5299,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Lorenzo Neil</t>
+          <t>Michelle L. Mazurek</t>
         </is>
       </c>
       <c r="B213" t="n">
@@ -5307,22 +5307,22 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>CCS-It Should Be Easy but... New Users' Experiences and Challenges with Secret Management Tools.</t>
+          <t>CCS-A Qualitative Analysis of Fuzzer Usability and Challenges.</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>North Carolina State University</t>
+          <t>University of Maryland, College Park</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Laurie A. Williams</t>
+          <t>Lorenzo Neil</t>
         </is>
       </c>
       <c r="B214" t="n">
@@ -5334,7 +5334,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Bradley Reaves</t>
+          <t>Laurie A. Williams</t>
         </is>
       </c>
       <c r="B215" t="n">
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Michael Torres</t>
+          <t>Bradley Reaves</t>
         </is>
       </c>
       <c r="B216" t="n">
@@ -5376,22 +5376,22 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>CCS-ExfilState: Automated Discovery of Timer-Free Cache Side Channels on ARM CPUs.</t>
+          <t>CCS-It Should Be Easy but... New Users' Experiences and Challenges with Secret Management Tools.</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>North Carolina State University</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Daniel Moghimi</t>
+          <t>Michael Torres</t>
         </is>
       </c>
       <c r="B217" t="n">
@@ -5403,7 +5403,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Flavien Solt</t>
+          <t>Daniel Moghimi</t>
         </is>
       </c>
       <c r="B218" t="n">
@@ -5422,22 +5422,22 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>CCS-MileSan: Detecting Exploitable Microarchitectural Leakage via Differential Hardware-Software Taint Tracking.</t>
+          <t>CCS-ExfilState: Automated Discovery of Timer-Free Cache Side Channels on ARM CPUs.</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Berkeley College; University of California, Berkeley</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Rui Zhao</t>
+          <t>Flavien Solt</t>
         </is>
       </c>
       <c r="B219" t="n">
@@ -5445,22 +5445,22 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>CCS-Rethinking Tamper-Evident Logging: A High-Performance, Co-Designed Auditing System.</t>
+          <t>CCS-MileSan: Detecting Exploitable Microarchitectural Leakage via Differential Hardware-Software Taint Tracking.</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>Berkeley College; University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Muhammad Shoaib</t>
+          <t>Rui Zhao</t>
         </is>
       </c>
       <c r="B220" t="n">
@@ -5472,7 +5472,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Wajih Ul Hassan</t>
+          <t>Muhammad Shoaib</t>
         </is>
       </c>
       <c r="B221" t="n">
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Moritz Schloegel</t>
+          <t>Wajih Ul Hassan</t>
         </is>
       </c>
       <c r="B222" t="n">
@@ -5514,22 +5514,22 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>CCS-Empirical Security Analysis of Software-based Fault Isolation through Controlled Fault Injection.</t>
+          <t>CCS-Rethinking Tamper-Evident Logging: A High-Performance, Co-Designed Auditing System.</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>University of Virginia</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Shixuan Zhao 0002</t>
+          <t>Moritz Schloegel</t>
         </is>
       </c>
       <c r="B223" t="n">
@@ -5537,22 +5537,22 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>CCS-GPU Travelling: Efficient Confidential Collaborative Training with TEE-Enabled GPUs.</t>
+          <t>CCS-Empirical Security Analysis of Software-based Fault Isolation through Controlled Fault Injection.</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>The Ohio State University</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Zhongshu Gu</t>
+          <t>Shixuan Zhao 0002</t>
         </is>
       </c>
       <c r="B224" t="n">
@@ -5564,18 +5564,18 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>IBM (United States)</t>
+          <t>The Ohio State University</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Salman Ahmed 0001</t>
+          <t>Zhongshu Gu</t>
         </is>
       </c>
       <c r="B225" t="n">
@@ -5587,7 +5587,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Enriquillo Valdez</t>
+          <t>Salman Ahmed 0001</t>
         </is>
       </c>
       <c r="B226" t="n">
@@ -5610,7 +5610,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Hani Jamjoom</t>
+          <t>Enriquillo Valdez</t>
         </is>
       </c>
       <c r="B227" t="n">
@@ -5633,7 +5633,7 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Zhiqiang Lin 0001</t>
+          <t>Hani Jamjoom</t>
         </is>
       </c>
       <c r="B228" t="n">
@@ -5656,18 +5656,18 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>The Ohio State University</t>
+          <t>IBM (United States)</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Tahina Ramananandro</t>
+          <t>Zhiqiang Lin 0001</t>
         </is>
       </c>
       <c r="B229" t="n">
@@ -5675,22 +5675,22 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>CCS-Secure Parsing and Serializing with Separation Logic Applied to CBOR, CDDL, and COSE.</t>
+          <t>CCS-GPU Travelling: Efficient Confidential Collaborative Training with TEE-Enabled GPUs.</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Microsoft (United States)</t>
+          <t>The Ohio State University</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Gabriel Ebner</t>
+          <t>Tahina Ramananandro</t>
         </is>
       </c>
       <c r="B230" t="n">
@@ -5702,7 +5702,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Guido Martínez</t>
+          <t>Gabriel Ebner</t>
         </is>
       </c>
       <c r="B231" t="n">
@@ -5725,7 +5725,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Nikhil Swamy</t>
+          <t>Guido Martínez</t>
         </is>
       </c>
       <c r="B232" t="n">
@@ -5748,7 +5748,7 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Sizhe Chen</t>
+          <t>Nikhil Swamy</t>
         </is>
       </c>
       <c r="B233" t="n">
@@ -5767,22 +5767,22 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>CCS-SecAlign: Defending Against Prompt Injection with Preference Optimization.</t>
+          <t>CCS-Secure Parsing and Serializing with Separation Logic Applied to CBOR, CDDL, and COSE.</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Berkeley College; University of California, Berkeley</t>
+          <t>Microsoft (United States)</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Stanley Wu</t>
+          <t>Sizhe Chen</t>
         </is>
       </c>
       <c r="B234" t="n">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>CCS-On the Feasibility of Poisoning Text-to-Image AI Models via Adversarial Mislabeling.</t>
+          <t>CCS-SecAlign: Defending Against Prompt Injection with Preference Optimization.</t>
         </is>
       </c>
       <c r="D234" t="n">
@@ -5798,14 +5798,14 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>University of Illinois Chicago; University of Chicago</t>
+          <t>Berkeley College; University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Ronik Bhaskar</t>
+          <t>Stanley Wu</t>
         </is>
       </c>
       <c r="B235" t="n">
@@ -5817,7 +5817,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Anna Yoo Jeong Ha</t>
+          <t>Ronik Bhaskar</t>
         </is>
       </c>
       <c r="B236" t="n">
@@ -5840,7 +5840,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Shawn Shan</t>
+          <t>Anna Yoo Jeong Ha</t>
         </is>
       </c>
       <c r="B237" t="n">
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Haitao Zheng 0001</t>
+          <t>Shawn Shan</t>
         </is>
       </c>
       <c r="B238" t="n">
@@ -5886,7 +5886,7 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Ben Y. Zhao</t>
+          <t>Haitao Zheng 0001</t>
         </is>
       </c>
       <c r="B239" t="n">
@@ -5909,7 +5909,7 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Zeyu Liu 0004</t>
+          <t>Ben Y. Zhao</t>
         </is>
       </c>
       <c r="B240" t="n">
@@ -5928,22 +5928,22 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>CCS-IND-CPA-D of Relaxed Functional Bootstrapping: A New Attack, A General Fix, and A Stronger Model.</t>
+          <t>CCS-On the Feasibility of Poisoning Text-to-Image AI Models via Adversarial Mislabeling.</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Yale University</t>
+          <t>University of Illinois Chicago; University of Chicago</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Yunhao Wang 0002</t>
+          <t>Zeyu Liu 0004</t>
         </is>
       </c>
       <c r="B241" t="n">
@@ -5955,7 +5955,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Ben Fisch</t>
+          <t>Yunhao Wang 0002</t>
         </is>
       </c>
       <c r="B242" t="n">
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Chris Tsoukaladelis</t>
+          <t>Ben Fisch</t>
         </is>
       </c>
       <c r="B243" t="n">
@@ -5997,22 +5997,22 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>CCS-The Power to Never Be Wrong: Evasions and Anachronistic Attacks Against Web Archives.</t>
+          <t>CCS-IND-CPA-D of Relaxed Functional Bootstrapping: A New Attack, A General Fix, and A Stronger Model.</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Stony Brook University</t>
+          <t>Yale University</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Nick Nikiforakis</t>
+          <t>Chris Tsoukaladelis</t>
         </is>
       </c>
       <c r="B244" t="n">
@@ -6024,7 +6024,7 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Johnny So</t>
+          <t>Nick Nikiforakis</t>
         </is>
       </c>
       <c r="B245" t="n">
@@ -6043,11 +6043,11 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>CCS-What Gets Measured Gets Managed: Mitigating Supply Chain Attacks with a Link Integrity Management System.</t>
+          <t>CCS-The Power to Never Be Wrong: Evasions and Anachronistic Attacks Against Web Archives.</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Michael Ferdman</t>
+          <t>Johnny So</t>
         </is>
       </c>
       <c r="B246" t="n">
@@ -6070,7 +6070,7 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Nick Nikiforakis</t>
+          <t>Michael Ferdman</t>
         </is>
       </c>
       <c r="B247" t="n">
@@ -6093,7 +6093,7 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Karthik Ramakrishnan</t>
+          <t>Nick Nikiforakis</t>
         </is>
       </c>
       <c r="B248" t="n">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>CCS-Head(er)s Up! Detecting Security Header Inconsistencies in Browsers.</t>
+          <t>CCS-What Gets Measured Gets Managed: Mitigating Supply Chain Attacks with a Link Integrity Management System.</t>
         </is>
       </c>
       <c r="D248" t="n">
@@ -6120,14 +6120,14 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>Stony Brook University</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Bo Li 0026</t>
+          <t>Karthik Ramakrishnan</t>
         </is>
       </c>
       <c r="B249" t="n">
@@ -6135,22 +6135,22 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>CCS-What's Pulling the Strings? Evaluating Integrity and Attribution in AI Training and Inference through Concept Shift.</t>
+          <t>CCS-Head(er)s Up! Detecting Security Header Inconsistencies in Browsers.</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Caleb Manicke</t>
+          <t>Bo Li 0026</t>
         </is>
       </c>
       <c r="B250" t="n">
@@ -6158,22 +6158,22 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>CCS-Busting the Paper Ballot: Voting Meets Adversarial Machine Learning.</t>
+          <t>CCS-What's Pulling the Strings? Evaluating Integrity and Attribution in AI Training and Inference through Concept Shift.</t>
         </is>
       </c>
       <c r="D250" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>University of Connecticut</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Ethan Rathbun</t>
+          <t>Caleb Manicke</t>
         </is>
       </c>
       <c r="B251" t="n">
@@ -6185,18 +6185,18 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>University of Connecticut</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Aayushi Verma</t>
+          <t>Ethan Rathbun</t>
         </is>
       </c>
       <c r="B252" t="n">
@@ -6208,18 +6208,18 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>University of Connecticut</t>
+          <t>Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Sohaib Ahmad</t>
+          <t>Aayushi Verma</t>
         </is>
       </c>
       <c r="B253" t="n">
@@ -6231,7 +6231,7 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
@@ -6242,7 +6242,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Nicholas Stamatakis</t>
+          <t>Sohaib Ahmad</t>
         </is>
       </c>
       <c r="B254" t="n">
@@ -6254,18 +6254,18 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Stony Brook University</t>
+          <t>University of Connecticut</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Laurent Michel</t>
+          <t>Nicholas Stamatakis</t>
         </is>
       </c>
       <c r="B255" t="n">
@@ -6277,18 +6277,18 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>University of Connecticut</t>
+          <t>Stony Brook University</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Benjamin Fuller 0001</t>
+          <t>Laurent Michel</t>
         </is>
       </c>
       <c r="B256" t="n">
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Lu Xian</t>
+          <t>Benjamin Fuller 0001</t>
         </is>
       </c>
       <c r="B257" t="n">
@@ -6319,22 +6319,22 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>CCS-Layered, Overlapping, and Inconsistent: A Large-Scale Analysis of the Multiple Privacy Policies and Controls of U.S. Banks.</t>
+          <t>CCS-Busting the Paper Ballot: Voting Meets Adversarial Machine Learning.</t>
         </is>
       </c>
       <c r="D257" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>University of Michigan</t>
+          <t>University of Connecticut</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Lauren Lee</t>
+          <t>Lu Xian</t>
         </is>
       </c>
       <c r="B258" t="n">
@@ -6346,7 +6346,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
@@ -6357,7 +6357,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Meera Kumar</t>
+          <t>Lauren Lee</t>
         </is>
       </c>
       <c r="B259" t="n">
@@ -6369,7 +6369,7 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Yichen Zhang</t>
+          <t>Meera Kumar</t>
         </is>
       </c>
       <c r="B260" t="n">
@@ -6392,18 +6392,18 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>University of Wisconsin–Madison</t>
+          <t>University of Michigan</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Florian Schaub</t>
+          <t>Yichen Zhang</t>
         </is>
       </c>
       <c r="B261" t="n">
@@ -6415,18 +6415,18 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>University of Michigan</t>
+          <t>University of Wisconsin–Madison</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Doowon Kim</t>
+          <t>Florian Schaub</t>
         </is>
       </c>
       <c r="B262" t="n">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>CCS-A Decade-long Landscape of Advanced Persistent Threats: Longitudinal Analysis and Global Trends.</t>
+          <t>CCS-Layered, Overlapping, and Inconsistent: A Large-Scale Analysis of the Multiple Privacy Policies and Controls of U.S. Banks.</t>
         </is>
       </c>
       <c r="D262" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>University of Tennessee at Knoxville</t>
+          <t>University of Michigan</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Nick Nikiforakis</t>
+          <t>Doowon Kim</t>
         </is>
       </c>
       <c r="B263" t="n">
@@ -6461,18 +6461,18 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Stony Brook University</t>
+          <t>University of Tennessee at Knoxville</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Emiliano De Cristofaro</t>
+          <t>Nick Nikiforakis</t>
         </is>
       </c>
       <c r="B264" t="n">
@@ -6480,7 +6480,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>CCS-The Importance of Being Discrete: Measuring the Impact of Discretization in End-to-End Differentially Private Synthetic Data.</t>
+          <t>CCS-A Decade-long Landscape of Advanced Persistent Threats: Longitudinal Analysis and Global Trends.</t>
         </is>
       </c>
       <c r="D264" t="n">
@@ -6488,14 +6488,14 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>University of California, Riverside</t>
+          <t>Stony Brook University</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Yi Zhu 0012</t>
+          <t>Emiliano De Cristofaro</t>
         </is>
       </c>
       <c r="B265" t="n">
@@ -6503,22 +6503,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>CCS-Asymmetry Vulnerability and Physical Attacks on Online Map Construction for Autonomous Driving.</t>
+          <t>CCS-The Importance of Being Discrete: Measuring the Impact of Discretization in End-to-End Differentially Private Synthetic Data.</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Wayne State University</t>
+          <t>University of California, Riverside</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Alan Wang 0004</t>
+          <t>Yi Zhu 0012</t>
         </is>
       </c>
       <c r="B266" t="n">
@@ -6526,22 +6526,22 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>CCS-Pixnapping: Bringing Pixel Stealing out of the Stone Age.</t>
+          <t>CCS-Asymmetry Vulnerability and Physical Attacks on Online Map Construction for Autonomous Driving.</t>
         </is>
       </c>
       <c r="D266" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>University of California, Berkeley</t>
+          <t>Wayne State University</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Pranav Gopalkrishnan</t>
+          <t>Alan Wang 0004</t>
         </is>
       </c>
       <c r="B267" t="n">
@@ -6553,18 +6553,18 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>University of Washington</t>
+          <t>University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Yingchen Wang</t>
+          <t>Pranav Gopalkrishnan</t>
         </is>
       </c>
       <c r="B268" t="n">
@@ -6576,18 +6576,18 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>University of California, Berkeley</t>
+          <t>University of Washington</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Christopher W. Fletcher</t>
+          <t>Yingchen Wang</t>
         </is>
       </c>
       <c r="B269" t="n">
@@ -6599,7 +6599,7 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E269" t="inlineStr">
         <is>
@@ -6610,7 +6610,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Hovav Shacham</t>
+          <t>Christopher W. Fletcher</t>
         </is>
       </c>
       <c r="B270" t="n">
@@ -6622,18 +6622,18 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>University of California San Diego</t>
+          <t>University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>David Kohlbrenner</t>
+          <t>Hovav Shacham</t>
         </is>
       </c>
       <c r="B271" t="n">
@@ -6645,18 +6645,18 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>University of Washington</t>
+          <t>University of California San Diego</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Riccardo Paccagnella</t>
+          <t>David Kohlbrenner</t>
         </is>
       </c>
       <c r="B272" t="n">
@@ -6668,18 +6668,18 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>University of Washington</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Long Huang</t>
+          <t>Riccardo Paccagnella</t>
         </is>
       </c>
       <c r="B273" t="n">
@@ -6687,22 +6687,22 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>CCS-HW-Spy: Handwriting Inference by Tracing Pen-Tail Movements.</t>
+          <t>CCS-Pixnapping: Bringing Pixel Stealing out of the Stone Age.</t>
         </is>
       </c>
       <c r="D273" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>University of Michigan</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Kang G. Shin</t>
+          <t>Long Huang</t>
         </is>
       </c>
       <c r="B274" t="n">
@@ -6714,7 +6714,7 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Hadleigh Schwartz</t>
+          <t>Kang G. Shin</t>
         </is>
       </c>
       <c r="B275" t="n">
@@ -6733,22 +6733,22 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>CCS-Combating Falsification of Speech Videos with Live Optical Signatures.</t>
+          <t>CCS-HW-Spy: Handwriting Inference by Tracing Pen-Tail Movements.</t>
         </is>
       </c>
       <c r="D275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Columbia University</t>
+          <t>University of Michigan</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Xiaofeng Yan</t>
+          <t>Hadleigh Schwartz</t>
         </is>
       </c>
       <c r="B276" t="n">
@@ -6760,7 +6760,7 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E276" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Charles J. Carver</t>
+          <t>Xiaofeng Yan</t>
         </is>
       </c>
       <c r="B277" t="n">
@@ -6783,18 +6783,18 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Massachusetts Institute of Technology</t>
+          <t>Columbia University</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Xia Zhou</t>
+          <t>Charles J. Carver</t>
         </is>
       </c>
       <c r="B278" t="n">
@@ -6806,18 +6806,18 @@
         </is>
       </c>
       <c r="D278" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Columbia University</t>
+          <t>Massachusetts Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Jinwen Wang</t>
+          <t>Xia Zhou</t>
         </is>
       </c>
       <c r="B279" t="n">
@@ -6825,22 +6825,22 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>CCS-ConTest: Taming the Cyber-physical Input Space in Fuzz Testing with Control Theory.</t>
+          <t>CCS-Combating Falsification of Speech Videos with Live Optical Signatures.</t>
         </is>
       </c>
       <c r="D279" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>The University of Texas at Dallas</t>
+          <t>Columbia University</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Andreas D. Kellas</t>
+          <t>Jinwen Wang</t>
         </is>
       </c>
       <c r="B280" t="n">
@@ -6848,7 +6848,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>CCS-PickleBall: Secure Deserialization of Pickle-based Machine Learning Models.</t>
+          <t>CCS-ConTest: Taming the Cyber-physical Input Space in Fuzz Testing with Control Theory.</t>
         </is>
       </c>
       <c r="D280" t="n">
@@ -6856,14 +6856,14 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Columbia University</t>
+          <t>The University of Texas at Dallas</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Neophytos Christou</t>
+          <t>Andreas D. Kellas</t>
         </is>
       </c>
       <c r="B281" t="n">
@@ -6875,18 +6875,18 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Brown University</t>
+          <t>Columbia University</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Wenxin Jiang 0001</t>
+          <t>Neophytos Christou</t>
         </is>
       </c>
       <c r="B282" t="n">
@@ -6898,18 +6898,18 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>Brown University</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Penghui Li 0001</t>
+          <t>Wenxin Jiang 0001</t>
         </is>
       </c>
       <c r="B283" t="n">
@@ -6921,18 +6921,18 @@
         </is>
       </c>
       <c r="D283" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Columbia University</t>
+          <t>Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Laurent Simon</t>
+          <t>Penghui Li 0001</t>
         </is>
       </c>
       <c r="B284" t="n">
@@ -6944,18 +6944,18 @@
         </is>
       </c>
       <c r="D284" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>Columbia University</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Vasileios P. Kemerlis</t>
+          <t>Laurent Simon</t>
         </is>
       </c>
       <c r="B285" t="n">
@@ -6967,18 +6967,18 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Brown University</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>James C. Davis 0001</t>
+          <t>Vasileios P. Kemerlis</t>
         </is>
       </c>
       <c r="B286" t="n">
@@ -6990,18 +6990,18 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>Brown University</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Junfeng Yang</t>
+          <t>James C. Davis 0001</t>
         </is>
       </c>
       <c r="B287" t="n">
@@ -7013,18 +7013,18 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Columbia University</t>
+          <t>Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Kangjie Lu</t>
+          <t>Junfeng Yang</t>
         </is>
       </c>
       <c r="B288" t="n">
@@ -7032,22 +7032,22 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>CCS-Dangers Behind Access Control: Understanding and Exploiting Implicit Permissions in Kubernetes.</t>
+          <t>CCS-PickleBall: Secure Deserialization of Pickle-based Machine Learning Models.</t>
         </is>
       </c>
       <c r="D288" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>University of Minnesota</t>
+          <t>Columbia University</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Tim Roughgarden</t>
+          <t>Nanzi Yang</t>
         </is>
       </c>
       <c r="B289" t="n">
@@ -7055,22 +7055,22 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>CCS-Accountable Liveness.</t>
+          <t>CCS-Dangers Behind Access Control: Understanding and Exploiting Implicit Permissions in Kubernetes.</t>
         </is>
       </c>
       <c r="D289" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Columbia University</t>
+          <t>University of Minnesota; Xidian University</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Shu-Jie Cao</t>
+          <t>Kangjie Lu</t>
         </is>
       </c>
       <c r="B290" t="n">
@@ -7078,22 +7078,22 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>CCS-How to Beat Nakamoto in the Race.</t>
+          <t>CCS-Dangers Behind Access Control: Understanding and Exploiting Implicit Permissions in Kubernetes.</t>
         </is>
       </c>
       <c r="D290" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Northwestern University</t>
+          <t>University of Minnesota</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Dongning Guo</t>
+          <t>Tim Roughgarden</t>
         </is>
       </c>
       <c r="B291" t="n">
@@ -7101,22 +7101,22 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>CCS-How to Beat Nakamoto in the Race.</t>
+          <t>CCS-Accountable Liveness.</t>
         </is>
       </c>
       <c r="D291" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Northwestern University</t>
+          <t>Columbia University</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Xinwen Fu</t>
+          <t>Shu-Jie Cao</t>
         </is>
       </c>
       <c r="B292" t="n">
@@ -7124,22 +7124,22 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>CCS-Time Tells All: Deanonymization of Blockchain RPC Users with Zero Transaction Fee.</t>
+          <t>CCS-How to Beat Nakamoto in the Race.</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>University of Massachusetts Lowell</t>
+          <t>Northwestern University</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Mahimna Kelkar</t>
+          <t>Dongning Guo</t>
         </is>
       </c>
       <c r="B293" t="n">
@@ -7147,22 +7147,22 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>CCS-Breaking Omertà: On Threshold Cryptography, Smart Collusion, and Whistleblowing.</t>
+          <t>CCS-How to Beat Nakamoto in the Race.</t>
         </is>
       </c>
       <c r="D293" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>Northwestern University</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Aadityan Ganesh</t>
+          <t>Xinwen Fu</t>
         </is>
       </c>
       <c r="B294" t="n">
@@ -7170,22 +7170,22 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>CCS-Breaking Omertà: On Threshold Cryptography, Smart Collusion, and Whistleblowing.</t>
+          <t>CCS-Time Tells All: Deanonymization of Blockchain RPC Users with Zero Transaction Fee.</t>
         </is>
       </c>
       <c r="D294" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Princeton University</t>
+          <t>University of Massachusetts Lowell</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Aditi Partap</t>
+          <t>Mahimna Kelkar</t>
         </is>
       </c>
       <c r="B295" t="n">
@@ -7197,18 +7197,18 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>Cornell University</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Joseph Bonneau</t>
+          <t>Aadityan Ganesh</t>
         </is>
       </c>
       <c r="B296" t="n">
@@ -7220,18 +7220,18 @@
         </is>
       </c>
       <c r="D296" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>New York University</t>
+          <t>Princeton University</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>S. Matthew Weinberg</t>
+          <t>Aditi Partap</t>
         </is>
       </c>
       <c r="B297" t="n">
@@ -7243,18 +7243,18 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Princeton University</t>
+          <t>Stanford University</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Tianfang Zhang</t>
+          <t>Joseph Bonneau</t>
         </is>
       </c>
       <c r="B298" t="n">
@@ -7262,22 +7262,22 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>CCS-Harnessing Vital Sign Vibration Harmonics for Effortless and Inbuilt XR User Authentication.</t>
+          <t>CCS-Breaking Omertà: On Threshold Cryptography, Smart Collusion, and Whistleblowing.</t>
         </is>
       </c>
       <c r="D298" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Rutgers, The State University of New Jersey</t>
+          <t>New York University</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Md Mojibur Rahman Redoy Akanda</t>
+          <t>S. Matthew Weinberg</t>
         </is>
       </c>
       <c r="B299" t="n">
@@ -7285,22 +7285,22 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>CCS-Harnessing Vital Sign Vibration Harmonics for Effortless and Inbuilt XR User Authentication.</t>
+          <t>CCS-Breaking Omertà: On Threshold Cryptography, Smart Collusion, and Whistleblowing.</t>
         </is>
       </c>
       <c r="D299" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>Princeton University</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Ahmed Tanvir Mahdad</t>
+          <t>Tianfang Zhang</t>
         </is>
       </c>
       <c r="B300" t="n">
@@ -7312,18 +7312,18 @@
         </is>
       </c>
       <c r="D300" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>Rutgers, The State University of New Jersey</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Nitesh Saxena</t>
+          <t>Md Mojibur Rahman Redoy Akanda</t>
         </is>
       </c>
       <c r="B301" t="n">
@@ -7335,7 +7335,7 @@
         </is>
       </c>
       <c r="D301" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Yingying Chen 0001</t>
+          <t>Ahmed Tanvir Mahdad</t>
         </is>
       </c>
       <c r="B302" t="n">
@@ -7358,18 +7358,18 @@
         </is>
       </c>
       <c r="D302" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Rutgers, The State University of New Jersey</t>
+          <t>Texas A&amp;M University</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Andrew Gan</t>
+          <t>Nitesh Saxena</t>
         </is>
       </c>
       <c r="B303" t="n">
@@ -7377,22 +7377,22 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>CCS-Sentry: Authenticating Machine Learning Artifacts on the Fly.</t>
+          <t>CCS-Harnessing Vital Sign Vibration Harmonics for Effortless and Inbuilt XR User Authentication.</t>
         </is>
       </c>
       <c r="D303" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>Texas A&amp;M University</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Zahra Ghodsi</t>
+          <t>Yingying Chen 0001</t>
         </is>
       </c>
       <c r="B304" t="n">
@@ -7400,22 +7400,22 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>CCS-Sentry: Authenticating Machine Learning Artifacts on the Fly.</t>
+          <t>CCS-Harnessing Vital Sign Vibration Harmonics for Effortless and Inbuilt XR User Authentication.</t>
         </is>
       </c>
       <c r="D304" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>Rutgers, The State University of New Jersey</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Kun Sun 0001</t>
+          <t>Andrew Gan</t>
         </is>
       </c>
       <c r="B305" t="n">
@@ -7423,22 +7423,22 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>CCS-Training Robust Classifiers for Classifying Encrypted Traffic under Dynamic Network Conditions.</t>
+          <t>CCS-Sentry: Authenticating Machine Learning Artifacts on the Fly.</t>
         </is>
       </c>
       <c r="D305" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>George Mason University</t>
+          <t>Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Amey Shukla</t>
+          <t>Zahra Ghodsi</t>
         </is>
       </c>
       <c r="B306" t="n">
@@ -7446,22 +7446,22 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>CCS-Fuzzy Extractors are Practical: Cryptographic Strength Key Derivation from the Iris.</t>
+          <t>CCS-Sentry: Authenticating Machine Learning Artifacts on the Fly.</t>
         </is>
       </c>
       <c r="D306" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>University of Connecticut</t>
+          <t>Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Benjamin Fuller 0001</t>
+          <t>Kun Sun 0001</t>
         </is>
       </c>
       <c r="B307" t="n">
@@ -7469,22 +7469,22 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>CCS-Fuzzy Extractors are Practical: Cryptographic Strength Key Derivation from the Iris.</t>
+          <t>CCS-Training Robust Classifiers for Classifying Encrypted Traffic under Dynamic Network Conditions.</t>
         </is>
       </c>
       <c r="D307" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>University of Connecticut</t>
+          <t>George Mason University</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Sohaib Ahmad</t>
+          <t>Amey Shukla</t>
         </is>
       </c>
       <c r="B308" t="n">
@@ -7496,7 +7496,7 @@
         </is>
       </c>
       <c r="D308" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E308" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Caleb Manicke</t>
+          <t>Benjamin Fuller 0001</t>
         </is>
       </c>
       <c r="B309" t="n">
@@ -7519,7 +7519,7 @@
         </is>
       </c>
       <c r="D309" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Alexander Russell</t>
+          <t>Sohaib Ahmad</t>
         </is>
       </c>
       <c r="B310" t="n">
@@ -7542,7 +7542,7 @@
         </is>
       </c>
       <c r="D310" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
@@ -7553,7 +7553,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Alexandra Boldyreva</t>
+          <t>Caleb Manicke</t>
         </is>
       </c>
       <c r="B311" t="n">
@@ -7561,22 +7561,22 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>CCS-May the Force</t>
+          <t>CCS-Fuzzy Extractors are Practical: Cryptographic Strength Key Derivation from the Iris.</t>
         </is>
       </c>
       <c r="D311" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>University of Connecticut</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Deep Inder Mohan</t>
+          <t>Alexander Russell</t>
         </is>
       </c>
       <c r="B312" t="n">
@@ -7584,22 +7584,22 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>CCS-May the Force</t>
+          <t>CCS-Fuzzy Extractors are Practical: Cryptographic Strength Key Derivation from the Iris.</t>
         </is>
       </c>
       <c r="D312" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>University of Connecticut</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Yunqing Sun</t>
+          <t>Alexandra Boldyreva</t>
         </is>
       </c>
       <c r="B313" t="n">
@@ -7607,7 +7607,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>CCS-Committed Vector Oblivious Linear Evaluation and Its Applications.</t>
+          <t>CCS-May the Force</t>
         </is>
       </c>
       <c r="D313" t="n">
@@ -7615,14 +7615,14 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Northwestern University</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Hanlin Liu</t>
+          <t>Deep Inder Mohan</t>
         </is>
       </c>
       <c r="B314" t="n">
@@ -7630,7 +7630,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>CCS-Committed Vector Oblivious Linear Evaluation and Its Applications.</t>
+          <t>CCS-May the Force</t>
         </is>
       </c>
       <c r="D314" t="n">
@@ -7638,14 +7638,14 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Northwestern University</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Xiao Wang 0012</t>
+          <t>Yunqing Sun</t>
         </is>
       </c>
       <c r="B315" t="n">
@@ -7657,7 +7657,7 @@
         </is>
       </c>
       <c r="D315" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E315" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Chenkai Weng</t>
+          <t>Hanlin Liu</t>
         </is>
       </c>
       <c r="B316" t="n">
@@ -7680,18 +7680,18 @@
         </is>
       </c>
       <c r="D316" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Northwestern University</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Zachary Ratliff</t>
+          <t>Xiao Wang 0012</t>
         </is>
       </c>
       <c r="B317" t="n">
@@ -7699,22 +7699,22 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>CCS-Timing Attacks on Differential Privacy are Practical.</t>
+          <t>CCS-Committed Vector Oblivious Linear Evaluation and Its Applications.</t>
         </is>
       </c>
       <c r="D317" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Harvard University Press</t>
+          <t>Northwestern University</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Nicolás Berrios</t>
+          <t>Chenkai Weng</t>
         </is>
       </c>
       <c r="B318" t="n">
@@ -7722,22 +7722,22 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>CCS-Timing Attacks on Differential Privacy are Practical.</t>
+          <t>CCS-Committed Vector Oblivious Linear Evaluation and Its Applications.</t>
         </is>
       </c>
       <c r="D318" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>James Mickens</t>
+          <t>Zachary Ratliff</t>
         </is>
       </c>
       <c r="B319" t="n">
@@ -7749,7 +7749,7 @@
         </is>
       </c>
       <c r="D319" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E319" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Pouneh Nikkhah Bahrami</t>
+          <t>Nicolás Berrios</t>
         </is>
       </c>
       <c r="B320" t="n">
@@ -7768,22 +7768,22 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>CCS-Byte by Byte: Unmasking Browser Fingerprinting at the Function Level using V8 Bytecode Transformers.</t>
+          <t>CCS-Timing Attacks on Differential Privacy are Practical.</t>
         </is>
       </c>
       <c r="D320" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>University of California, Davis</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Dylan Cutler</t>
+          <t>James Mickens</t>
         </is>
       </c>
       <c r="B321" t="n">
@@ -7791,22 +7791,22 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>CCS-Byte by Byte: Unmasking Browser Fingerprinting at the Function Level using V8 Bytecode Transformers.</t>
+          <t>CCS-Timing Attacks on Differential Privacy are Practical.</t>
         </is>
       </c>
       <c r="D321" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>Harvard University Press</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Igor Bilogrevic</t>
+          <t>Pouneh Nikkhah Bahrami</t>
         </is>
       </c>
       <c r="B322" t="n">
@@ -7818,18 +7818,18 @@
         </is>
       </c>
       <c r="D322" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Google (Switzerland)</t>
+          <t>University of California, Davis</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Xiaoqian Jiang</t>
+          <t>Dylan Cutler</t>
         </is>
       </c>
       <c r="B323" t="n">
@@ -7837,22 +7837,22 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>CCS-THOR: Secure Transformer Inference with Homomorphic Encryption.</t>
+          <t>CCS-Byte by Byte: Unmasking Browser Fingerprinting at the Function Level using V8 Bytecode Transformers.</t>
         </is>
       </c>
       <c r="D323" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>The University of Texas Health Science Center at Houston</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Aniket Kate</t>
+          <t>Igor Bilogrevic</t>
         </is>
       </c>
       <c r="B324" t="n">
@@ -7860,7 +7860,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>CCS-Optimistic, Signature-Free Reliable Broadcast and Its Applications.</t>
+          <t>CCS-Byte by Byte: Unmasking Browser Fingerprinting at the Function Level using V8 Bytecode Transformers.</t>
         </is>
       </c>
       <c r="D324" t="n">
@@ -7868,14 +7868,14 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>Google (Switzerland)</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Giuliano Losa</t>
+          <t>Xiaoqian Jiang</t>
         </is>
       </c>
       <c r="B325" t="n">
@@ -7883,22 +7883,22 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>CCS-Optimistic, Signature-Free Reliable Broadcast and Its Applications.</t>
+          <t>CCS-THOR: Secure Transformer Inference with Homomorphic Encryption.</t>
         </is>
       </c>
       <c r="D325" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Stellar Solutions (United States)</t>
+          <t>The University of Texas Health Science Center at Houston</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Kartik Nayak</t>
+          <t>Aniket Kate</t>
         </is>
       </c>
       <c r="B326" t="n">
@@ -7910,18 +7910,18 @@
         </is>
       </c>
       <c r="D326" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Duke University</t>
+          <t>Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Yi Zhu 0012</t>
+          <t>Giuliano Losa</t>
         </is>
       </c>
       <c r="B327" t="n">
@@ -7929,22 +7929,22 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>CCS-Towards Real-Time Defense against Object-Based LiDAR Attacks in Autonomous Driving.</t>
+          <t>CCS-Optimistic, Signature-Free Reliable Broadcast and Its Applications.</t>
         </is>
       </c>
       <c r="D327" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Wayne State University</t>
+          <t>Stellar Solutions (United States)</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Haining Wang 0001</t>
+          <t>Kartik Nayak</t>
         </is>
       </c>
       <c r="B328" t="n">
@@ -7952,22 +7952,22 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>CCS-Dynamic Vulnerability Patching for Heterogeneous Embedded Systems Using Stack Frame Reconstruction.</t>
+          <t>CCS-Optimistic, Signature-Free Reliable Broadcast and Its Applications.</t>
         </is>
       </c>
       <c r="D328" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>Duke University</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Minghao Lin</t>
+          <t>Yi Zhu 0012</t>
         </is>
       </c>
       <c r="B329" t="n">
@@ -7975,22 +7975,22 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>CCS-Chekhov's Gun: Uncovering Hidden Risks in macOS Application-Sandboxed PID-Domain Services.</t>
+          <t>CCS-Towards Real-Time Defense against Object-Based LiDAR Attacks in Autonomous Driving.</t>
         </is>
       </c>
       <c r="D329" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>Wayne State University</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Elisa Bertino</t>
+          <t>Haining Wang 0001</t>
         </is>
       </c>
       <c r="B330" t="n">
@@ -7998,22 +7998,22 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>CCS-Training with Only 1.0 ‰ Samples: Malicious Traffic Detection via Cross-Modality Feature Fusion.</t>
+          <t>CCS-Dynamic Vulnerability Patching for Heterogeneous Embedded Systems Using Stack Frame Reconstruction.</t>
         </is>
       </c>
       <c r="D330" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Diwen Xue</t>
+          <t>Minghao Lin</t>
         </is>
       </c>
       <c r="B331" t="n">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>CCS-Fingerprinting Deep Packet Inspection Devices by their Ambiguities.</t>
+          <t>CCS-Chekhov's Gun: Uncovering Hidden Risks in macOS Application-Sandboxed PID-Domain Services.</t>
         </is>
       </c>
       <c r="D331" t="n">
@@ -8029,14 +8029,14 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>University of Michigan</t>
+          <t>University of Southern California</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Armin Huremagic</t>
+          <t>Elisa Bertino</t>
         </is>
       </c>
       <c r="B332" t="n">
@@ -8044,22 +8044,22 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>CCS-Fingerprinting Deep Packet Inspection Devices by their Ambiguities.</t>
+          <t>CCS-Training with Only 1.0 ‰ Samples: Malicious Traffic Detection via Cross-Modality Feature Fusion.</t>
         </is>
       </c>
       <c r="D332" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>University of Michigan</t>
+          <t>Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Wayne Wang</t>
+          <t>Diwen Xue</t>
         </is>
       </c>
       <c r="B333" t="n">
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="D333" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E333" t="inlineStr">
         <is>
@@ -8082,7 +8082,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Ram Sundara Raman</t>
+          <t>Armin Huremagic</t>
         </is>
       </c>
       <c r="B334" t="n">
@@ -8094,18 +8094,18 @@
         </is>
       </c>
       <c r="D334" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>University of California, Santa Cruz</t>
+          <t>University of Michigan</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Roya Ensafi</t>
+          <t>Wayne Wang</t>
         </is>
       </c>
       <c r="B335" t="n">
@@ -8117,7 +8117,7 @@
         </is>
       </c>
       <c r="D335" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E335" t="inlineStr">
         <is>
@@ -8128,7 +8128,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Wenyi Morty Zhang</t>
+          <t>Ram Sundara Raman</t>
         </is>
       </c>
       <c r="B336" t="n">
@@ -8136,22 +8136,22 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>CCS-Don't Look Up: There Are Sensitive Internal Links in the Clear on GEO Satellites.</t>
+          <t>CCS-Fingerprinting Deep Packet Inspection Devices by their Ambiguities.</t>
         </is>
       </c>
       <c r="D336" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>University of California San Diego</t>
+          <t>University of California, Santa Cruz</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Annie Dai</t>
+          <t>Roya Ensafi</t>
         </is>
       </c>
       <c r="B337" t="n">
@@ -8159,22 +8159,22 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>CCS-Don't Look Up: There Are Sensitive Internal Links in the Clear on GEO Satellites.</t>
+          <t>CCS-Fingerprinting Deep Packet Inspection Devices by their Ambiguities.</t>
         </is>
       </c>
       <c r="D337" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>University of Maryland, College Park</t>
+          <t>University of Michigan</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Keegan Ryan</t>
+          <t>Wenyi Morty Zhang</t>
         </is>
       </c>
       <c r="B338" t="n">
@@ -8186,7 +8186,7 @@
         </is>
       </c>
       <c r="D338" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E338" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Dave Levin</t>
+          <t>Annie Dai</t>
         </is>
       </c>
       <c r="B339" t="n">
@@ -8209,7 +8209,7 @@
         </is>
       </c>
       <c r="D339" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E339" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Nadia Heninger</t>
+          <t>Keegan Ryan</t>
         </is>
       </c>
       <c r="B340" t="n">
@@ -8232,7 +8232,7 @@
         </is>
       </c>
       <c r="D340" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E340" t="inlineStr">
         <is>
@@ -8243,7 +8243,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Aaron Schulman</t>
+          <t>Dave Levin</t>
         </is>
       </c>
       <c r="B341" t="n">
@@ -8255,18 +8255,18 @@
         </is>
       </c>
       <c r="D341" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>University of California San Diego</t>
+          <t>University of Maryland, College Park</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Zeyu Liu 0004</t>
+          <t>Nadia Heninger</t>
         </is>
       </c>
       <c r="B342" t="n">
@@ -8274,22 +8274,22 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>CCS-Phalanx: An FHE-Friendly SNARK for Verifiable Computation on Encrypted Data.</t>
+          <t>CCS-Don't Look Up: There Are Sensitive Internal Links in the Clear on GEO Satellites.</t>
         </is>
       </c>
       <c r="D342" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Yale University</t>
+          <t>University of California San Diego</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Ben Fisch</t>
+          <t>Aaron Schulman</t>
         </is>
       </c>
       <c r="B343" t="n">
@@ -8297,7 +8297,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>CCS-Phalanx: An FHE-Friendly SNARK for Verifiable Computation on Encrypted Data.</t>
+          <t>CCS-Don't Look Up: There Are Sensitive Internal Links in the Clear on GEO Satellites.</t>
         </is>
       </c>
       <c r="D343" t="n">
@@ -8305,14 +8305,14 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Yale University</t>
+          <t>University of California San Diego</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Xiaozhong Liu 0001</t>
+          <t>Zeyu Liu 0004</t>
         </is>
       </c>
       <c r="B344" t="n">
@@ -8320,22 +8320,22 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>CCS-FlippedRAG: Black-Box Opinion Manipulation Adversarial Attacks to Retrieval-Augmented Generation Models.</t>
+          <t>CCS-Phalanx: An FHE-Friendly SNARK for Verifiable Computation on Encrypted Data.</t>
         </is>
       </c>
       <c r="D344" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Worcester Polytechnic Institute</t>
+          <t>Yale University</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Chen Gong 0005</t>
+          <t>Ben Fisch</t>
         </is>
       </c>
       <c r="B345" t="n">
@@ -8343,22 +8343,22 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>CCS-DPImageBench: A Unified Benchmark for Differentially Private Image Synthesis.</t>
+          <t>CCS-Phalanx: An FHE-Friendly SNARK for Verifiable Computation on Encrypted Data.</t>
         </is>
       </c>
       <c r="D345" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>Yale University</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Kecen Li</t>
+          <t>Xiaozhong Liu 0001</t>
         </is>
       </c>
       <c r="B346" t="n">
@@ -8366,22 +8366,22 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>CCS-DPImageBench: A Unified Benchmark for Differentially Private Image Synthesis.</t>
+          <t>CCS-FlippedRAG: Black-Box Opinion Manipulation Adversarial Attacks to Retrieval-Augmented Generation Models.</t>
         </is>
       </c>
       <c r="D346" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>Worcester Polytechnic Institute</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Zinan Lin 0001</t>
+          <t>Chen Gong 0005</t>
         </is>
       </c>
       <c r="B347" t="n">
@@ -8393,18 +8393,18 @@
         </is>
       </c>
       <c r="D347" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Microsoft (United States)</t>
+          <t>University of Virginia</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Tianhao Wang 0001</t>
+          <t>Kecen Li</t>
         </is>
       </c>
       <c r="B348" t="n">
@@ -8416,7 +8416,7 @@
         </is>
       </c>
       <c r="D348" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E348" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Xiaolong Ma</t>
+          <t>Zinan Lin 0001</t>
         </is>
       </c>
       <c r="B349" t="n">
@@ -8435,22 +8435,22 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>CCS-What Lurks Within? Concept Auditing for Shared Diffusion Models at Scale.</t>
+          <t>CCS-DPImageBench: A Unified Benchmark for Differentially Private Image Synthesis.</t>
         </is>
       </c>
       <c r="D349" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>University of Arizona</t>
+          <t>Microsoft (United States)</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Hanshen Xiao</t>
+          <t>Tianhao Wang 0001</t>
         </is>
       </c>
       <c r="B350" t="n">
@@ -8458,22 +8458,22 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>CCS-One-Sided Bounded Noise: Theory, Optimization Algorithms and Applications.</t>
+          <t>CCS-DPImageBench: A Unified Benchmark for Differentially Private Image Synthesis.</t>
         </is>
       </c>
       <c r="D350" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>University of Virginia</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Elaine Shi</t>
+          <t>Xiaolong Ma</t>
         </is>
       </c>
       <c r="B351" t="n">
@@ -8481,22 +8481,22 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>CCS-One-Sided Bounded Noise: Theory, Optimization Algorithms and Applications.</t>
+          <t>CCS-What Lurks Within? Concept Auditing for Shared Diffusion Models at Scale.</t>
         </is>
       </c>
       <c r="D351" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>University of Arizona</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Srinivas Devadas</t>
+          <t>Hanshen Xiao</t>
         </is>
       </c>
       <c r="B352" t="n">
@@ -8508,18 +8508,18 @@
         </is>
       </c>
       <c r="D352" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Massachusetts Institute of Technology</t>
+          <t>Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Paschalis Bekos</t>
+          <t>Elaine Shi</t>
         </is>
       </c>
       <c r="B353" t="n">
@@ -8527,22 +8527,22 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>CCS-PIIxel Leaks: Passive Identification of Personally Identifiable Information Leakage through Meta Pixel.</t>
+          <t>CCS-One-Sided Bounded Noise: Theory, Optimization Algorithms and Applications.</t>
         </is>
       </c>
       <c r="D353" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Stony Brook University</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Michalis Polychronakis</t>
+          <t>Srinivas Devadas</t>
         </is>
       </c>
       <c r="B354" t="n">
@@ -8550,7 +8550,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>CCS-PIIxel Leaks: Passive Identification of Personally Identifiable Information Leakage through Meta Pixel.</t>
+          <t>CCS-One-Sided Bounded Noise: Theory, Optimization Algorithms and Applications.</t>
         </is>
       </c>
       <c r="D354" t="n">
@@ -8558,14 +8558,14 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Stony Brook University</t>
+          <t>Massachusetts Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>David Inyangson</t>
+          <t>Paschalis Bekos</t>
         </is>
       </c>
       <c r="B355" t="n">
@@ -8573,7 +8573,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>CCS-Amigo: Secure Group Mesh Messaging in Realistic Protest Settings.</t>
+          <t>CCS-PIIxel Leaks: Passive Identification of Personally Identifiable Information Leakage through Meta Pixel.</t>
         </is>
       </c>
       <c r="D355" t="n">
@@ -8581,14 +8581,14 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Johns Hopkins University</t>
+          <t>Stony Brook University</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Sarah Radway</t>
+          <t>Michalis Polychronakis</t>
         </is>
       </c>
       <c r="B356" t="n">
@@ -8596,22 +8596,22 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>CCS-Amigo: Secure Group Mesh Messaging in Realistic Protest Settings.</t>
+          <t>CCS-PIIxel Leaks: Passive Identification of Personally Identifiable Information Leakage through Meta Pixel.</t>
         </is>
       </c>
       <c r="D356" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Harvard University Press</t>
+          <t>Stony Brook University</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Tushar M. Jois</t>
+          <t>David Inyangson</t>
         </is>
       </c>
       <c r="B357" t="n">
@@ -8623,18 +8623,18 @@
         </is>
       </c>
       <c r="D357" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>City College of New York</t>
+          <t>Johns Hopkins University</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Nelly Fazio</t>
+          <t>Sarah Radway</t>
         </is>
       </c>
       <c r="B358" t="n">
@@ -8646,18 +8646,18 @@
         </is>
       </c>
       <c r="D358" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>City College of New York</t>
+          <t>Harvard University Press</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>James Mickens</t>
+          <t>Tushar M. Jois</t>
         </is>
       </c>
       <c r="B359" t="n">
@@ -8669,18 +8669,18 @@
         </is>
       </c>
       <c r="D359" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Harvard University Press</t>
+          <t>City College of New York</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Somiya Chhillar</t>
+          <t>Nelly Fazio</t>
         </is>
       </c>
       <c r="B360" t="n">
@@ -8688,22 +8688,22 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>CCS-Exposing Privacy Risks in Anonymizing Clinical Data: Combinatorial Refinement Attacks on</t>
+          <t>CCS-Amigo: Secure Group Mesh Messaging in Realistic Protest Settings.</t>
         </is>
       </c>
       <c r="D360" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>George Mason University</t>
+          <t>City College of New York</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Rebecca E. Sutter</t>
+          <t>James Mickens</t>
         </is>
       </c>
       <c r="B361" t="n">
@@ -8711,22 +8711,22 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>CCS-Exposing Privacy Risks in Anonymizing Clinical Data: Combinatorial Refinement Attacks on</t>
+          <t>CCS-Amigo: Secure Group Mesh Messaging in Realistic Protest Settings.</t>
         </is>
       </c>
       <c r="D361" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>George Mason University</t>
+          <t>Harvard University Press</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Evgenios M. Kornaropoulos</t>
+          <t>Somiya Chhillar</t>
         </is>
       </c>
       <c r="B362" t="n">
@@ -8738,7 +8738,7 @@
         </is>
       </c>
       <c r="D362" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E362" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Julia Nonnenkamp</t>
+          <t>Rebecca E. Sutter</t>
         </is>
       </c>
       <c r="B363" t="n">
@@ -8757,22 +8757,22 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>CCS-Hidden in Plain Bytes: Investigating Interpersonal Account Compromise with Data Exports.</t>
+          <t>CCS-Exposing Privacy Risks in Anonymizing Clinical Data: Combinatorial Refinement Attacks on</t>
         </is>
       </c>
       <c r="D363" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>University of Wisconsin–Madison</t>
+          <t>George Mason University</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Naman Gupta</t>
+          <t>Evgenios M. Kornaropoulos</t>
         </is>
       </c>
       <c r="B364" t="n">
@@ -8780,22 +8780,22 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>CCS-Hidden in Plain Bytes: Investigating Interpersonal Account Compromise with Data Exports.</t>
+          <t>CCS-Exposing Privacy Risks in Anonymizing Clinical Data: Combinatorial Refinement Attacks on</t>
         </is>
       </c>
       <c r="D364" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>University of Wisconsin–Madison</t>
+          <t>George Mason University</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Abhimanyu Dev Gupta</t>
+          <t>Julia Nonnenkamp</t>
         </is>
       </c>
       <c r="B365" t="n">
@@ -8807,7 +8807,7 @@
         </is>
       </c>
       <c r="D365" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E365" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Rahul Chatterjee 0001</t>
+          <t>Naman Gupta</t>
         </is>
       </c>
       <c r="B366" t="n">
@@ -8830,7 +8830,7 @@
         </is>
       </c>
       <c r="D366" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E366" t="inlineStr">
         <is>
@@ -8841,7 +8841,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Jan Tolsdorf</t>
+          <t>Abhimanyu Dev Gupta</t>
         </is>
       </c>
       <c r="B367" t="n">
@@ -8849,22 +8849,22 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>CCS-Phishing Susceptibility and the (In-)Effectiveness of Common Anti-Phishing Interventions in a Large University Hospital.</t>
+          <t>CCS-Hidden in Plain Bytes: Investigating Interpersonal Account Compromise with Data Exports.</t>
         </is>
       </c>
       <c r="D367" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>George Washington University</t>
+          <t>University of Wisconsin–Madison</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Yaman Yu</t>
+          <t>Rahul Chatterjee 0001</t>
         </is>
       </c>
       <c r="B368" t="n">
@@ -8872,22 +8872,22 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>CCS-YouthSafe: A Youth-Centric Safety Benchmark and Safeguard Model for Large Language Models.</t>
+          <t>CCS-Hidden in Plain Bytes: Investigating Interpersonal Account Compromise with Data Exports.</t>
         </is>
       </c>
       <c r="D368" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>University of Wisconsin–Madison</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Yiren Liu</t>
+          <t>Jan Tolsdorf</t>
         </is>
       </c>
       <c r="B369" t="n">
@@ -8895,22 +8895,22 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>CCS-YouthSafe: A Youth-Centric Safety Benchmark and Safeguard Model for Large Language Models.</t>
+          <t>CCS-Phishing Susceptibility and the (In-)Effectiveness of Common Anti-Phishing Interventions in a Large University Hospital.</t>
         </is>
       </c>
       <c r="D369" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>George Washington University</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Yuqi Zhang</t>
+          <t>Yaman Yu</t>
         </is>
       </c>
       <c r="B370" t="n">
@@ -8922,7 +8922,7 @@
         </is>
       </c>
       <c r="D370" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E370" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Yun Huang 0003</t>
+          <t>Yiren Liu</t>
         </is>
       </c>
       <c r="B371" t="n">
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="D371" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E371" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Yang Wang 0005</t>
+          <t>Yuqi Zhang</t>
         </is>
       </c>
       <c r="B372" t="n">
@@ -8968,7 +8968,7 @@
         </is>
       </c>
       <c r="D372" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E372" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Milad Nasr</t>
+          <t>Yun Huang 0003</t>
         </is>
       </c>
       <c r="B373" t="n">
@@ -8987,22 +8987,22 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>CCS-Evaluating the Robustness of a Production Malware Detection System to Transferable Adversarial Attacks.</t>
+          <t>CCS-YouthSafe: A Youth-Centric Safety Benchmark and Safeguard Model for Large Language Models.</t>
         </is>
       </c>
       <c r="D373" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Yanick Fratantonio</t>
+          <t>Yang Wang 0005</t>
         </is>
       </c>
       <c r="B374" t="n">
@@ -9010,22 +9010,22 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>CCS-Evaluating the Robustness of a Production Malware Detection System to Transferable Adversarial Attacks.</t>
+          <t>CCS-YouthSafe: A Youth-Centric Safety Benchmark and Safeguard Model for Large Language Models.</t>
         </is>
       </c>
       <c r="D374" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>Google (Switzerland)</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Luca Invernizzi</t>
+          <t>Milad Nasr</t>
         </is>
       </c>
       <c r="B375" t="n">
@@ -9037,18 +9037,18 @@
         </is>
       </c>
       <c r="D375" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>Google (Switzerland)</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Ange Albertini</t>
+          <t>Yanick Fratantonio</t>
         </is>
       </c>
       <c r="B376" t="n">
@@ -9060,7 +9060,7 @@
         </is>
       </c>
       <c r="D376" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E376" t="inlineStr">
         <is>
@@ -9071,7 +9071,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Alex Petit-Bianco</t>
+          <t>Luca Invernizzi</t>
         </is>
       </c>
       <c r="B377" t="n">
@@ -9083,18 +9083,18 @@
         </is>
       </c>
       <c r="D377" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>Google (Switzerland)</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Andreas Terzis</t>
+          <t>Ange Albertini</t>
         </is>
       </c>
       <c r="B378" t="n">
@@ -9106,18 +9106,18 @@
         </is>
       </c>
       <c r="D378" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>Google (Switzerland)</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Kurt Thomas</t>
+          <t>Alex Petit-Bianco</t>
         </is>
       </c>
       <c r="B379" t="n">
@@ -9129,7 +9129,7 @@
         </is>
       </c>
       <c r="D379" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E379" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Elie Bursztein</t>
+          <t>Andreas Terzis</t>
         </is>
       </c>
       <c r="B380" t="n">
@@ -9152,7 +9152,7 @@
         </is>
       </c>
       <c r="D380" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E380" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Nicholas Carlini</t>
+          <t>Kurt Thomas</t>
         </is>
       </c>
       <c r="B381" t="n">
@@ -9175,7 +9175,7 @@
         </is>
       </c>
       <c r="D381" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E381" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Harsh Chaudhari</t>
+          <t>Elie Bursztein</t>
         </is>
       </c>
       <c r="B382" t="n">
@@ -9194,22 +9194,22 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>CCS-Cascading Adversarial Bias from Injection to Distillation in Language Models.</t>
+          <t>CCS-Evaluating the Robustness of a Production Malware Detection System to Transferable Adversarial Attacks.</t>
         </is>
       </c>
       <c r="D382" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Jamie Hayes</t>
+          <t>Nicholas Carlini</t>
         </is>
       </c>
       <c r="B383" t="n">
@@ -9217,22 +9217,22 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>CCS-Cascading Adversarial Bias from Injection to Distillation in Language Models.</t>
+          <t>CCS-Evaluating the Robustness of a Production Malware Detection System to Transferable Adversarial Attacks.</t>
         </is>
       </c>
       <c r="D383" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>Google (United Kingdom)</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Matthew Jagielski</t>
+          <t>Harsh Chaudhari</t>
         </is>
       </c>
       <c r="B384" t="n">
@@ -9244,18 +9244,18 @@
         </is>
       </c>
       <c r="D384" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Ilia Shumailov</t>
+          <t>Jamie Hayes</t>
         </is>
       </c>
       <c r="B385" t="n">
@@ -9267,18 +9267,18 @@
         </is>
       </c>
       <c r="D385" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>Google DeepMind (United Kingdom); Google (United Kingdom)</t>
+          <t>Google (United Kingdom)</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Milad Nasr</t>
+          <t>Matthew Jagielski</t>
         </is>
       </c>
       <c r="B386" t="n">
@@ -9290,7 +9290,7 @@
         </is>
       </c>
       <c r="D386" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E386" t="inlineStr">
         <is>
@@ -9301,7 +9301,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Alina Oprea</t>
+          <t>Ilia Shumailov</t>
         </is>
       </c>
       <c r="B387" t="n">
@@ -9313,18 +9313,18 @@
         </is>
       </c>
       <c r="D387" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>Google DeepMind (United Kingdom); Google (United Kingdom)</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Changjiang Li</t>
+          <t>Milad Nasr</t>
         </is>
       </c>
       <c r="B388" t="n">
@@ -9332,22 +9332,22 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>CCS-You Can't Steal Nothing: Mitigating Prompt Leakages in LLMs via System Vectors.</t>
+          <t>CCS-Cascading Adversarial Bias from Injection to Distillation in Language Models.</t>
         </is>
       </c>
       <c r="D388" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>Palo Alto Networks (United States)</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Ting Wang 0006</t>
+          <t>Alina Oprea</t>
         </is>
       </c>
       <c r="B389" t="n">
@@ -9355,22 +9355,22 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>CCS-You Can't Steal Nothing: Mitigating Prompt Leakages in LLMs via System Vectors.</t>
+          <t>CCS-Cascading Adversarial Bias from Injection to Distillation in Language Models.</t>
         </is>
       </c>
       <c r="D389" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>Stony Brook University</t>
+          <t>Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Sangho Lee 0001</t>
+          <t>Changjiang Li</t>
         </is>
       </c>
       <c r="B390" t="n">
@@ -9378,22 +9378,22 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>CCS-IOValve: Leakage-Free I/O Sandbox for Large-Scale Untrusted Data Processing.</t>
+          <t>CCS-You Can't Steal Nothing: Mitigating Prompt Leakages in LLMs via System Vectors.</t>
         </is>
       </c>
       <c r="D390" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>Microsoft (United States)</t>
+          <t>Palo Alto Networks (United States)</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Jules Drean</t>
+          <t>Ting Wang 0006</t>
         </is>
       </c>
       <c r="B391" t="n">
@@ -9401,22 +9401,22 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>CCS-IOValve: Leakage-Free I/O Sandbox for Large-Scale Untrusted Data Processing.</t>
+          <t>CCS-You Can't Steal Nothing: Mitigating Prompt Leakages in LLMs via System Vectors.</t>
         </is>
       </c>
       <c r="D391" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>Massachusetts Institute of Technology</t>
+          <t>Stony Brook University</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Yue Tan</t>
+          <t>Sangho Lee 0001</t>
         </is>
       </c>
       <c r="B392" t="n">
@@ -9428,18 +9428,18 @@
         </is>
       </c>
       <c r="D392" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>Princeton University</t>
+          <t>Microsoft (United States)</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Marcus Peinado</t>
+          <t>Jules Drean</t>
         </is>
       </c>
       <c r="B393" t="n">
@@ -9451,18 +9451,18 @@
         </is>
       </c>
       <c r="D393" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>Microsoft (United States)</t>
+          <t>Massachusetts Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Moritz Schloegel</t>
+          <t>Yue Tan</t>
         </is>
       </c>
       <c r="B394" t="n">
@@ -9470,22 +9470,22 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>CCS-Protocol-Aware Firmware Rehosting for Effective Fuzzing of Embedded Network Stacks.</t>
+          <t>CCS-IOValve: Leakage-Free I/O Sandbox for Large-Scale Untrusted Data Processing.</t>
         </is>
       </c>
       <c r="D394" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Princeton University</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Brian Johannesmeyer</t>
+          <t>Marcus Peinado</t>
         </is>
       </c>
       <c r="B395" t="n">
@@ -9493,22 +9493,22 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>CCS-Dynamic Detection of Vulnerable DMA Race Conditions.</t>
+          <t>CCS-IOValve: Leakage-Free I/O Sandbox for Large-Scale Untrusted Data Processing.</t>
         </is>
       </c>
       <c r="D395" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>Qualcomm (United States)</t>
+          <t>Microsoft (United States)</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Kun Sun 0001</t>
+          <t>Moritz Schloegel</t>
         </is>
       </c>
       <c r="B396" t="n">
@@ -9516,22 +9516,22 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>CCS-Off-Path TCP Exploits: PMTUD Breaks TCP Connection Isolation in IP Address Sharing Scenarios.</t>
+          <t>CCS-Protocol-Aware Firmware Rehosting for Effective Fuzzing of Embedded Network Stacks.</t>
         </is>
       </c>
       <c r="D396" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>George Mason University</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Lucien K. L. Ng</t>
+          <t>Brian Johannesmeyer</t>
         </is>
       </c>
       <c r="B397" t="n">
@@ -9539,7 +9539,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>CCS-Toss: Garbled PIR from Table-Only Stacking.</t>
+          <t>CCS-Dynamic Detection of Vulnerable DMA Race Conditions.</t>
         </is>
       </c>
       <c r="D397" t="n">
@@ -9547,14 +9547,14 @@
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>Qualcomm (United States)</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Vladimir Kolesnikov</t>
+          <t>Kun Sun 0001</t>
         </is>
       </c>
       <c r="B398" t="n">
@@ -9562,22 +9562,22 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>CCS-Toss: Garbled PIR from Table-Only Stacking.</t>
+          <t>CCS-Off-Path TCP Exploits: PMTUD Breaks TCP Connection Isolation in IP Address Sharing Scenarios.</t>
         </is>
       </c>
       <c r="D398" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>George Mason University</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Xiao Wang 0012</t>
+          <t>Lucien K. L. Ng</t>
         </is>
       </c>
       <c r="B399" t="n">
@@ -9585,22 +9585,22 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>CCS-Secure Noise Sampling for Differentially Private Collaborative Learning.</t>
+          <t>CCS-Toss: Garbled PIR from Table-Only Stacking.</t>
         </is>
       </c>
       <c r="D399" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>Northwestern University</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Somesh Jha</t>
+          <t>Vladimir Kolesnikov</t>
         </is>
       </c>
       <c r="B400" t="n">
@@ -9608,22 +9608,22 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>CCS-Secure Noise Sampling for Differentially Private Collaborative Learning.</t>
+          <t>CCS-Toss: Garbled PIR from Table-Only Stacking.</t>
         </is>
       </c>
       <c r="D400" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Lucas Piske</t>
+          <t>Xiao Wang 0012</t>
         </is>
       </c>
       <c r="B401" t="n">
@@ -9631,22 +9631,22 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>CCS-Distance-Aware OT with Application to Fuzzy PSI.</t>
+          <t>CCS-Secure Noise Sampling for Differentially Private Collaborative Learning.</t>
         </is>
       </c>
       <c r="D401" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Northwestern University</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Jaspal Singh</t>
+          <t>Somesh Jha</t>
         </is>
       </c>
       <c r="B402" t="n">
@@ -9654,22 +9654,22 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>CCS-Distance-Aware OT with Application to Fuzzy PSI.</t>
+          <t>CCS-Secure Noise Sampling for Differentially Private Collaborative Learning.</t>
         </is>
       </c>
       <c r="D402" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology; Purdue University West Lafayette</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Ni Trieu</t>
+          <t>Lucas Piske</t>
         </is>
       </c>
       <c r="B403" t="n">
@@ -9681,7 +9681,7 @@
         </is>
       </c>
       <c r="D403" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E403" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Vladimir Kolesnikov</t>
+          <t>Jaspal Singh</t>
         </is>
       </c>
       <c r="B404" t="n">
@@ -9704,18 +9704,18 @@
         </is>
       </c>
       <c r="D404" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>Georgia Institute of Technology; Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Vassilis Zikas</t>
+          <t>Ni Trieu</t>
         </is>
       </c>
       <c r="B405" t="n">
@@ -9727,18 +9727,18 @@
         </is>
       </c>
       <c r="D405" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Wei-Kai Lin</t>
+          <t>Vladimir Kolesnikov</t>
         </is>
       </c>
       <c r="B406" t="n">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>CCS-MegaBlocks: Breaking the Logarithmic I/O-Overhead Barrier for Oblivious RAM.</t>
+          <t>CCS-Distance-Aware OT with Application to Fuzzy PSI.</t>
         </is>
       </c>
       <c r="D406" t="n">
@@ -9754,14 +9754,14 @@
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Sara Rampazzi</t>
+          <t>Vassilis Zikas</t>
         </is>
       </c>
       <c r="B407" t="n">
@@ -9769,22 +9769,22 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>CCS-Poster: Recapture Detection Using Disparity Map Obtained from Dual-Pixel Image Sensors.</t>
+          <t>CCS-Distance-Aware OT with Application to Fuzzy PSI.</t>
         </is>
       </c>
       <c r="D407" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>University of Florida</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Dominik Wermke</t>
+          <t>Wei-Kai Lin</t>
         </is>
       </c>
       <c r="B408" t="n">
@@ -9792,22 +9792,22 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>CCS-Poster: Computer Security Researchers' Experiences with Vulnerability Disclosures.</t>
+          <t>CCS-MegaBlocks: Breaking the Logarithmic I/O-Overhead Barrier for Oblivious RAM.</t>
         </is>
       </c>
       <c r="D408" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>North Carolina State University</t>
+          <t>University of Virginia</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Yan Chen 0004</t>
+          <t>Sara Rampazzi</t>
         </is>
       </c>
       <c r="B409" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>CCS-Poster: Obfuscating Function Activity States to Enhance Privacy in Serverless Applications.</t>
+          <t>CCS-Poster: Recapture Detection Using Disparity Map Obtained from Dual-Pixel Image Sensors.</t>
         </is>
       </c>
       <c r="D409" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>Northwestern University</t>
+          <t>University of Florida</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Kostas Kryptos Chalkias</t>
+          <t>Dominik Wermke</t>
         </is>
       </c>
       <c r="B410" t="n">
@@ -9838,22 +9838,22 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>CCS-Poster: Post-Quantum Readiness in EdDSA Chains.</t>
+          <t>CCS-Poster: Computer Security Researchers' Experiences with Vulnerability Disclosures.</t>
         </is>
       </c>
       <c r="D410" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>Hewlett-Packard (United States)</t>
+          <t>North Carolina State University</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Tashi Stirewalt</t>
+          <t>Yan Chen 0004</t>
         </is>
       </c>
       <c r="B411" t="n">
@@ -9861,22 +9861,22 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>CCS-Poster: Adversarial Habituation Attack: A Psychological Extension and Re-framing of Boiling Frog Attack.</t>
+          <t>CCS-Poster: Obfuscating Function Activity States to Enhance Privacy in Serverless Applications.</t>
         </is>
       </c>
       <c r="D411" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>Washington State University</t>
+          <t>Northwestern University</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Assefaw Hadish Gebremedhin</t>
+          <t>Kostas Kryptos Chalkias</t>
         </is>
       </c>
       <c r="B412" t="n">
@@ -9884,22 +9884,22 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>CCS-Poster: Adversarial Habituation Attack: A Psychological Extension and Re-framing of Boiling Frog Attack.</t>
+          <t>CCS-Poster: Post-Quantum Readiness in EdDSA Chains.</t>
         </is>
       </c>
       <c r="D412" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>Washington State University</t>
+          <t>Hewlett-Packard (United States)</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Gefei Tan</t>
+          <t>Tashi Stirewalt</t>
         </is>
       </c>
       <c r="B413" t="n">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>CCS-Scalable Cryptography for Trustworthy Machine Learning in the LLM Era.</t>
+          <t>CCS-Poster: Adversarial Habituation Attack: A Psychological Extension and Re-framing of Boiling Frog Attack.</t>
         </is>
       </c>
       <c r="D413" t="n">
@@ -9915,14 +9915,14 @@
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>Northwestern University</t>
+          <t>Washington State University</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Daniel Olszewski</t>
+          <t>Assefaw Hadish Gebremedhin</t>
         </is>
       </c>
       <c r="B414" t="n">
@@ -9930,22 +9930,22 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>CCS-On Defining Reproducible Outcomes for the Computer Security Community.</t>
+          <t>CCS-Poster: Adversarial Habituation Attack: A Psychological Extension and Re-framing of Boiling Frog Attack.</t>
         </is>
       </c>
       <c r="D414" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>University of Florida</t>
+          <t>Washington State University</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>F. Betül Durak</t>
+          <t>Gefei Tan</t>
         </is>
       </c>
       <c r="B415" t="n">
@@ -9953,7 +9953,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>CCS-ACM CCS Young Scholars Development Program.</t>
+          <t>CCS-Scalable Cryptography for Trustworthy Machine Learning in the LLM Era.</t>
         </is>
       </c>
       <c r="D415" t="n">
@@ -9961,14 +9961,14 @@
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>Microsoft (United States)</t>
+          <t>Northwestern University</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Fengjun Li</t>
+          <t>Daniel Olszewski</t>
         </is>
       </c>
       <c r="B416" t="n">
@@ -9976,22 +9976,22 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>CCS-ACM CCS Young Scholars Development Program.</t>
+          <t>CCS-On Defining Reproducible Outcomes for the Computer Security Community.</t>
         </is>
       </c>
       <c r="D416" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>University of Kansas</t>
+          <t>University of Florida</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Sophie Stephenson</t>
+          <t>F. Betül Durak</t>
         </is>
       </c>
       <c r="B417" t="n">
@@ -10003,18 +10003,18 @@
         </is>
       </c>
       <c r="D417" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>University of Wisconsin–Madison</t>
+          <t>Microsoft (United States)</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Ruoxi Jia 0001</t>
+          <t>Fengjun Li</t>
         </is>
       </c>
       <c r="B418" t="n">
@@ -10022,22 +10022,22 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>CCS-AISec '25: 18th ACM Workshop on Artificial Intelligence and Security.</t>
+          <t>CCS-ACM CCS Young Scholars Development Program.</t>
         </is>
       </c>
       <c r="D418" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>University of Kansas</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Kassem Fawaz</t>
+          <t>Sophie Stephenson</t>
         </is>
       </c>
       <c r="B419" t="n">
@@ -10045,11 +10045,11 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>CCS-CPSIoTSec'25: The 7th Joint Workshop on CPS &amp; IoT Security and Privacy.</t>
+          <t>CCS-ACM CCS Young Scholars Development Program.</t>
         </is>
       </c>
       <c r="D419" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E419" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Jinoh Kim</t>
+          <t>Ruoxi Jia 0001</t>
         </is>
       </c>
       <c r="B420" t="n">
@@ -10068,22 +10068,22 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>CCS-WATCH '25: First Workshop on Analytics, Telemetry, and Cybersecurity for HPCC.</t>
+          <t>CCS-AISec '25: 18th ACM Workshop on Artificial Intelligence and Security.</t>
         </is>
       </c>
       <c r="D420" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>East Texas A&amp;M University</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Aditya Sirish A Yelgundhalli</t>
+          <t>Kassem Fawaz</t>
         </is>
       </c>
       <c r="B421" t="n">
@@ -10091,7 +10091,7 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>CCS-SCORED '25: Workshop on Software Supply Chain Offensive Research and Ecosystem Defenses.</t>
+          <t>CCS-CPSIoTSec'25: The 7th Joint Workshop on CPS &amp; IoT Security and Privacy.</t>
         </is>
       </c>
       <c r="D421" t="n">
@@ -10099,14 +10099,14 @@
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>Bloomberg (United States)</t>
+          <t>University of Wisconsin–Madison</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Dennis Roellke</t>
+          <t>Jinoh Kim</t>
         </is>
       </c>
       <c r="B422" t="n">
@@ -10114,22 +10114,22 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>CCS-SCORED '25: Workshop on Software Supply Chain Offensive Research and Ecosystem Defenses.</t>
+          <t>CCS-WATCH '25: First Workshop on Analytics, Telemetry, and Cybersecurity for HPCC.</t>
         </is>
       </c>
       <c r="D422" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>Bloomberg (United States)</t>
+          <t>East Texas A&amp;M University</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Drew Davidson</t>
+          <t>Aditya Sirish A Yelgundhalli</t>
         </is>
       </c>
       <c r="B423" t="n">
@@ -10141,18 +10141,18 @@
         </is>
       </c>
       <c r="D423" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>University of Kansas</t>
+          <t>Bloomberg (United States)</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Marcela S. Melara</t>
+          <t>Dennis Roellke</t>
         </is>
       </c>
       <c r="B424" t="n">
@@ -10164,18 +10164,18 @@
         </is>
       </c>
       <c r="D424" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>Intel (United States)</t>
+          <t>Bloomberg (United States)</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Santiago Torres-Arias</t>
+          <t>Drew Davidson</t>
         </is>
       </c>
       <c r="B425" t="n">
@@ -10187,18 +10187,18 @@
         </is>
       </c>
       <c r="D425" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>University of Kansas</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Sarah Evans</t>
+          <t>Marcela S. Melara</t>
         </is>
       </c>
       <c r="B426" t="n">
@@ -10210,18 +10210,18 @@
         </is>
       </c>
       <c r="D426" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>DELL (United States)</t>
+          <t>Intel (United States)</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Yuchen Zhang 0006</t>
+          <t>Santiago Torres-Arias</t>
         </is>
       </c>
       <c r="B427" t="n">
@@ -10233,18 +10233,18 @@
         </is>
       </c>
       <c r="D427" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>New York University</t>
+          <t>Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Tianshi Li 0001</t>
+          <t>Sarah Evans</t>
         </is>
       </c>
       <c r="B428" t="n">
@@ -10252,22 +10252,22 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>CCS-HAIPS '25: First ACM CCS Workshop on Human-Centered AI Privacy and Security.</t>
+          <t>CCS-SCORED '25: Workshop on Software Supply Chain Offensive Research and Ecosystem Defenses.</t>
         </is>
       </c>
       <c r="D428" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>University of Notre Dame; Northeastern University</t>
+          <t>DELL (United States)</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Toby Jia-Jun Li</t>
+          <t>Yuchen Zhang 0006</t>
         </is>
       </c>
       <c r="B429" t="n">
@@ -10275,22 +10275,22 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>CCS-HAIPS '25: First ACM CCS Workshop on Human-Centered AI Privacy and Security.</t>
+          <t>CCS-SCORED '25: Workshop on Software Supply Chain Offensive Research and Ecosystem Defenses.</t>
         </is>
       </c>
       <c r="D429" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>University of Notre Dame; Northeastern University</t>
+          <t>New York University</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Yaxing Yao</t>
+          <t>Tianshi Li 0001</t>
         </is>
       </c>
       <c r="B430" t="n">
@@ -10302,18 +10302,18 @@
         </is>
       </c>
       <c r="D430" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>Johns Hopkins University</t>
+          <t>University of Notre Dame; Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Sauvik Das</t>
+          <t>Toby Jia-Jun Li</t>
         </is>
       </c>
       <c r="B431" t="n">
@@ -10325,18 +10325,18 @@
         </is>
       </c>
       <c r="D431" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>University of Notre Dame; Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Zion Leonahenahe Basque</t>
+          <t>Yaxing Yao</t>
         </is>
       </c>
       <c r="B432" t="n">
@@ -10344,22 +10344,22 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>CCS-SURE '25: The 1st ACM Workshop on Software Understanding and Reverse Engineering.</t>
+          <t>CCS-HAIPS '25: First ACM CCS Workshop on Human-Centered AI Privacy and Security.</t>
         </is>
       </c>
       <c r="D432" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Johns Hopkins University</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Ati Priya Bajaj</t>
+          <t>Sauvik Das</t>
         </is>
       </c>
       <c r="B433" t="n">
@@ -10367,22 +10367,22 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>CCS-SURE '25: The 1st ACM Workshop on Software Understanding and Reverse Engineering.</t>
+          <t>CCS-HAIPS '25: First ACM CCS Workshop on Human-Centered AI Privacy and Security.</t>
         </is>
       </c>
       <c r="D433" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Muhammad Taqi Raza</t>
+          <t>Zion Leonahenahe Basque</t>
         </is>
       </c>
       <c r="B434" t="n">
@@ -10390,7 +10390,7 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>CCS-QSec '25: Workshop on Quantum Security and Privacy.</t>
+          <t>CCS-SURE '25: The 1st ACM Workshop on Software Understanding and Reverse Engineering.</t>
         </is>
       </c>
       <c r="D434" t="n">
@@ -10398,14 +10398,14 @@
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>University of Massachusetts Amherst</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Jakub Szefer</t>
+          <t>Ati Priya Bajaj</t>
         </is>
       </c>
       <c r="B435" t="n">
@@ -10413,7 +10413,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>CCS-QSec '25: Workshop on Quantum Security and Privacy.</t>
+          <t>CCS-SURE '25: The 1st ACM Workshop on Software Understanding and Reverse Engineering.</t>
         </is>
       </c>
       <c r="D435" t="n">
@@ -10421,14 +10421,14 @@
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>Northwestern University</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Cristina Nita-Rotaru</t>
+          <t>Muhammad Taqi Raza</t>
         </is>
       </c>
       <c r="B436" t="n">
@@ -10436,22 +10436,22 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>CCS-QRSec 2025: ACM CCS First Workshop on Quantum-Resistant Cryptography and Security.</t>
+          <t>CCS-QSec '25: Workshop on Quantum Security and Privacy.</t>
         </is>
       </c>
       <c r="D436" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>University of Massachusetts Amherst</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Mu Zhang 0001</t>
+          <t>Jakub Szefer</t>
         </is>
       </c>
       <c r="B437" t="n">
@@ -10459,7 +10459,7 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>CCS-RICSS'25: 3rd International Workshop on Re-design Industrial Control Systems with Security.</t>
+          <t>CCS-QSec '25: Workshop on Quantum Security and Privacy.</t>
         </is>
       </c>
       <c r="D437" t="n">
@@ -10467,14 +10467,14 @@
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>Northwestern University</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Bimal Viswanath</t>
+          <t>Cristina Nita-Rotaru</t>
         </is>
       </c>
       <c r="B438" t="n">
@@ -10482,22 +10482,22 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>CCS-3D-Sec '25: The 1st ACM Workshop on Deepfake, Deception, and Disinformation Security.</t>
+          <t>CCS-QRSec 2025: ACM CCS First Workshop on Quantum-Resistant Cryptography and Security.</t>
         </is>
       </c>
       <c r="D438" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Luyi Xing</t>
+          <t>Mu Zhang 0001</t>
         </is>
       </c>
       <c r="B439" t="n">
@@ -10505,22 +10505,22 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>CCS-SaTS '25: The 3rd ACM Workshop on Security and Privacy of AI-Empowered Mobile Super Apps.</t>
+          <t>CCS-RICSS'25: 3rd International Workshop on Re-design Industrial Control Systems with Security.</t>
         </is>
       </c>
       <c r="D439" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>University of Utah</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Yue Xiao 0007</t>
+          <t>Bimal Viswanath</t>
         </is>
       </c>
       <c r="B440" t="n">
@@ -10528,22 +10528,22 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>CCS-SaTS '25: The 3rd ACM Workshop on Security and Privacy of AI-Empowered Mobile Super Apps.</t>
+          <t>CCS-3D-Sec '25: The 1st ACM Workshop on Deepfake, Deception, and Disinformation Security.</t>
         </is>
       </c>
       <c r="D440" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>William &amp; Mary; Williams (United States)</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Yuriy Polyakov</t>
+          <t>Luyi Xing</t>
         </is>
       </c>
       <c r="B441" t="n">
@@ -10551,22 +10551,22 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>CCS-WAHC 2025: 13th Workshop on Encrypted Computing &amp; Applied Homomorphic Cryptography.</t>
+          <t>CCS-SaTS '25: The 3rd ACM Workshop on Security and Privacy of AI-Empowered Mobile Super Apps.</t>
         </is>
       </c>
       <c r="D441" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>Duality (United States)</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>Kurt Rohloff</t>
+          <t>Yue Xiao 0007</t>
         </is>
       </c>
       <c r="B442" t="n">
@@ -10574,22 +10574,22 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>CCS-WAHC 2025: 13th Workshop on Encrypted Computing &amp; Applied Homomorphic Cryptography.</t>
+          <t>CCS-SaTS '25: The 3rd ACM Workshop on Security and Privacy of AI-Empowered Mobile Super Apps.</t>
         </is>
       </c>
       <c r="D442" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>Duality (United States)</t>
+          <t>William &amp; Mary; Williams (United States)</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>K. K. Ramakrishnan</t>
+          <t>Yuriy Polyakov</t>
         </is>
       </c>
       <c r="B443" t="n">
@@ -10597,13 +10597,59 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>CCS-free5GC '25: The 1st free5GC World Forum.</t>
+          <t>CCS-WAHC 2025: 13th Workshop on Encrypted Computing &amp; Applied Homomorphic Cryptography.</t>
         </is>
       </c>
       <c r="D443" t="n">
         <v>1</v>
       </c>
       <c r="E443" t="inlineStr">
+        <is>
+          <t>Duality (United States)</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Kurt Rohloff</t>
+        </is>
+      </c>
+      <c r="B444" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>CCS-WAHC 2025: 13th Workshop on Encrypted Computing &amp; Applied Homomorphic Cryptography.</t>
+        </is>
+      </c>
+      <c r="D444" t="n">
+        <v>2</v>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>Duality (United States)</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>K. K. Ramakrishnan</t>
+        </is>
+      </c>
+      <c r="B445" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>CCS-free5GC '25: The 1st free5GC World Forum.</t>
+        </is>
+      </c>
+      <c r="D445" t="n">
+        <v>1</v>
+      </c>
+      <c r="E445" t="inlineStr">
         <is>
           <t>University of California, Riverside</t>
         </is>
